--- a/dados/BD_Bombonas.xlsx
+++ b/dados/BD_Bombonas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupomateus-my.sharepoint.com/personal/hamilton_pires_grupomateus_com/Documents/hamilton/Consultoria/Lidiane/2026/app_bombonas/dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="116" documentId="8_{40E215D4-4623-41EB-B246-4B63951E0A13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EAFEE7CF-26A0-49BF-9FC1-AF19D2FCFF14}"/>
+  <xr:revisionPtr revIDLastSave="123" documentId="8_{40E215D4-4623-41EB-B246-4B63951E0A13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D8BB6E10-B8CE-480A-972E-925FF03919F1}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{9588DCE0-F8D9-46B8-8782-90EC7820DC70}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="BASE BOMBONAS" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BASE BOMBONAS'!$A$1:$L$808</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BASE BOMBONAS'!$A$1:$L$802</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28817,7 +28817,7 @@
     </row>
     <row r="747" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A747" s="1">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B747" t="s">
         <v>2</v>
@@ -28829,10 +28829,10 @@
         <v>0</v>
       </c>
       <c r="E747">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F747">
-        <v>0</v>
+        <v>175</v>
       </c>
       <c r="G747">
         <v>0</v>
@@ -28847,15 +28847,15 @@
         <v>0</v>
       </c>
       <c r="K747">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L747">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="748" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A748" s="1">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B748" t="s">
         <v>3</v>
@@ -28867,10 +28867,10 @@
         <v>0</v>
       </c>
       <c r="E748">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F748">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="G748">
         <v>0</v>
@@ -28879,21 +28879,21 @@
         <v>0</v>
       </c>
       <c r="I748">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J748">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K748">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L748">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="749" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A749" s="1">
-        <v>46024</v>
+        <v>46055</v>
       </c>
       <c r="B749" t="s">
         <v>2</v>
@@ -28905,10 +28905,10 @@
         <v>0</v>
       </c>
       <c r="E749">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F749">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="G749">
         <v>0</v>
@@ -28931,45 +28931,45 @@
     </row>
     <row r="750" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A750" s="1">
-        <v>46024</v>
+        <v>46055</v>
       </c>
       <c r="B750" t="s">
         <v>3</v>
       </c>
       <c r="C750">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D750">
+        <v>0</v>
+      </c>
+      <c r="E750">
+        <v>19</v>
+      </c>
+      <c r="F750">
+        <v>475</v>
+      </c>
+      <c r="G750">
+        <v>0</v>
+      </c>
+      <c r="H750">
+        <v>0</v>
+      </c>
+      <c r="I750">
+        <v>1</v>
+      </c>
+      <c r="J750">
         <v>25</v>
       </c>
-      <c r="E750">
-        <v>36</v>
-      </c>
-      <c r="F750">
-        <v>900</v>
-      </c>
-      <c r="G750">
-        <v>0</v>
-      </c>
-      <c r="H750">
-        <v>0</v>
-      </c>
-      <c r="I750">
-        <v>2</v>
-      </c>
-      <c r="J750">
-        <v>50</v>
-      </c>
       <c r="K750">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L750">
-        <v>100</v>
+        <v>25</v>
       </c>
     </row>
     <row r="751" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A751" s="1">
-        <v>46025</v>
+        <v>46056</v>
       </c>
       <c r="B751" t="s">
         <v>2</v>
@@ -28981,10 +28981,10 @@
         <v>0</v>
       </c>
       <c r="E751">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F751">
-        <v>175</v>
+        <v>125</v>
       </c>
       <c r="G751">
         <v>0</v>
@@ -28993,21 +28993,21 @@
         <v>0</v>
       </c>
       <c r="I751">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J751">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K751">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L751">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="752" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A752" s="1">
-        <v>46025</v>
+        <v>46056</v>
       </c>
       <c r="B752" t="s">
         <v>3</v>
@@ -29019,10 +29019,10 @@
         <v>0</v>
       </c>
       <c r="E752">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F752">
-        <v>425</v>
+        <v>450</v>
       </c>
       <c r="G752">
         <v>0</v>
@@ -29031,10 +29031,10 @@
         <v>0</v>
       </c>
       <c r="I752">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J752">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="K752">
         <v>2</v>
@@ -29045,22 +29045,22 @@
     </row>
     <row r="753" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A753" s="1">
-        <v>46026</v>
+        <v>46057</v>
       </c>
       <c r="B753" t="s">
         <v>2</v>
       </c>
       <c r="C753">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D753">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E753">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F753">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="G753">
         <v>0</v>
@@ -29075,15 +29075,15 @@
         <v>0</v>
       </c>
       <c r="K753">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L753">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="754" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A754" s="1">
-        <v>46026</v>
+        <v>46057</v>
       </c>
       <c r="B754" t="s">
         <v>3</v>
@@ -29095,10 +29095,10 @@
         <v>25</v>
       </c>
       <c r="E754">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F754">
-        <v>450</v>
+        <v>425</v>
       </c>
       <c r="G754">
         <v>0</v>
@@ -29107,21 +29107,21 @@
         <v>0</v>
       </c>
       <c r="I754">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J754">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K754">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L754">
-        <v>50</v>
+        <v>75</v>
       </c>
     </row>
     <row r="755" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A755" s="1">
-        <v>46027</v>
+        <v>46058</v>
       </c>
       <c r="B755" t="s">
         <v>2</v>
@@ -29133,10 +29133,10 @@
         <v>0</v>
       </c>
       <c r="E755">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F755">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="G755">
         <v>0</v>
@@ -29159,7 +29159,7 @@
     </row>
     <row r="756" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A756" s="1">
-        <v>46027</v>
+        <v>46058</v>
       </c>
       <c r="B756" t="s">
         <v>3</v>
@@ -29171,10 +29171,10 @@
         <v>0</v>
       </c>
       <c r="E756">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F756">
-        <v>400</v>
+        <v>475</v>
       </c>
       <c r="G756">
         <v>0</v>
@@ -29183,21 +29183,21 @@
         <v>0</v>
       </c>
       <c r="I756">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J756">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="K756">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L756">
-        <v>60</v>
+        <v>25</v>
       </c>
     </row>
     <row r="757" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A757" s="1">
-        <v>46028</v>
+        <v>46059</v>
       </c>
       <c r="B757" t="s">
         <v>2</v>
@@ -29205,15 +29205,21 @@
       <c r="C757">
         <v>0</v>
       </c>
+      <c r="D757">
+        <v>0</v>
+      </c>
       <c r="E757">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F757">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="G757">
         <v>0</v>
       </c>
+      <c r="H757">
+        <v>0</v>
+      </c>
       <c r="I757">
         <v>0</v>
       </c>
@@ -29221,24 +29227,24 @@
         <v>0</v>
       </c>
       <c r="K757">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L757">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="758" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A758" s="1">
-        <v>46028</v>
+        <v>46059</v>
       </c>
       <c r="B758" t="s">
         <v>3</v>
       </c>
       <c r="C758">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D758">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E758">
         <v>18</v>
@@ -29247,10 +29253,10 @@
         <v>450</v>
       </c>
       <c r="G758">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H758">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I758">
         <v>1</v>
@@ -29259,15 +29265,15 @@
         <v>25</v>
       </c>
       <c r="K758">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L758">
-        <v>40</v>
+        <v>75</v>
       </c>
     </row>
     <row r="759" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A759" s="1">
-        <v>46029</v>
+        <v>46060</v>
       </c>
       <c r="B759" t="s">
         <v>2</v>
@@ -29291,36 +29297,36 @@
         <v>0</v>
       </c>
       <c r="I759">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J759">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K759">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L759">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="760" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A760" s="1">
-        <v>46029</v>
+        <v>46060</v>
       </c>
       <c r="B760" t="s">
         <v>3</v>
       </c>
       <c r="C760">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D760">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E760">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F760">
-        <v>450</v>
+        <v>400</v>
       </c>
       <c r="G760">
         <v>0</v>
@@ -29335,15 +29341,15 @@
         <v>25</v>
       </c>
       <c r="K760">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L760">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="761" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A761" s="1">
-        <v>46030</v>
+        <v>46061</v>
       </c>
       <c r="B761" t="s">
         <v>2</v>
@@ -29381,7 +29387,7 @@
     </row>
     <row r="762" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A762" s="1">
-        <v>46030</v>
+        <v>46061</v>
       </c>
       <c r="B762" t="s">
         <v>3</v>
@@ -29393,10 +29399,10 @@
         <v>0</v>
       </c>
       <c r="E762">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F762">
-        <v>425</v>
+        <v>500</v>
       </c>
       <c r="G762">
         <v>0</v>
@@ -29419,7 +29425,7 @@
     </row>
     <row r="763" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A763" s="1">
-        <v>46031</v>
+        <v>46062</v>
       </c>
       <c r="B763" t="s">
         <v>2</v>
@@ -29431,10 +29437,10 @@
         <v>0</v>
       </c>
       <c r="E763">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F763">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="G763">
         <v>0</v>
@@ -29457,7 +29463,7 @@
     </row>
     <row r="764" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A764" s="1">
-        <v>46031</v>
+        <v>46062</v>
       </c>
       <c r="B764" t="s">
         <v>3</v>
@@ -29475,27 +29481,27 @@
         <v>450</v>
       </c>
       <c r="G764">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H764">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I764">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J764">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="K764">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L764">
-        <v>75</v>
+        <v>25</v>
       </c>
     </row>
     <row r="765" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A765" s="1">
-        <v>46032</v>
+        <v>46063</v>
       </c>
       <c r="B765" t="s">
         <v>2</v>
@@ -29507,10 +29513,10 @@
         <v>0</v>
       </c>
       <c r="E765">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F765">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="G765">
         <v>0</v>
@@ -29533,7 +29539,7 @@
     </row>
     <row r="766" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A766" s="1">
-        <v>46032</v>
+        <v>46063</v>
       </c>
       <c r="B766" t="s">
         <v>3</v>
@@ -29545,10 +29551,10 @@
         <v>0</v>
       </c>
       <c r="E766">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F766">
-        <v>400</v>
+        <v>475</v>
       </c>
       <c r="G766">
         <v>0</v>
@@ -29557,10 +29563,10 @@
         <v>0</v>
       </c>
       <c r="I766">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J766">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K766">
         <v>2</v>
@@ -29571,7 +29577,7 @@
     </row>
     <row r="767" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A767" s="1">
-        <v>46033</v>
+        <v>46064</v>
       </c>
       <c r="B767" t="s">
         <v>2</v>
@@ -29583,10 +29589,10 @@
         <v>0</v>
       </c>
       <c r="E767">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F767">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="G767">
         <v>0</v>
@@ -29609,7 +29615,7 @@
     </row>
     <row r="768" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A768" s="1">
-        <v>46033</v>
+        <v>46064</v>
       </c>
       <c r="B768" t="s">
         <v>3</v>
@@ -29621,33 +29627,33 @@
         <v>0</v>
       </c>
       <c r="E768">
+        <v>17</v>
+      </c>
+      <c r="F768">
+        <v>425</v>
+      </c>
+      <c r="G768">
+        <v>1</v>
+      </c>
+      <c r="H768">
         <v>15</v>
       </c>
-      <c r="F768">
-        <v>375</v>
-      </c>
-      <c r="G768">
-        <v>0</v>
-      </c>
-      <c r="H768">
-        <v>0</v>
-      </c>
       <c r="I768">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J768">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K768">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L768">
-        <v>50</v>
+        <v>75</v>
       </c>
     </row>
     <row r="769" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A769" s="1">
-        <v>46034</v>
+        <v>46065</v>
       </c>
       <c r="B769" t="s">
         <v>2</v>
@@ -29659,10 +29665,10 @@
         <v>0</v>
       </c>
       <c r="E769">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F769">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="G769">
         <v>0</v>
@@ -29677,15 +29683,15 @@
         <v>0</v>
       </c>
       <c r="K769">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L769">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="770" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A770" s="1">
-        <v>46034</v>
+        <v>46065</v>
       </c>
       <c r="B770" t="s">
         <v>3</v>
@@ -29697,10 +29703,10 @@
         <v>0</v>
       </c>
       <c r="E770">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F770">
-        <v>400</v>
+        <v>450</v>
       </c>
       <c r="G770">
         <v>0</v>
@@ -29709,10 +29715,10 @@
         <v>0</v>
       </c>
       <c r="I770">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J770">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="K770">
         <v>2</v>
@@ -29723,7 +29729,7 @@
     </row>
     <row r="771" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A771" s="1">
-        <v>46035</v>
+        <v>46066</v>
       </c>
       <c r="B771" t="s">
         <v>2</v>
@@ -29735,10 +29741,10 @@
         <v>0</v>
       </c>
       <c r="E771">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F771">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="G771">
         <v>0</v>
@@ -29753,30 +29759,30 @@
         <v>0</v>
       </c>
       <c r="K771">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L771">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="772" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A772" s="1">
-        <v>46035</v>
+        <v>46066</v>
       </c>
       <c r="B772" t="s">
         <v>3</v>
       </c>
       <c r="C772">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D772">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E772">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F772">
-        <v>375</v>
+        <v>475</v>
       </c>
       <c r="G772">
         <v>0</v>
@@ -29799,7 +29805,7 @@
     </row>
     <row r="773" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A773" s="1">
-        <v>46036</v>
+        <v>46067</v>
       </c>
       <c r="B773" t="s">
         <v>2</v>
@@ -29811,10 +29817,10 @@
         <v>0</v>
       </c>
       <c r="E773">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F773">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="G773">
         <v>0</v>
@@ -29837,7 +29843,7 @@
     </row>
     <row r="774" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A774" s="1">
-        <v>46036</v>
+        <v>46067</v>
       </c>
       <c r="B774" t="s">
         <v>3</v>
@@ -29861,10 +29867,10 @@
         <v>0</v>
       </c>
       <c r="I774">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J774">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K774">
         <v>2</v>
@@ -29875,7 +29881,7 @@
     </row>
     <row r="775" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A775" s="1">
-        <v>46037</v>
+        <v>46068</v>
       </c>
       <c r="B775" t="s">
         <v>2</v>
@@ -29905,30 +29911,30 @@
         <v>0</v>
       </c>
       <c r="K775">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L775">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="776" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A776" s="1">
-        <v>46037</v>
+        <v>46068</v>
       </c>
       <c r="B776" t="s">
         <v>3</v>
       </c>
       <c r="C776">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D776">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E776">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F776">
-        <v>425</v>
+        <v>450</v>
       </c>
       <c r="G776">
         <v>0</v>
@@ -29937,10 +29943,10 @@
         <v>0</v>
       </c>
       <c r="I776">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J776">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K776">
         <v>2</v>
@@ -29951,7 +29957,7 @@
     </row>
     <row r="777" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A777" s="1">
-        <v>46038</v>
+        <v>46069</v>
       </c>
       <c r="B777" t="s">
         <v>2</v>
@@ -29963,10 +29969,10 @@
         <v>0</v>
       </c>
       <c r="E777">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F777">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="G777">
         <v>0</v>
@@ -29981,53 +29987,53 @@
         <v>0</v>
       </c>
       <c r="K777">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L777">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="778" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A778" s="1">
-        <v>46038</v>
+        <v>46069</v>
       </c>
       <c r="B778" t="s">
         <v>3</v>
       </c>
       <c r="C778">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D778">
+        <v>0</v>
+      </c>
+      <c r="E778">
+        <v>15</v>
+      </c>
+      <c r="F778">
+        <v>375</v>
+      </c>
+      <c r="G778">
+        <v>0</v>
+      </c>
+      <c r="H778">
+        <v>0</v>
+      </c>
+      <c r="I778">
+        <v>1</v>
+      </c>
+      <c r="J778">
+        <v>25</v>
+      </c>
+      <c r="K778">
+        <v>2</v>
+      </c>
+      <c r="L778">
         <v>50</v>
-      </c>
-      <c r="E778">
-        <v>17</v>
-      </c>
-      <c r="F778">
-        <v>425</v>
-      </c>
-      <c r="G778">
-        <v>0</v>
-      </c>
-      <c r="H778">
-        <v>0</v>
-      </c>
-      <c r="I778">
-        <v>0</v>
-      </c>
-      <c r="J778">
-        <v>0</v>
-      </c>
-      <c r="K778">
-        <v>1</v>
-      </c>
-      <c r="L778">
-        <v>20</v>
       </c>
     </row>
     <row r="779" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A779" s="1">
-        <v>46039</v>
+        <v>46070</v>
       </c>
       <c r="B779" t="s">
         <v>2</v>
@@ -30039,10 +30045,10 @@
         <v>0</v>
       </c>
       <c r="E779">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F779">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="G779">
         <v>0</v>
@@ -30057,30 +30063,30 @@
         <v>0</v>
       </c>
       <c r="K779">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L779">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="780" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A780" s="1">
-        <v>46039</v>
+        <v>46070</v>
       </c>
       <c r="B780" t="s">
         <v>3</v>
       </c>
       <c r="C780">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D780">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E780">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F780">
-        <v>425</v>
+        <v>475</v>
       </c>
       <c r="G780">
         <v>0</v>
@@ -30089,10 +30095,10 @@
         <v>0</v>
       </c>
       <c r="I780">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J780">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K780">
         <v>2</v>
@@ -30103,7 +30109,7 @@
     </row>
     <row r="781" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A781" s="1">
-        <v>46040</v>
+        <v>46071</v>
       </c>
       <c r="B781" t="s">
         <v>2</v>
@@ -30115,10 +30121,10 @@
         <v>0</v>
       </c>
       <c r="E781">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F781">
-        <v>100</v>
+        <v>175</v>
       </c>
       <c r="G781">
         <v>0</v>
@@ -30133,15 +30139,15 @@
         <v>0</v>
       </c>
       <c r="K781">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L781">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="782" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A782" s="1">
-        <v>46040</v>
+        <v>46071</v>
       </c>
       <c r="B782" t="s">
         <v>3</v>
@@ -30153,10 +30159,10 @@
         <v>0</v>
       </c>
       <c r="E782">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F782">
-        <v>425</v>
+        <v>400</v>
       </c>
       <c r="G782">
         <v>0</v>
@@ -30165,21 +30171,21 @@
         <v>0</v>
       </c>
       <c r="I782">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J782">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K782">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L782">
-        <v>75</v>
+        <v>50</v>
       </c>
     </row>
     <row r="783" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A783" s="1">
-        <v>46041</v>
+        <v>46072</v>
       </c>
       <c r="B783" t="s">
         <v>2</v>
@@ -30191,10 +30197,10 @@
         <v>0</v>
       </c>
       <c r="E783">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F783">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="G783">
         <v>0</v>
@@ -30217,22 +30223,22 @@
     </row>
     <row r="784" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A784" s="1">
-        <v>46041</v>
+        <v>46072</v>
       </c>
       <c r="B784" t="s">
         <v>3</v>
       </c>
       <c r="C784">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D784">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E784">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F784">
-        <v>550</v>
+        <v>425</v>
       </c>
       <c r="G784">
         <v>0</v>
@@ -30247,15 +30253,15 @@
         <v>25</v>
       </c>
       <c r="K784">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L784">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="785" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A785" s="1">
-        <v>46042</v>
+        <v>46073</v>
       </c>
       <c r="B785" t="s">
         <v>2</v>
@@ -30267,10 +30273,10 @@
         <v>0</v>
       </c>
       <c r="E785">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F785">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="G785">
         <v>0</v>
@@ -30293,7 +30299,7 @@
     </row>
     <row r="786" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A786" s="1">
-        <v>46042</v>
+        <v>46073</v>
       </c>
       <c r="B786" t="s">
         <v>3</v>
@@ -30305,10 +30311,10 @@
         <v>0</v>
       </c>
       <c r="E786">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F786">
-        <v>450</v>
+        <v>375</v>
       </c>
       <c r="G786">
         <v>0</v>
@@ -30331,7 +30337,7 @@
     </row>
     <row r="787" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A787" s="1">
-        <v>46043</v>
+        <v>46074</v>
       </c>
       <c r="B787" t="s">
         <v>2</v>
@@ -30343,10 +30349,10 @@
         <v>0</v>
       </c>
       <c r="E787">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F787">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="G787">
         <v>0</v>
@@ -30361,15 +30367,15 @@
         <v>0</v>
       </c>
       <c r="K787">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L787">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="788" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A788" s="1">
-        <v>46043</v>
+        <v>46074</v>
       </c>
       <c r="B788" t="s">
         <v>3</v>
@@ -30381,10 +30387,10 @@
         <v>0</v>
       </c>
       <c r="E788">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F788">
-        <v>250</v>
+        <v>425</v>
       </c>
       <c r="G788">
         <v>0</v>
@@ -30393,10 +30399,10 @@
         <v>0</v>
       </c>
       <c r="I788">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J788">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="K788">
         <v>1</v>
@@ -30407,7 +30413,7 @@
     </row>
     <row r="789" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A789" s="1">
-        <v>46044</v>
+        <v>46075</v>
       </c>
       <c r="B789" t="s">
         <v>2</v>
@@ -30445,7 +30451,7 @@
     </row>
     <row r="790" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A790" s="1">
-        <v>46044</v>
+        <v>46075</v>
       </c>
       <c r="B790" t="s">
         <v>3</v>
@@ -30457,10 +30463,10 @@
         <v>0</v>
       </c>
       <c r="E790">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F790">
-        <v>425</v>
+        <v>400</v>
       </c>
       <c r="G790">
         <v>0</v>
@@ -30483,22 +30489,22 @@
     </row>
     <row r="791" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A791" s="1">
-        <v>46045</v>
+        <v>46076</v>
       </c>
       <c r="B791" t="s">
         <v>2</v>
       </c>
       <c r="C791">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D791">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E791">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F791">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="G791">
         <v>0</v>
@@ -30521,7 +30527,7 @@
     </row>
     <row r="792" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A792" s="1">
-        <v>46045</v>
+        <v>46076</v>
       </c>
       <c r="B792" t="s">
         <v>3</v>
@@ -30533,10 +30539,10 @@
         <v>0</v>
       </c>
       <c r="E792">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F792">
-        <v>475</v>
+        <v>500</v>
       </c>
       <c r="G792">
         <v>0</v>
@@ -30545,21 +30551,21 @@
         <v>0</v>
       </c>
       <c r="I792">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J792">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K792">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L792">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="793" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A793" s="1">
-        <v>46046</v>
+        <v>46077</v>
       </c>
       <c r="B793" t="s">
         <v>2</v>
@@ -30571,10 +30577,10 @@
         <v>0</v>
       </c>
       <c r="E793">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F793">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="G793">
         <v>0</v>
@@ -30589,30 +30595,30 @@
         <v>0</v>
       </c>
       <c r="K793">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L793">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="794" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A794" s="1">
-        <v>46046</v>
+        <v>46077</v>
       </c>
       <c r="B794" t="s">
         <v>3</v>
       </c>
       <c r="C794">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D794">
         <v>0</v>
       </c>
       <c r="E794">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F794">
-        <v>425</v>
+        <v>450</v>
       </c>
       <c r="G794">
         <v>0</v>
@@ -30621,21 +30627,21 @@
         <v>0</v>
       </c>
       <c r="I794">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J794">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="K794">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L794">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="795" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A795" s="1">
-        <v>46047</v>
+        <v>46078</v>
       </c>
       <c r="B795" t="s">
         <v>2</v>
@@ -30647,10 +30653,10 @@
         <v>0</v>
       </c>
       <c r="E795">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F795">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="G795">
         <v>0</v>
@@ -30665,15 +30671,15 @@
         <v>0</v>
       </c>
       <c r="K795">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L795">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="796" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A796" s="1">
-        <v>46047</v>
+        <v>46078</v>
       </c>
       <c r="B796" t="s">
         <v>3</v>
@@ -30703,15 +30709,15 @@
         <v>25</v>
       </c>
       <c r="K796">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L796">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="797" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A797" s="1">
-        <v>46048</v>
+        <v>46079</v>
       </c>
       <c r="B797" t="s">
         <v>2</v>
@@ -30723,10 +30729,10 @@
         <v>0</v>
       </c>
       <c r="E797">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F797">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="G797">
         <v>0</v>
@@ -30741,53 +30747,53 @@
         <v>0</v>
       </c>
       <c r="K797">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L797">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="798" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A798" s="1">
-        <v>46048</v>
+        <v>46079</v>
       </c>
       <c r="B798" t="s">
         <v>3</v>
       </c>
       <c r="C798">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D798">
+        <v>0</v>
+      </c>
+      <c r="E798">
+        <v>17</v>
+      </c>
+      <c r="F798">
+        <v>425</v>
+      </c>
+      <c r="G798">
+        <v>1</v>
+      </c>
+      <c r="H798">
+        <v>15</v>
+      </c>
+      <c r="I798">
+        <v>1</v>
+      </c>
+      <c r="J798">
         <v>25</v>
       </c>
-      <c r="E798">
-        <v>16</v>
-      </c>
-      <c r="F798">
-        <v>450</v>
-      </c>
-      <c r="G798">
-        <v>0</v>
-      </c>
-      <c r="H798">
-        <v>0</v>
-      </c>
-      <c r="I798">
-        <v>0</v>
-      </c>
-      <c r="J798">
-        <v>0</v>
-      </c>
       <c r="K798">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L798">
-        <v>75</v>
+        <v>100</v>
       </c>
     </row>
     <row r="799" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A799" s="1">
-        <v>46049</v>
+        <v>46080</v>
       </c>
       <c r="B799" t="s">
         <v>2</v>
@@ -30799,10 +30805,10 @@
         <v>0</v>
       </c>
       <c r="E799">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F799">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="G799">
         <v>0</v>
@@ -30817,15 +30823,15 @@
         <v>0</v>
       </c>
       <c r="K799">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L799">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="800" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A800" s="1">
-        <v>46049</v>
+        <v>46080</v>
       </c>
       <c r="B800" t="s">
         <v>3</v>
@@ -30837,10 +30843,10 @@
         <v>0</v>
       </c>
       <c r="E800">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F800">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="G800">
         <v>0</v>
@@ -30849,10 +30855,10 @@
         <v>0</v>
       </c>
       <c r="I800">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J800">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="K800">
         <v>2</v>
@@ -30863,22 +30869,22 @@
     </row>
     <row r="801" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A801" s="1">
-        <v>46050</v>
+        <v>46081</v>
       </c>
       <c r="B801" t="s">
         <v>2</v>
       </c>
       <c r="C801">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="D801">
-        <v>425</v>
+        <v>0</v>
       </c>
       <c r="E801">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F801">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="G801">
         <v>0</v>
@@ -30893,30 +30899,30 @@
         <v>0</v>
       </c>
       <c r="K801">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L801">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="802" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A802" s="1">
-        <v>46050</v>
+        <v>46081</v>
       </c>
       <c r="B802" t="s">
         <v>3</v>
       </c>
       <c r="C802">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D802">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E802">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F802">
-        <v>525</v>
+        <v>400</v>
       </c>
       <c r="G802">
         <v>0</v>
@@ -30931,15 +30937,15 @@
         <v>25</v>
       </c>
       <c r="K802">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L802">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="803" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A803" s="1">
-        <v>46051</v>
+        <v>46023</v>
       </c>
       <c r="B803" t="s">
         <v>2</v>
@@ -30951,10 +30957,10 @@
         <v>0</v>
       </c>
       <c r="E803">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F803">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G803">
         <v>0</v>
@@ -30963,10 +30969,10 @@
         <v>0</v>
       </c>
       <c r="I803">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J803">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K803">
         <v>0</v>
@@ -30977,7 +30983,7 @@
     </row>
     <row r="804" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A804" s="1">
-        <v>46051</v>
+        <v>46023</v>
       </c>
       <c r="B804" t="s">
         <v>3</v>
@@ -30989,10 +30995,10 @@
         <v>0</v>
       </c>
       <c r="E804">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F804">
-        <v>450</v>
+        <v>0</v>
       </c>
       <c r="G804">
         <v>0</v>
@@ -31001,21 +31007,21 @@
         <v>0</v>
       </c>
       <c r="I804">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J804">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="K804">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L804">
-        <v>75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="805" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A805" s="1">
-        <v>46052</v>
+        <v>46024</v>
       </c>
       <c r="B805" t="s">
         <v>2</v>
@@ -31027,10 +31033,10 @@
         <v>0</v>
       </c>
       <c r="E805">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F805">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="G805">
         <v>0</v>
@@ -31053,22 +31059,22 @@
     </row>
     <row r="806" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A806" s="1">
-        <v>46052</v>
+        <v>46024</v>
       </c>
       <c r="B806" t="s">
         <v>3</v>
       </c>
       <c r="C806">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D806">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E806">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="F806">
-        <v>425</v>
+        <v>900</v>
       </c>
       <c r="G806">
         <v>0</v>
@@ -31077,21 +31083,21 @@
         <v>0</v>
       </c>
       <c r="I806">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J806">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K806">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L806">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="807" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A807" s="1">
-        <v>46053</v>
+        <v>46025</v>
       </c>
       <c r="B807" t="s">
         <v>2</v>
@@ -31103,10 +31109,10 @@
         <v>0</v>
       </c>
       <c r="E807">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F807">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="G807">
         <v>0</v>
@@ -31115,21 +31121,21 @@
         <v>0</v>
       </c>
       <c r="I807">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J807">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K807">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L807">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="808" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A808" s="1">
-        <v>46053</v>
+        <v>46025</v>
       </c>
       <c r="B808" t="s">
         <v>3</v>
@@ -31141,10 +31147,10 @@
         <v>0</v>
       </c>
       <c r="E808">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F808">
-        <v>475</v>
+        <v>425</v>
       </c>
       <c r="G808">
         <v>0</v>
@@ -31159,15 +31165,15 @@
         <v>25</v>
       </c>
       <c r="K808">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L808">
-        <v>75</v>
+        <v>50</v>
       </c>
     </row>
     <row r="809" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A809" s="1">
-        <v>46054</v>
+        <v>46026</v>
       </c>
       <c r="B809" t="s">
         <v>2</v>
@@ -31179,10 +31185,10 @@
         <v>0</v>
       </c>
       <c r="E809">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F809">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="G809">
         <v>0</v>
@@ -31197,30 +31203,30 @@
         <v>0</v>
       </c>
       <c r="K809">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L809">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="810" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A810" s="1">
-        <v>46054</v>
+        <v>46026</v>
       </c>
       <c r="B810" t="s">
         <v>3</v>
       </c>
       <c r="C810">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D810">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E810">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F810">
-        <v>400</v>
+        <v>450</v>
       </c>
       <c r="G810">
         <v>0</v>
@@ -31229,10 +31235,10 @@
         <v>0</v>
       </c>
       <c r="I810">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J810">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K810">
         <v>2</v>
@@ -31243,7 +31249,7 @@
     </row>
     <row r="811" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A811" s="1">
-        <v>46055</v>
+        <v>46027</v>
       </c>
       <c r="B811" t="s">
         <v>2</v>
@@ -31255,10 +31261,10 @@
         <v>0</v>
       </c>
       <c r="E811">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F811">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="G811">
         <v>0</v>
@@ -31281,7 +31287,7 @@
     </row>
     <row r="812" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A812" s="1">
-        <v>46055</v>
+        <v>46027</v>
       </c>
       <c r="B812" t="s">
         <v>3</v>
@@ -31293,10 +31299,10 @@
         <v>0</v>
       </c>
       <c r="E812">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F812">
-        <v>475</v>
+        <v>400</v>
       </c>
       <c r="G812">
         <v>0</v>
@@ -31305,21 +31311,21 @@
         <v>0</v>
       </c>
       <c r="I812">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J812">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="K812">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L812">
-        <v>25</v>
+        <v>60</v>
       </c>
     </row>
     <row r="813" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A813" s="1">
-        <v>46056</v>
+        <v>46028</v>
       </c>
       <c r="B813" t="s">
         <v>2</v>
@@ -31327,19 +31333,13 @@
       <c r="C813">
         <v>0</v>
       </c>
-      <c r="D813">
-        <v>0</v>
-      </c>
       <c r="E813">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F813">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="G813">
-        <v>0</v>
-      </c>
-      <c r="H813">
         <v>0</v>
       </c>
       <c r="I813">
@@ -31357,16 +31357,16 @@
     </row>
     <row r="814" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A814" s="1">
-        <v>46056</v>
+        <v>46028</v>
       </c>
       <c r="B814" t="s">
         <v>3</v>
       </c>
       <c r="C814">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D814">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E814">
         <v>18</v>
@@ -31381,48 +31381,48 @@
         <v>0</v>
       </c>
       <c r="I814">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J814">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="K814">
         <v>2</v>
       </c>
       <c r="L814">
-        <v>50</v>
+        <v>40</v>
       </c>
     </row>
     <row r="815" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A815" s="1">
-        <v>46057</v>
+        <v>46029</v>
       </c>
       <c r="B815" t="s">
         <v>2</v>
       </c>
       <c r="C815">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D815">
+        <v>0</v>
+      </c>
+      <c r="E815">
+        <v>5</v>
+      </c>
+      <c r="F815">
+        <v>125</v>
+      </c>
+      <c r="G815">
+        <v>0</v>
+      </c>
+      <c r="H815">
+        <v>0</v>
+      </c>
+      <c r="I815">
+        <v>1</v>
+      </c>
+      <c r="J815">
         <v>25</v>
-      </c>
-      <c r="E815">
-        <v>7</v>
-      </c>
-      <c r="F815">
-        <v>175</v>
-      </c>
-      <c r="G815">
-        <v>0</v>
-      </c>
-      <c r="H815">
-        <v>0</v>
-      </c>
-      <c r="I815">
-        <v>0</v>
-      </c>
-      <c r="J815">
-        <v>0</v>
       </c>
       <c r="K815">
         <v>1</v>
@@ -31433,7 +31433,7 @@
     </row>
     <row r="816" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A816" s="1">
-        <v>46057</v>
+        <v>46029</v>
       </c>
       <c r="B816" t="s">
         <v>3</v>
@@ -31445,10 +31445,10 @@
         <v>25</v>
       </c>
       <c r="E816">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F816">
-        <v>425</v>
+        <v>450</v>
       </c>
       <c r="G816">
         <v>0</v>
@@ -31463,15 +31463,15 @@
         <v>25</v>
       </c>
       <c r="K816">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L816">
-        <v>75</v>
+        <v>25</v>
       </c>
     </row>
     <row r="817" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A817" s="1">
-        <v>46058</v>
+        <v>46030</v>
       </c>
       <c r="B817" t="s">
         <v>2</v>
@@ -31501,15 +31501,15 @@
         <v>0</v>
       </c>
       <c r="K817">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L817">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="818" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A818" s="1">
-        <v>46058</v>
+        <v>46030</v>
       </c>
       <c r="B818" t="s">
         <v>3</v>
@@ -31521,10 +31521,10 @@
         <v>0</v>
       </c>
       <c r="E818">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F818">
-        <v>475</v>
+        <v>425</v>
       </c>
       <c r="G818">
         <v>0</v>
@@ -31533,21 +31533,21 @@
         <v>0</v>
       </c>
       <c r="I818">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J818">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K818">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L818">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="819" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A819" s="1">
-        <v>46059</v>
+        <v>46031</v>
       </c>
       <c r="B819" t="s">
         <v>2</v>
@@ -31559,10 +31559,10 @@
         <v>0</v>
       </c>
       <c r="E819">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F819">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="G819">
         <v>0</v>
@@ -31577,15 +31577,15 @@
         <v>0</v>
       </c>
       <c r="K819">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L819">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="820" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A820" s="1">
-        <v>46059</v>
+        <v>46031</v>
       </c>
       <c r="B820" t="s">
         <v>3</v>
@@ -31603,16 +31603,16 @@
         <v>450</v>
       </c>
       <c r="G820">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H820">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I820">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J820">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="K820">
         <v>3</v>
@@ -31623,7 +31623,7 @@
     </row>
     <row r="821" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A821" s="1">
-        <v>46060</v>
+        <v>46032</v>
       </c>
       <c r="B821" t="s">
         <v>2</v>
@@ -31635,10 +31635,10 @@
         <v>0</v>
       </c>
       <c r="E821">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F821">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="G821">
         <v>0</v>
@@ -31653,15 +31653,15 @@
         <v>0</v>
       </c>
       <c r="K821">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L821">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="822" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A822" s="1">
-        <v>46060</v>
+        <v>46032</v>
       </c>
       <c r="B822" t="s">
         <v>3</v>
@@ -31685,10 +31685,10 @@
         <v>0</v>
       </c>
       <c r="I822">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J822">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K822">
         <v>2</v>
@@ -31699,7 +31699,7 @@
     </row>
     <row r="823" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A823" s="1">
-        <v>46061</v>
+        <v>46033</v>
       </c>
       <c r="B823" t="s">
         <v>2</v>
@@ -31711,10 +31711,10 @@
         <v>0</v>
       </c>
       <c r="E823">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F823">
-        <v>175</v>
+        <v>125</v>
       </c>
       <c r="G823">
         <v>0</v>
@@ -31729,15 +31729,15 @@
         <v>0</v>
       </c>
       <c r="K823">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L823">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="824" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A824" s="1">
-        <v>46061</v>
+        <v>46033</v>
       </c>
       <c r="B824" t="s">
         <v>3</v>
@@ -31749,10 +31749,10 @@
         <v>0</v>
       </c>
       <c r="E824">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F824">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="G824">
         <v>0</v>
@@ -31761,10 +31761,10 @@
         <v>0</v>
       </c>
       <c r="I824">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J824">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K824">
         <v>2</v>
@@ -31775,7 +31775,7 @@
     </row>
     <row r="825" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A825" s="1">
-        <v>46062</v>
+        <v>46034</v>
       </c>
       <c r="B825" t="s">
         <v>2</v>
@@ -31787,10 +31787,10 @@
         <v>0</v>
       </c>
       <c r="E825">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F825">
-        <v>175</v>
+        <v>125</v>
       </c>
       <c r="G825">
         <v>0</v>
@@ -31813,7 +31813,7 @@
     </row>
     <row r="826" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A826" s="1">
-        <v>46062</v>
+        <v>46034</v>
       </c>
       <c r="B826" t="s">
         <v>3</v>
@@ -31825,33 +31825,33 @@
         <v>0</v>
       </c>
       <c r="E826">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F826">
-        <v>450</v>
+        <v>400</v>
       </c>
       <c r="G826">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H826">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I826">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J826">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K826">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L826">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="827" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A827" s="1">
-        <v>46063</v>
+        <v>46035</v>
       </c>
       <c r="B827" t="s">
         <v>2</v>
@@ -31863,10 +31863,10 @@
         <v>0</v>
       </c>
       <c r="E827">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F827">
-        <v>200</v>
+        <v>125</v>
       </c>
       <c r="G827">
         <v>0</v>
@@ -31889,22 +31889,22 @@
     </row>
     <row r="828" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A828" s="1">
-        <v>46063</v>
+        <v>46035</v>
       </c>
       <c r="B828" t="s">
         <v>3</v>
       </c>
       <c r="C828">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D828">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E828">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F828">
-        <v>475</v>
+        <v>375</v>
       </c>
       <c r="G828">
         <v>0</v>
@@ -31913,10 +31913,10 @@
         <v>0</v>
       </c>
       <c r="I828">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J828">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="K828">
         <v>2</v>
@@ -31927,7 +31927,7 @@
     </row>
     <row r="829" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A829" s="1">
-        <v>46064</v>
+        <v>46036</v>
       </c>
       <c r="B829" t="s">
         <v>2</v>
@@ -31939,10 +31939,10 @@
         <v>0</v>
       </c>
       <c r="E829">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F829">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="G829">
         <v>0</v>
@@ -31957,15 +31957,15 @@
         <v>0</v>
       </c>
       <c r="K829">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L829">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="830" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A830" s="1">
-        <v>46064</v>
+        <v>46036</v>
       </c>
       <c r="B830" t="s">
         <v>3</v>
@@ -31977,33 +31977,33 @@
         <v>0</v>
       </c>
       <c r="E830">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F830">
-        <v>425</v>
+        <v>475</v>
       </c>
       <c r="G830">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H830">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I830">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J830">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K830">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L830">
-        <v>75</v>
+        <v>50</v>
       </c>
     </row>
     <row r="831" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A831" s="1">
-        <v>46065</v>
+        <v>46037</v>
       </c>
       <c r="B831" t="s">
         <v>2</v>
@@ -32015,10 +32015,10 @@
         <v>0</v>
       </c>
       <c r="E831">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F831">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="G831">
         <v>0</v>
@@ -32041,22 +32041,22 @@
     </row>
     <row r="832" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A832" s="1">
-        <v>46065</v>
+        <v>46037</v>
       </c>
       <c r="B832" t="s">
         <v>3</v>
       </c>
       <c r="C832">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D832">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E832">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F832">
-        <v>450</v>
+        <v>425</v>
       </c>
       <c r="G832">
         <v>0</v>
@@ -32065,10 +32065,10 @@
         <v>0</v>
       </c>
       <c r="I832">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J832">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="K832">
         <v>2</v>
@@ -32079,7 +32079,7 @@
     </row>
     <row r="833" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A833" s="1">
-        <v>46066</v>
+        <v>46038</v>
       </c>
       <c r="B833" t="s">
         <v>2</v>
@@ -32091,10 +32091,10 @@
         <v>0</v>
       </c>
       <c r="E833">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F833">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="G833">
         <v>0</v>
@@ -32117,22 +32117,22 @@
     </row>
     <row r="834" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A834" s="1">
-        <v>46066</v>
+        <v>46038</v>
       </c>
       <c r="B834" t="s">
         <v>3</v>
       </c>
       <c r="C834">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D834">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E834">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F834">
-        <v>475</v>
+        <v>425</v>
       </c>
       <c r="G834">
         <v>0</v>
@@ -32141,21 +32141,21 @@
         <v>0</v>
       </c>
       <c r="I834">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J834">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K834">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L834">
-        <v>50</v>
+        <v>20</v>
       </c>
     </row>
     <row r="835" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A835" s="1">
-        <v>46067</v>
+        <v>46039</v>
       </c>
       <c r="B835" t="s">
         <v>2</v>
@@ -32167,10 +32167,10 @@
         <v>0</v>
       </c>
       <c r="E835">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F835">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="G835">
         <v>0</v>
@@ -32193,22 +32193,22 @@
     </row>
     <row r="836" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A836" s="1">
-        <v>46067</v>
+        <v>46039</v>
       </c>
       <c r="B836" t="s">
         <v>3</v>
       </c>
       <c r="C836">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D836">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E836">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F836">
-        <v>475</v>
+        <v>425</v>
       </c>
       <c r="G836">
         <v>0</v>
@@ -32217,10 +32217,10 @@
         <v>0</v>
       </c>
       <c r="I836">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J836">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K836">
         <v>2</v>
@@ -32231,7 +32231,7 @@
     </row>
     <row r="837" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A837" s="1">
-        <v>46068</v>
+        <v>46040</v>
       </c>
       <c r="B837" t="s">
         <v>2</v>
@@ -32243,10 +32243,10 @@
         <v>0</v>
       </c>
       <c r="E837">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F837">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="G837">
         <v>0</v>
@@ -32269,7 +32269,7 @@
     </row>
     <row r="838" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A838" s="1">
-        <v>46068</v>
+        <v>46040</v>
       </c>
       <c r="B838" t="s">
         <v>3</v>
@@ -32281,10 +32281,10 @@
         <v>0</v>
       </c>
       <c r="E838">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F838">
-        <v>450</v>
+        <v>425</v>
       </c>
       <c r="G838">
         <v>0</v>
@@ -32299,15 +32299,15 @@
         <v>0</v>
       </c>
       <c r="K838">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L838">
-        <v>50</v>
+        <v>75</v>
       </c>
     </row>
     <row r="839" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A839" s="1">
-        <v>46069</v>
+        <v>46041</v>
       </c>
       <c r="B839" t="s">
         <v>2</v>
@@ -32319,10 +32319,10 @@
         <v>0</v>
       </c>
       <c r="E839">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F839">
-        <v>175</v>
+        <v>200</v>
       </c>
       <c r="G839">
         <v>0</v>
@@ -32337,30 +32337,30 @@
         <v>0</v>
       </c>
       <c r="K839">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L839">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="840" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A840" s="1">
-        <v>46069</v>
+        <v>46041</v>
       </c>
       <c r="B840" t="s">
         <v>3</v>
       </c>
       <c r="C840">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D840">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E840">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F840">
-        <v>375</v>
+        <v>550</v>
       </c>
       <c r="G840">
         <v>0</v>
@@ -32383,7 +32383,7 @@
     </row>
     <row r="841" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A841" s="1">
-        <v>46070</v>
+        <v>46042</v>
       </c>
       <c r="B841" t="s">
         <v>2</v>
@@ -32395,10 +32395,10 @@
         <v>0</v>
       </c>
       <c r="E841">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F841">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="G841">
         <v>0</v>
@@ -32413,15 +32413,15 @@
         <v>0</v>
       </c>
       <c r="K841">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L841">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="842" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A842" s="1">
-        <v>46070</v>
+        <v>46042</v>
       </c>
       <c r="B842" t="s">
         <v>3</v>
@@ -32433,10 +32433,10 @@
         <v>0</v>
       </c>
       <c r="E842">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F842">
-        <v>475</v>
+        <v>450</v>
       </c>
       <c r="G842">
         <v>0</v>
@@ -32445,10 +32445,10 @@
         <v>0</v>
       </c>
       <c r="I842">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J842">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K842">
         <v>2</v>
@@ -32459,7 +32459,7 @@
     </row>
     <row r="843" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A843" s="1">
-        <v>46071</v>
+        <v>46043</v>
       </c>
       <c r="B843" t="s">
         <v>2</v>
@@ -32471,10 +32471,10 @@
         <v>0</v>
       </c>
       <c r="E843">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F843">
-        <v>175</v>
+        <v>100</v>
       </c>
       <c r="G843">
         <v>0</v>
@@ -32497,7 +32497,7 @@
     </row>
     <row r="844" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A844" s="1">
-        <v>46071</v>
+        <v>46043</v>
       </c>
       <c r="B844" t="s">
         <v>3</v>
@@ -32509,10 +32509,10 @@
         <v>0</v>
       </c>
       <c r="E844">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F844">
-        <v>400</v>
+        <v>250</v>
       </c>
       <c r="G844">
         <v>0</v>
@@ -32521,21 +32521,21 @@
         <v>0</v>
       </c>
       <c r="I844">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J844">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="K844">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L844">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="845" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A845" s="1">
-        <v>46072</v>
+        <v>46044</v>
       </c>
       <c r="B845" t="s">
         <v>2</v>
@@ -32573,7 +32573,7 @@
     </row>
     <row r="846" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A846" s="1">
-        <v>46072</v>
+        <v>46044</v>
       </c>
       <c r="B846" t="s">
         <v>3</v>
@@ -32603,30 +32603,30 @@
         <v>25</v>
       </c>
       <c r="K846">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L846">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="847" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A847" s="1">
-        <v>46073</v>
+        <v>46045</v>
       </c>
       <c r="B847" t="s">
         <v>2</v>
       </c>
       <c r="C847">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D847">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E847">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F847">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="G847">
         <v>0</v>
@@ -32649,7 +32649,7 @@
     </row>
     <row r="848" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A848" s="1">
-        <v>46073</v>
+        <v>46045</v>
       </c>
       <c r="B848" t="s">
         <v>3</v>
@@ -32661,10 +32661,10 @@
         <v>0</v>
       </c>
       <c r="E848">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F848">
-        <v>375</v>
+        <v>475</v>
       </c>
       <c r="G848">
         <v>0</v>
@@ -32673,21 +32673,21 @@
         <v>0</v>
       </c>
       <c r="I848">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J848">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K848">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L848">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="849" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A849" s="1">
-        <v>46074</v>
+        <v>46046</v>
       </c>
       <c r="B849" t="s">
         <v>2</v>
@@ -32717,21 +32717,21 @@
         <v>0</v>
       </c>
       <c r="K849">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L849">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="850" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A850" s="1">
-        <v>46074</v>
+        <v>46046</v>
       </c>
       <c r="B850" t="s">
         <v>3</v>
       </c>
       <c r="C850">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D850">
         <v>0</v>
@@ -32749,10 +32749,10 @@
         <v>0</v>
       </c>
       <c r="I850">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J850">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="K850">
         <v>1</v>
@@ -32763,7 +32763,7 @@
     </row>
     <row r="851" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A851" s="1">
-        <v>46075</v>
+        <v>46047</v>
       </c>
       <c r="B851" t="s">
         <v>2</v>
@@ -32775,10 +32775,10 @@
         <v>0</v>
       </c>
       <c r="E851">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F851">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="G851">
         <v>0</v>
@@ -32801,7 +32801,7 @@
     </row>
     <row r="852" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A852" s="1">
-        <v>46075</v>
+        <v>46047</v>
       </c>
       <c r="B852" t="s">
         <v>3</v>
@@ -32813,10 +32813,10 @@
         <v>0</v>
       </c>
       <c r="E852">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F852">
-        <v>400</v>
+        <v>450</v>
       </c>
       <c r="G852">
         <v>0</v>
@@ -32831,15 +32831,15 @@
         <v>25</v>
       </c>
       <c r="K852">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L852">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="853" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A853" s="1">
-        <v>46076</v>
+        <v>46048</v>
       </c>
       <c r="B853" t="s">
         <v>2</v>
@@ -32851,10 +32851,10 @@
         <v>0</v>
       </c>
       <c r="E853">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F853">
-        <v>125</v>
+        <v>200</v>
       </c>
       <c r="G853">
         <v>0</v>
@@ -32877,22 +32877,22 @@
     </row>
     <row r="854" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A854" s="1">
-        <v>46076</v>
+        <v>46048</v>
       </c>
       <c r="B854" t="s">
         <v>3</v>
       </c>
       <c r="C854">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D854">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E854">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F854">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="G854">
         <v>0</v>
@@ -32901,21 +32901,21 @@
         <v>0</v>
       </c>
       <c r="I854">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J854">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K854">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L854">
-        <v>50</v>
+        <v>75</v>
       </c>
     </row>
     <row r="855" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A855" s="1">
-        <v>46077</v>
+        <v>46049</v>
       </c>
       <c r="B855" t="s">
         <v>2</v>
@@ -32927,10 +32927,10 @@
         <v>0</v>
       </c>
       <c r="E855">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F855">
-        <v>175</v>
+        <v>200</v>
       </c>
       <c r="G855">
         <v>0</v>
@@ -32953,7 +32953,7 @@
     </row>
     <row r="856" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A856" s="1">
-        <v>46077</v>
+        <v>46049</v>
       </c>
       <c r="B856" t="s">
         <v>3</v>
@@ -32965,10 +32965,10 @@
         <v>0</v>
       </c>
       <c r="E856">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F856">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="G856">
         <v>0</v>
@@ -32977,10 +32977,10 @@
         <v>0</v>
       </c>
       <c r="I856">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J856">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="K856">
         <v>2</v>
@@ -32991,7 +32991,7 @@
     </row>
     <row r="857" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A857" s="1">
-        <v>46078</v>
+        <v>46050</v>
       </c>
       <c r="B857" t="s">
         <v>2</v>
@@ -33003,10 +33003,10 @@
         <v>0</v>
       </c>
       <c r="E857">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F857">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="G857">
         <v>0</v>
@@ -33029,22 +33029,22 @@
     </row>
     <row r="858" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A858" s="1">
-        <v>46078</v>
+        <v>46050</v>
       </c>
       <c r="B858" t="s">
         <v>3</v>
       </c>
       <c r="C858">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D858">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E858">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F858">
-        <v>450</v>
+        <v>525</v>
       </c>
       <c r="G858">
         <v>0</v>
@@ -33059,15 +33059,15 @@
         <v>25</v>
       </c>
       <c r="K858">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L858">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="859" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A859" s="1">
-        <v>46079</v>
+        <v>46051</v>
       </c>
       <c r="B859" t="s">
         <v>2</v>
@@ -33079,10 +33079,10 @@
         <v>0</v>
       </c>
       <c r="E859">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F859">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="G859">
         <v>0</v>
@@ -33091,10 +33091,10 @@
         <v>0</v>
       </c>
       <c r="I859">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J859">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K859">
         <v>0</v>
@@ -33105,7 +33105,7 @@
     </row>
     <row r="860" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A860" s="1">
-        <v>46079</v>
+        <v>46051</v>
       </c>
       <c r="B860" t="s">
         <v>3</v>
@@ -33117,33 +33117,33 @@
         <v>0</v>
       </c>
       <c r="E860">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F860">
-        <v>425</v>
+        <v>450</v>
       </c>
       <c r="G860">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H860">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I860">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J860">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="K860">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L860">
-        <v>100</v>
+        <v>75</v>
       </c>
     </row>
     <row r="861" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A861" s="1">
-        <v>46080</v>
+        <v>46052</v>
       </c>
       <c r="B861" t="s">
         <v>2</v>
@@ -33173,15 +33173,15 @@
         <v>0</v>
       </c>
       <c r="K861">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L861">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="862" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A862" s="1">
-        <v>46080</v>
+        <v>46052</v>
       </c>
       <c r="B862" t="s">
         <v>3</v>
@@ -33193,10 +33193,10 @@
         <v>0</v>
       </c>
       <c r="E862">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F862">
-        <v>450</v>
+        <v>425</v>
       </c>
       <c r="G862">
         <v>0</v>
@@ -33205,10 +33205,10 @@
         <v>0</v>
       </c>
       <c r="I862">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J862">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K862">
         <v>2</v>
@@ -33219,7 +33219,7 @@
     </row>
     <row r="863" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A863" s="1">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B863" t="s">
         <v>2</v>
@@ -33249,15 +33249,15 @@
         <v>0</v>
       </c>
       <c r="K863">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L863">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="864" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A864" s="1">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B864" t="s">
         <v>3</v>
@@ -33269,10 +33269,10 @@
         <v>0</v>
       </c>
       <c r="E864">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F864">
-        <v>400</v>
+        <v>475</v>
       </c>
       <c r="G864">
         <v>0</v>
@@ -33287,10 +33287,10 @@
         <v>25</v>
       </c>
       <c r="K864">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L864">
-        <v>50</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/dados/BD_Bombonas.xlsx
+++ b/dados/BD_Bombonas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupomateus-my.sharepoint.com/personal/hamilton_pires_grupomateus_com/Documents/hamilton/Consultoria/Lidiane/2026/app_bombonas/dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="123" documentId="8_{40E215D4-4623-41EB-B246-4B63951E0A13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D8BB6E10-B8CE-480A-972E-925FF03919F1}"/>
+  <xr:revisionPtr revIDLastSave="198" documentId="8_{40E215D4-4623-41EB-B246-4B63951E0A13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F4EC47C-0C1D-4A60-A064-51090B02DF62}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{9588DCE0-F8D9-46B8-8782-90EC7820DC70}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="BASE BOMBONAS" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BASE BOMBONAS'!$A$1:$L$802</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BASE BOMBONAS'!$A$1:$L$926</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="875" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="937" uniqueCount="14">
   <si>
     <t>DATA</t>
   </si>
@@ -99,12 +99,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -119,9 +125,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -459,7 +467,7 @@
   <sheetPr>
     <tabColor theme="6" tint="0.39997558519241921"/>
   </sheetPr>
-  <dimension ref="A1:L864"/>
+  <dimension ref="A1:L926"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
@@ -28817,7 +28825,7 @@
     </row>
     <row r="747" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A747" s="1">
-        <v>46054</v>
+        <v>46023</v>
       </c>
       <c r="B747" t="s">
         <v>2</v>
@@ -28829,10 +28837,10 @@
         <v>0</v>
       </c>
       <c r="E747">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F747">
-        <v>175</v>
+        <v>0</v>
       </c>
       <c r="G747">
         <v>0</v>
@@ -28847,15 +28855,15 @@
         <v>0</v>
       </c>
       <c r="K747">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L747">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="748" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A748" s="1">
-        <v>46054</v>
+        <v>46023</v>
       </c>
       <c r="B748" t="s">
         <v>3</v>
@@ -28867,10 +28875,10 @@
         <v>0</v>
       </c>
       <c r="E748">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F748">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="G748">
         <v>0</v>
@@ -28879,21 +28887,21 @@
         <v>0</v>
       </c>
       <c r="I748">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J748">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K748">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L748">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="749" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A749" s="1">
-        <v>46055</v>
+        <v>46024</v>
       </c>
       <c r="B749" t="s">
         <v>2</v>
@@ -28905,10 +28913,10 @@
         <v>0</v>
       </c>
       <c r="E749">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F749">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="G749">
         <v>0</v>
@@ -28931,22 +28939,22 @@
     </row>
     <row r="750" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A750" s="1">
-        <v>46055</v>
+        <v>46024</v>
       </c>
       <c r="B750" t="s">
         <v>3</v>
       </c>
       <c r="C750">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D750">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E750">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="F750">
-        <v>475</v>
+        <v>900</v>
       </c>
       <c r="G750">
         <v>0</v>
@@ -28955,21 +28963,21 @@
         <v>0</v>
       </c>
       <c r="I750">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J750">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="K750">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L750">
-        <v>25</v>
+        <v>100</v>
       </c>
     </row>
     <row r="751" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A751" s="1">
-        <v>46056</v>
+        <v>46025</v>
       </c>
       <c r="B751" t="s">
         <v>2</v>
@@ -28981,10 +28989,10 @@
         <v>0</v>
       </c>
       <c r="E751">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F751">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="G751">
         <v>0</v>
@@ -28993,21 +29001,21 @@
         <v>0</v>
       </c>
       <c r="I751">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J751">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K751">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L751">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="752" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A752" s="1">
-        <v>46056</v>
+        <v>46025</v>
       </c>
       <c r="B752" t="s">
         <v>3</v>
@@ -29019,10 +29027,10 @@
         <v>0</v>
       </c>
       <c r="E752">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F752">
-        <v>450</v>
+        <v>425</v>
       </c>
       <c r="G752">
         <v>0</v>
@@ -29031,10 +29039,10 @@
         <v>0</v>
       </c>
       <c r="I752">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J752">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="K752">
         <v>2</v>
@@ -29045,22 +29053,22 @@
     </row>
     <row r="753" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A753" s="1">
-        <v>46057</v>
+        <v>46026</v>
       </c>
       <c r="B753" t="s">
         <v>2</v>
       </c>
       <c r="C753">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D753">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E753">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F753">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="G753">
         <v>0</v>
@@ -29075,15 +29083,15 @@
         <v>0</v>
       </c>
       <c r="K753">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L753">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="754" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A754" s="1">
-        <v>46057</v>
+        <v>46026</v>
       </c>
       <c r="B754" t="s">
         <v>3</v>
@@ -29095,10 +29103,10 @@
         <v>25</v>
       </c>
       <c r="E754">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F754">
-        <v>425</v>
+        <v>450</v>
       </c>
       <c r="G754">
         <v>0</v>
@@ -29107,21 +29115,21 @@
         <v>0</v>
       </c>
       <c r="I754">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J754">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K754">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L754">
-        <v>75</v>
+        <v>50</v>
       </c>
     </row>
     <row r="755" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A755" s="1">
-        <v>46058</v>
+        <v>46027</v>
       </c>
       <c r="B755" t="s">
         <v>2</v>
@@ -29133,10 +29141,10 @@
         <v>0</v>
       </c>
       <c r="E755">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F755">
-        <v>175</v>
+        <v>200</v>
       </c>
       <c r="G755">
         <v>0</v>
@@ -29159,7 +29167,7 @@
     </row>
     <row r="756" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A756" s="1">
-        <v>46058</v>
+        <v>46027</v>
       </c>
       <c r="B756" t="s">
         <v>3</v>
@@ -29171,10 +29179,10 @@
         <v>0</v>
       </c>
       <c r="E756">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F756">
-        <v>475</v>
+        <v>400</v>
       </c>
       <c r="G756">
         <v>0</v>
@@ -29183,21 +29191,21 @@
         <v>0</v>
       </c>
       <c r="I756">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J756">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="K756">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L756">
-        <v>25</v>
+        <v>60</v>
       </c>
     </row>
     <row r="757" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A757" s="1">
-        <v>46059</v>
+        <v>46028</v>
       </c>
       <c r="B757" t="s">
         <v>2</v>
@@ -29205,21 +29213,15 @@
       <c r="C757">
         <v>0</v>
       </c>
-      <c r="D757">
-        <v>0</v>
-      </c>
       <c r="E757">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F757">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="G757">
         <v>0</v>
       </c>
-      <c r="H757">
-        <v>0</v>
-      </c>
       <c r="I757">
         <v>0</v>
       </c>
@@ -29227,24 +29229,24 @@
         <v>0</v>
       </c>
       <c r="K757">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L757">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="758" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A758" s="1">
-        <v>46059</v>
+        <v>46028</v>
       </c>
       <c r="B758" t="s">
         <v>3</v>
       </c>
       <c r="C758">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D758">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E758">
         <v>18</v>
@@ -29253,10 +29255,10 @@
         <v>450</v>
       </c>
       <c r="G758">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H758">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I758">
         <v>1</v>
@@ -29265,15 +29267,15 @@
         <v>25</v>
       </c>
       <c r="K758">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L758">
-        <v>75</v>
+        <v>40</v>
       </c>
     </row>
     <row r="759" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A759" s="1">
-        <v>46060</v>
+        <v>46029</v>
       </c>
       <c r="B759" t="s">
         <v>2</v>
@@ -29297,36 +29299,36 @@
         <v>0</v>
       </c>
       <c r="I759">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J759">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K759">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L759">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="760" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A760" s="1">
-        <v>46060</v>
+        <v>46029</v>
       </c>
       <c r="B760" t="s">
         <v>3</v>
       </c>
       <c r="C760">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D760">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E760">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F760">
-        <v>400</v>
+        <v>450</v>
       </c>
       <c r="G760">
         <v>0</v>
@@ -29341,15 +29343,15 @@
         <v>25</v>
       </c>
       <c r="K760">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L760">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="761" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A761" s="1">
-        <v>46061</v>
+        <v>46030</v>
       </c>
       <c r="B761" t="s">
         <v>2</v>
@@ -29387,7 +29389,7 @@
     </row>
     <row r="762" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A762" s="1">
-        <v>46061</v>
+        <v>46030</v>
       </c>
       <c r="B762" t="s">
         <v>3</v>
@@ -29399,10 +29401,10 @@
         <v>0</v>
       </c>
       <c r="E762">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F762">
-        <v>500</v>
+        <v>425</v>
       </c>
       <c r="G762">
         <v>0</v>
@@ -29425,7 +29427,7 @@
     </row>
     <row r="763" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A763" s="1">
-        <v>46062</v>
+        <v>46031</v>
       </c>
       <c r="B763" t="s">
         <v>2</v>
@@ -29437,10 +29439,10 @@
         <v>0</v>
       </c>
       <c r="E763">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F763">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="G763">
         <v>0</v>
@@ -29463,7 +29465,7 @@
     </row>
     <row r="764" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A764" s="1">
-        <v>46062</v>
+        <v>46031</v>
       </c>
       <c r="B764" t="s">
         <v>3</v>
@@ -29481,27 +29483,27 @@
         <v>450</v>
       </c>
       <c r="G764">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H764">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I764">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J764">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="K764">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L764">
-        <v>25</v>
+        <v>75</v>
       </c>
     </row>
     <row r="765" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A765" s="1">
-        <v>46063</v>
+        <v>46032</v>
       </c>
       <c r="B765" t="s">
         <v>2</v>
@@ -29513,10 +29515,10 @@
         <v>0</v>
       </c>
       <c r="E765">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F765">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="G765">
         <v>0</v>
@@ -29539,7 +29541,7 @@
     </row>
     <row r="766" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A766" s="1">
-        <v>46063</v>
+        <v>46032</v>
       </c>
       <c r="B766" t="s">
         <v>3</v>
@@ -29551,10 +29553,10 @@
         <v>0</v>
       </c>
       <c r="E766">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F766">
-        <v>475</v>
+        <v>400</v>
       </c>
       <c r="G766">
         <v>0</v>
@@ -29563,10 +29565,10 @@
         <v>0</v>
       </c>
       <c r="I766">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J766">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K766">
         <v>2</v>
@@ -29577,7 +29579,7 @@
     </row>
     <row r="767" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A767" s="1">
-        <v>46064</v>
+        <v>46033</v>
       </c>
       <c r="B767" t="s">
         <v>2</v>
@@ -29589,10 +29591,10 @@
         <v>0</v>
       </c>
       <c r="E767">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F767">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="G767">
         <v>0</v>
@@ -29615,7 +29617,7 @@
     </row>
     <row r="768" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A768" s="1">
-        <v>46064</v>
+        <v>46033</v>
       </c>
       <c r="B768" t="s">
         <v>3</v>
@@ -29627,33 +29629,33 @@
         <v>0</v>
       </c>
       <c r="E768">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F768">
-        <v>425</v>
+        <v>375</v>
       </c>
       <c r="G768">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H768">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I768">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J768">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K768">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L768">
-        <v>75</v>
+        <v>50</v>
       </c>
     </row>
     <row r="769" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A769" s="1">
-        <v>46065</v>
+        <v>46034</v>
       </c>
       <c r="B769" t="s">
         <v>2</v>
@@ -29665,10 +29667,10 @@
         <v>0</v>
       </c>
       <c r="E769">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F769">
-        <v>175</v>
+        <v>125</v>
       </c>
       <c r="G769">
         <v>0</v>
@@ -29683,15 +29685,15 @@
         <v>0</v>
       </c>
       <c r="K769">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L769">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="770" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A770" s="1">
-        <v>46065</v>
+        <v>46034</v>
       </c>
       <c r="B770" t="s">
         <v>3</v>
@@ -29703,10 +29705,10 @@
         <v>0</v>
       </c>
       <c r="E770">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F770">
-        <v>450</v>
+        <v>400</v>
       </c>
       <c r="G770">
         <v>0</v>
@@ -29715,10 +29717,10 @@
         <v>0</v>
       </c>
       <c r="I770">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J770">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="K770">
         <v>2</v>
@@ -29729,7 +29731,7 @@
     </row>
     <row r="771" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A771" s="1">
-        <v>46066</v>
+        <v>46035</v>
       </c>
       <c r="B771" t="s">
         <v>2</v>
@@ -29741,10 +29743,10 @@
         <v>0</v>
       </c>
       <c r="E771">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F771">
-        <v>175</v>
+        <v>125</v>
       </c>
       <c r="G771">
         <v>0</v>
@@ -29759,30 +29761,30 @@
         <v>0</v>
       </c>
       <c r="K771">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L771">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="772" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A772" s="1">
-        <v>46066</v>
+        <v>46035</v>
       </c>
       <c r="B772" t="s">
         <v>3</v>
       </c>
       <c r="C772">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D772">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E772">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F772">
-        <v>475</v>
+        <v>375</v>
       </c>
       <c r="G772">
         <v>0</v>
@@ -29805,7 +29807,7 @@
     </row>
     <row r="773" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A773" s="1">
-        <v>46067</v>
+        <v>46036</v>
       </c>
       <c r="B773" t="s">
         <v>2</v>
@@ -29817,10 +29819,10 @@
         <v>0</v>
       </c>
       <c r="E773">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F773">
-        <v>175</v>
+        <v>125</v>
       </c>
       <c r="G773">
         <v>0</v>
@@ -29843,7 +29845,7 @@
     </row>
     <row r="774" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A774" s="1">
-        <v>46067</v>
+        <v>46036</v>
       </c>
       <c r="B774" t="s">
         <v>3</v>
@@ -29867,10 +29869,10 @@
         <v>0</v>
       </c>
       <c r="I774">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J774">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K774">
         <v>2</v>
@@ -29881,7 +29883,7 @@
     </row>
     <row r="775" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A775" s="1">
-        <v>46068</v>
+        <v>46037</v>
       </c>
       <c r="B775" t="s">
         <v>2</v>
@@ -29911,30 +29913,30 @@
         <v>0</v>
       </c>
       <c r="K775">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L775">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="776" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A776" s="1">
-        <v>46068</v>
+        <v>46037</v>
       </c>
       <c r="B776" t="s">
         <v>3</v>
       </c>
       <c r="C776">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D776">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E776">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F776">
-        <v>450</v>
+        <v>425</v>
       </c>
       <c r="G776">
         <v>0</v>
@@ -29943,10 +29945,10 @@
         <v>0</v>
       </c>
       <c r="I776">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J776">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K776">
         <v>2</v>
@@ -29957,7 +29959,7 @@
     </row>
     <row r="777" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A777" s="1">
-        <v>46069</v>
+        <v>46038</v>
       </c>
       <c r="B777" t="s">
         <v>2</v>
@@ -29969,10 +29971,10 @@
         <v>0</v>
       </c>
       <c r="E777">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F777">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="G777">
         <v>0</v>
@@ -29987,30 +29989,30 @@
         <v>0</v>
       </c>
       <c r="K777">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L777">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="778" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A778" s="1">
-        <v>46069</v>
+        <v>46038</v>
       </c>
       <c r="B778" t="s">
         <v>3</v>
       </c>
       <c r="C778">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D778">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E778">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F778">
-        <v>375</v>
+        <v>425</v>
       </c>
       <c r="G778">
         <v>0</v>
@@ -30019,21 +30021,21 @@
         <v>0</v>
       </c>
       <c r="I778">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J778">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K778">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L778">
-        <v>50</v>
+        <v>20</v>
       </c>
     </row>
     <row r="779" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A779" s="1">
-        <v>46070</v>
+        <v>46039</v>
       </c>
       <c r="B779" t="s">
         <v>2</v>
@@ -30045,10 +30047,10 @@
         <v>0</v>
       </c>
       <c r="E779">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F779">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="G779">
         <v>0</v>
@@ -30063,30 +30065,30 @@
         <v>0</v>
       </c>
       <c r="K779">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L779">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="780" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A780" s="1">
-        <v>46070</v>
+        <v>46039</v>
       </c>
       <c r="B780" t="s">
         <v>3</v>
       </c>
       <c r="C780">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D780">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E780">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F780">
-        <v>475</v>
+        <v>425</v>
       </c>
       <c r="G780">
         <v>0</v>
@@ -30095,10 +30097,10 @@
         <v>0</v>
       </c>
       <c r="I780">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J780">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K780">
         <v>2</v>
@@ -30109,7 +30111,7 @@
     </row>
     <row r="781" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A781" s="1">
-        <v>46071</v>
+        <v>46040</v>
       </c>
       <c r="B781" t="s">
         <v>2</v>
@@ -30121,10 +30123,10 @@
         <v>0</v>
       </c>
       <c r="E781">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F781">
-        <v>175</v>
+        <v>100</v>
       </c>
       <c r="G781">
         <v>0</v>
@@ -30139,15 +30141,15 @@
         <v>0</v>
       </c>
       <c r="K781">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L781">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="782" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A782" s="1">
-        <v>46071</v>
+        <v>46040</v>
       </c>
       <c r="B782" t="s">
         <v>3</v>
@@ -30159,10 +30161,10 @@
         <v>0</v>
       </c>
       <c r="E782">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F782">
-        <v>400</v>
+        <v>425</v>
       </c>
       <c r="G782">
         <v>0</v>
@@ -30171,21 +30173,21 @@
         <v>0</v>
       </c>
       <c r="I782">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J782">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K782">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L782">
-        <v>50</v>
+        <v>75</v>
       </c>
     </row>
     <row r="783" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A783" s="1">
-        <v>46072</v>
+        <v>46041</v>
       </c>
       <c r="B783" t="s">
         <v>2</v>
@@ -30197,10 +30199,10 @@
         <v>0</v>
       </c>
       <c r="E783">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F783">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="G783">
         <v>0</v>
@@ -30223,22 +30225,22 @@
     </row>
     <row r="784" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A784" s="1">
-        <v>46072</v>
+        <v>46041</v>
       </c>
       <c r="B784" t="s">
         <v>3</v>
       </c>
       <c r="C784">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D784">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E784">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F784">
-        <v>425</v>
+        <v>550</v>
       </c>
       <c r="G784">
         <v>0</v>
@@ -30253,15 +30255,15 @@
         <v>25</v>
       </c>
       <c r="K784">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L784">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="785" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A785" s="1">
-        <v>46073</v>
+        <v>46042</v>
       </c>
       <c r="B785" t="s">
         <v>2</v>
@@ -30273,10 +30275,10 @@
         <v>0</v>
       </c>
       <c r="E785">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F785">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="G785">
         <v>0</v>
@@ -30299,7 +30301,7 @@
     </row>
     <row r="786" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A786" s="1">
-        <v>46073</v>
+        <v>46042</v>
       </c>
       <c r="B786" t="s">
         <v>3</v>
@@ -30311,10 +30313,10 @@
         <v>0</v>
       </c>
       <c r="E786">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F786">
-        <v>375</v>
+        <v>450</v>
       </c>
       <c r="G786">
         <v>0</v>
@@ -30337,7 +30339,7 @@
     </row>
     <row r="787" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A787" s="1">
-        <v>46074</v>
+        <v>46043</v>
       </c>
       <c r="B787" t="s">
         <v>2</v>
@@ -30349,10 +30351,10 @@
         <v>0</v>
       </c>
       <c r="E787">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F787">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="G787">
         <v>0</v>
@@ -30367,15 +30369,15 @@
         <v>0</v>
       </c>
       <c r="K787">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L787">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="788" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A788" s="1">
-        <v>46074</v>
+        <v>46043</v>
       </c>
       <c r="B788" t="s">
         <v>3</v>
@@ -30387,10 +30389,10 @@
         <v>0</v>
       </c>
       <c r="E788">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F788">
-        <v>425</v>
+        <v>250</v>
       </c>
       <c r="G788">
         <v>0</v>
@@ -30399,10 +30401,10 @@
         <v>0</v>
       </c>
       <c r="I788">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J788">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="K788">
         <v>1</v>
@@ -30413,7 +30415,7 @@
     </row>
     <row r="789" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A789" s="1">
-        <v>46075</v>
+        <v>46044</v>
       </c>
       <c r="B789" t="s">
         <v>2</v>
@@ -30451,7 +30453,7 @@
     </row>
     <row r="790" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A790" s="1">
-        <v>46075</v>
+        <v>46044</v>
       </c>
       <c r="B790" t="s">
         <v>3</v>
@@ -30463,10 +30465,10 @@
         <v>0</v>
       </c>
       <c r="E790">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F790">
-        <v>400</v>
+        <v>425</v>
       </c>
       <c r="G790">
         <v>0</v>
@@ -30489,22 +30491,22 @@
     </row>
     <row r="791" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A791" s="1">
-        <v>46076</v>
+        <v>46045</v>
       </c>
       <c r="B791" t="s">
         <v>2</v>
       </c>
       <c r="C791">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D791">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E791">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F791">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="G791">
         <v>0</v>
@@ -30527,7 +30529,7 @@
     </row>
     <row r="792" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A792" s="1">
-        <v>46076</v>
+        <v>46045</v>
       </c>
       <c r="B792" t="s">
         <v>3</v>
@@ -30539,10 +30541,10 @@
         <v>0</v>
       </c>
       <c r="E792">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F792">
-        <v>500</v>
+        <v>475</v>
       </c>
       <c r="G792">
         <v>0</v>
@@ -30551,21 +30553,21 @@
         <v>0</v>
       </c>
       <c r="I792">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J792">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K792">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L792">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="793" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A793" s="1">
-        <v>46077</v>
+        <v>46046</v>
       </c>
       <c r="B793" t="s">
         <v>2</v>
@@ -30577,10 +30579,10 @@
         <v>0</v>
       </c>
       <c r="E793">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F793">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="G793">
         <v>0</v>
@@ -30595,30 +30597,30 @@
         <v>0</v>
       </c>
       <c r="K793">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L793">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="794" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A794" s="1">
-        <v>46077</v>
+        <v>46046</v>
       </c>
       <c r="B794" t="s">
         <v>3</v>
       </c>
       <c r="C794">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D794">
         <v>0</v>
       </c>
       <c r="E794">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F794">
-        <v>450</v>
+        <v>425</v>
       </c>
       <c r="G794">
         <v>0</v>
@@ -30627,21 +30629,21 @@
         <v>0</v>
       </c>
       <c r="I794">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J794">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="K794">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L794">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="795" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A795" s="1">
-        <v>46078</v>
+        <v>46047</v>
       </c>
       <c r="B795" t="s">
         <v>2</v>
@@ -30653,10 +30655,10 @@
         <v>0</v>
       </c>
       <c r="E795">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F795">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="G795">
         <v>0</v>
@@ -30671,15 +30673,15 @@
         <v>0</v>
       </c>
       <c r="K795">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L795">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="796" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A796" s="1">
-        <v>46078</v>
+        <v>46047</v>
       </c>
       <c r="B796" t="s">
         <v>3</v>
@@ -30709,15 +30711,15 @@
         <v>25</v>
       </c>
       <c r="K796">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L796">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="797" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A797" s="1">
-        <v>46079</v>
+        <v>46048</v>
       </c>
       <c r="B797" t="s">
         <v>2</v>
@@ -30729,10 +30731,10 @@
         <v>0</v>
       </c>
       <c r="E797">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F797">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="G797">
         <v>0</v>
@@ -30747,53 +30749,53 @@
         <v>0</v>
       </c>
       <c r="K797">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L797">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="798" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A798" s="1">
-        <v>46079</v>
+        <v>46048</v>
       </c>
       <c r="B798" t="s">
         <v>3</v>
       </c>
       <c r="C798">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D798">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E798">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F798">
-        <v>425</v>
+        <v>400</v>
       </c>
       <c r="G798">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H798">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I798">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J798">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K798">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L798">
-        <v>100</v>
+        <v>75</v>
       </c>
     </row>
     <row r="799" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A799" s="1">
-        <v>46080</v>
+        <v>46049</v>
       </c>
       <c r="B799" t="s">
         <v>2</v>
@@ -30805,10 +30807,10 @@
         <v>0</v>
       </c>
       <c r="E799">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F799">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="G799">
         <v>0</v>
@@ -30823,15 +30825,15 @@
         <v>0</v>
       </c>
       <c r="K799">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L799">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="800" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A800" s="1">
-        <v>46080</v>
+        <v>46049</v>
       </c>
       <c r="B800" t="s">
         <v>3</v>
@@ -30843,10 +30845,10 @@
         <v>0</v>
       </c>
       <c r="E800">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F800">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="G800">
         <v>0</v>
@@ -30855,10 +30857,10 @@
         <v>0</v>
       </c>
       <c r="I800">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J800">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="K800">
         <v>2</v>
@@ -30869,7 +30871,7 @@
     </row>
     <row r="801" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A801" s="1">
-        <v>46081</v>
+        <v>46050</v>
       </c>
       <c r="B801" t="s">
         <v>2</v>
@@ -30881,7 +30883,7 @@
         <v>0</v>
       </c>
       <c r="E801">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F801">
         <v>150</v>
@@ -30899,30 +30901,30 @@
         <v>0</v>
       </c>
       <c r="K801">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L801">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="802" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A802" s="1">
-        <v>46081</v>
+        <v>46050</v>
       </c>
       <c r="B802" t="s">
         <v>3</v>
       </c>
       <c r="C802">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D802">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E802">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F802">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="G802">
         <v>0</v>
@@ -30937,15 +30939,15 @@
         <v>25</v>
       </c>
       <c r="K802">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L802">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="803" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A803" s="1">
-        <v>46023</v>
+        <v>46051</v>
       </c>
       <c r="B803" t="s">
         <v>2</v>
@@ -30957,10 +30959,10 @@
         <v>0</v>
       </c>
       <c r="E803">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F803">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G803">
         <v>0</v>
@@ -30969,10 +30971,10 @@
         <v>0</v>
       </c>
       <c r="I803">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J803">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K803">
         <v>0</v>
@@ -30983,7 +30985,7 @@
     </row>
     <row r="804" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A804" s="1">
-        <v>46023</v>
+        <v>46051</v>
       </c>
       <c r="B804" t="s">
         <v>3</v>
@@ -30995,10 +30997,10 @@
         <v>0</v>
       </c>
       <c r="E804">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F804">
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="G804">
         <v>0</v>
@@ -31007,21 +31009,21 @@
         <v>0</v>
       </c>
       <c r="I804">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J804">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="K804">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L804">
-        <v>0</v>
+        <v>75</v>
       </c>
     </row>
     <row r="805" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A805" s="1">
-        <v>46024</v>
+        <v>46052</v>
       </c>
       <c r="B805" t="s">
         <v>2</v>
@@ -31033,10 +31035,10 @@
         <v>0</v>
       </c>
       <c r="E805">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F805">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="G805">
         <v>0</v>
@@ -31059,22 +31061,22 @@
     </row>
     <row r="806" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A806" s="1">
-        <v>46024</v>
+        <v>46052</v>
       </c>
       <c r="B806" t="s">
         <v>3</v>
       </c>
       <c r="C806">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D806">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E806">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="F806">
-        <v>900</v>
+        <v>425</v>
       </c>
       <c r="G806">
         <v>0</v>
@@ -31083,21 +31085,21 @@
         <v>0</v>
       </c>
       <c r="I806">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J806">
+        <v>0</v>
+      </c>
+      <c r="K806">
+        <v>2</v>
+      </c>
+      <c r="L806">
         <v>50</v>
-      </c>
-      <c r="K806">
-        <v>4</v>
-      </c>
-      <c r="L806">
-        <v>100</v>
       </c>
     </row>
     <row r="807" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A807" s="1">
-        <v>46025</v>
+        <v>46053</v>
       </c>
       <c r="B807" t="s">
         <v>2</v>
@@ -31109,10 +31111,10 @@
         <v>0</v>
       </c>
       <c r="E807">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F807">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="G807">
         <v>0</v>
@@ -31121,21 +31123,21 @@
         <v>0</v>
       </c>
       <c r="I807">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J807">
+        <v>0</v>
+      </c>
+      <c r="K807">
+        <v>1</v>
+      </c>
+      <c r="L807">
         <v>25</v>
-      </c>
-      <c r="K807">
-        <v>2</v>
-      </c>
-      <c r="L807">
-        <v>50</v>
       </c>
     </row>
     <row r="808" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A808" s="1">
-        <v>46025</v>
+        <v>46053</v>
       </c>
       <c r="B808" t="s">
         <v>3</v>
@@ -31147,10 +31149,10 @@
         <v>0</v>
       </c>
       <c r="E808">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F808">
-        <v>425</v>
+        <v>475</v>
       </c>
       <c r="G808">
         <v>0</v>
@@ -31165,15 +31167,15 @@
         <v>25</v>
       </c>
       <c r="K808">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L808">
-        <v>50</v>
+        <v>75</v>
       </c>
     </row>
     <row r="809" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A809" s="1">
-        <v>46026</v>
+        <v>46054</v>
       </c>
       <c r="B809" t="s">
         <v>2</v>
@@ -31185,10 +31187,10 @@
         <v>0</v>
       </c>
       <c r="E809">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F809">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="G809">
         <v>0</v>
@@ -31203,42 +31205,42 @@
         <v>0</v>
       </c>
       <c r="K809">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L809">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="810" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A810" s="1">
-        <v>46026</v>
+        <v>46054</v>
       </c>
       <c r="B810" t="s">
         <v>3</v>
       </c>
       <c r="C810">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D810">
+        <v>0</v>
+      </c>
+      <c r="E810">
+        <v>16</v>
+      </c>
+      <c r="F810">
+        <v>400</v>
+      </c>
+      <c r="G810">
+        <v>0</v>
+      </c>
+      <c r="H810">
+        <v>0</v>
+      </c>
+      <c r="I810">
+        <v>1</v>
+      </c>
+      <c r="J810">
         <v>25</v>
-      </c>
-      <c r="E810">
-        <v>18</v>
-      </c>
-      <c r="F810">
-        <v>450</v>
-      </c>
-      <c r="G810">
-        <v>0</v>
-      </c>
-      <c r="H810">
-        <v>0</v>
-      </c>
-      <c r="I810">
-        <v>0</v>
-      </c>
-      <c r="J810">
-        <v>0</v>
       </c>
       <c r="K810">
         <v>2</v>
@@ -31249,7 +31251,7 @@
     </row>
     <row r="811" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A811" s="1">
-        <v>46027</v>
+        <v>46055</v>
       </c>
       <c r="B811" t="s">
         <v>2</v>
@@ -31261,10 +31263,10 @@
         <v>0</v>
       </c>
       <c r="E811">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F811">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="G811">
         <v>0</v>
@@ -31287,7 +31289,7 @@
     </row>
     <row r="812" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A812" s="1">
-        <v>46027</v>
+        <v>46055</v>
       </c>
       <c r="B812" t="s">
         <v>3</v>
@@ -31299,10 +31301,10 @@
         <v>0</v>
       </c>
       <c r="E812">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F812">
-        <v>400</v>
+        <v>475</v>
       </c>
       <c r="G812">
         <v>0</v>
@@ -31311,21 +31313,21 @@
         <v>0</v>
       </c>
       <c r="I812">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J812">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="K812">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L812">
-        <v>60</v>
+        <v>25</v>
       </c>
     </row>
     <row r="813" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A813" s="1">
-        <v>46028</v>
+        <v>46056</v>
       </c>
       <c r="B813" t="s">
         <v>2</v>
@@ -31333,13 +31335,19 @@
       <c r="C813">
         <v>0</v>
       </c>
+      <c r="D813">
+        <v>0</v>
+      </c>
       <c r="E813">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F813">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="G813">
+        <v>0</v>
+      </c>
+      <c r="H813">
         <v>0</v>
       </c>
       <c r="I813">
@@ -31357,16 +31365,16 @@
     </row>
     <row r="814" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A814" s="1">
-        <v>46028</v>
+        <v>46056</v>
       </c>
       <c r="B814" t="s">
         <v>3</v>
       </c>
       <c r="C814">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D814">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E814">
         <v>18</v>
@@ -31381,36 +31389,36 @@
         <v>0</v>
       </c>
       <c r="I814">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J814">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="K814">
         <v>2</v>
       </c>
       <c r="L814">
-        <v>40</v>
+        <v>50</v>
       </c>
     </row>
     <row r="815" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A815" s="1">
-        <v>46029</v>
+        <v>46057</v>
       </c>
       <c r="B815" t="s">
         <v>2</v>
       </c>
       <c r="C815">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D815">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E815">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F815">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="G815">
         <v>0</v>
@@ -31419,10 +31427,10 @@
         <v>0</v>
       </c>
       <c r="I815">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J815">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K815">
         <v>1</v>
@@ -31433,7 +31441,7 @@
     </row>
     <row r="816" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A816" s="1">
-        <v>46029</v>
+        <v>46057</v>
       </c>
       <c r="B816" t="s">
         <v>3</v>
@@ -31445,10 +31453,10 @@
         <v>25</v>
       </c>
       <c r="E816">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F816">
-        <v>450</v>
+        <v>425</v>
       </c>
       <c r="G816">
         <v>0</v>
@@ -31463,15 +31471,15 @@
         <v>25</v>
       </c>
       <c r="K816">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L816">
-        <v>25</v>
+        <v>75</v>
       </c>
     </row>
     <row r="817" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A817" s="1">
-        <v>46030</v>
+        <v>46058</v>
       </c>
       <c r="B817" t="s">
         <v>2</v>
@@ -31501,15 +31509,15 @@
         <v>0</v>
       </c>
       <c r="K817">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L817">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="818" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A818" s="1">
-        <v>46030</v>
+        <v>46058</v>
       </c>
       <c r="B818" t="s">
         <v>3</v>
@@ -31521,10 +31529,10 @@
         <v>0</v>
       </c>
       <c r="E818">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F818">
-        <v>425</v>
+        <v>475</v>
       </c>
       <c r="G818">
         <v>0</v>
@@ -31533,21 +31541,21 @@
         <v>0</v>
       </c>
       <c r="I818">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J818">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K818">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L818">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="819" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A819" s="1">
-        <v>46031</v>
+        <v>46059</v>
       </c>
       <c r="B819" t="s">
         <v>2</v>
@@ -31559,10 +31567,10 @@
         <v>0</v>
       </c>
       <c r="E819">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F819">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="G819">
         <v>0</v>
@@ -31577,15 +31585,15 @@
         <v>0</v>
       </c>
       <c r="K819">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L819">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="820" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A820" s="1">
-        <v>46031</v>
+        <v>46059</v>
       </c>
       <c r="B820" t="s">
         <v>3</v>
@@ -31603,16 +31611,16 @@
         <v>450</v>
       </c>
       <c r="G820">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H820">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I820">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J820">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="K820">
         <v>3</v>
@@ -31623,7 +31631,7 @@
     </row>
     <row r="821" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A821" s="1">
-        <v>46032</v>
+        <v>46060</v>
       </c>
       <c r="B821" t="s">
         <v>2</v>
@@ -31635,10 +31643,10 @@
         <v>0</v>
       </c>
       <c r="E821">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F821">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="G821">
         <v>0</v>
@@ -31653,15 +31661,15 @@
         <v>0</v>
       </c>
       <c r="K821">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L821">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="822" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A822" s="1">
-        <v>46032</v>
+        <v>46060</v>
       </c>
       <c r="B822" t="s">
         <v>3</v>
@@ -31685,10 +31693,10 @@
         <v>0</v>
       </c>
       <c r="I822">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J822">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K822">
         <v>2</v>
@@ -31699,7 +31707,7 @@
     </row>
     <row r="823" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A823" s="1">
-        <v>46033</v>
+        <v>46061</v>
       </c>
       <c r="B823" t="s">
         <v>2</v>
@@ -31711,10 +31719,10 @@
         <v>0</v>
       </c>
       <c r="E823">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F823">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="G823">
         <v>0</v>
@@ -31729,15 +31737,15 @@
         <v>0</v>
       </c>
       <c r="K823">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L823">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="824" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A824" s="1">
-        <v>46033</v>
+        <v>46061</v>
       </c>
       <c r="B824" t="s">
         <v>3</v>
@@ -31749,10 +31757,10 @@
         <v>0</v>
       </c>
       <c r="E824">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F824">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="G824">
         <v>0</v>
@@ -31761,10 +31769,10 @@
         <v>0</v>
       </c>
       <c r="I824">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J824">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K824">
         <v>2</v>
@@ -31775,7 +31783,7 @@
     </row>
     <row r="825" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A825" s="1">
-        <v>46034</v>
+        <v>46062</v>
       </c>
       <c r="B825" t="s">
         <v>2</v>
@@ -31787,10 +31795,10 @@
         <v>0</v>
       </c>
       <c r="E825">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F825">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="G825">
         <v>0</v>
@@ -31813,7 +31821,7 @@
     </row>
     <row r="826" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A826" s="1">
-        <v>46034</v>
+        <v>46062</v>
       </c>
       <c r="B826" t="s">
         <v>3</v>
@@ -31825,33 +31833,33 @@
         <v>0</v>
       </c>
       <c r="E826">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F826">
-        <v>400</v>
+        <v>450</v>
       </c>
       <c r="G826">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H826">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I826">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J826">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K826">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L826">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="827" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A827" s="1">
-        <v>46035</v>
+        <v>46063</v>
       </c>
       <c r="B827" t="s">
         <v>2</v>
@@ -31863,10 +31871,10 @@
         <v>0</v>
       </c>
       <c r="E827">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F827">
-        <v>125</v>
+        <v>200</v>
       </c>
       <c r="G827">
         <v>0</v>
@@ -31889,34 +31897,34 @@
     </row>
     <row r="828" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A828" s="1">
-        <v>46035</v>
+        <v>46063</v>
       </c>
       <c r="B828" t="s">
         <v>3</v>
       </c>
       <c r="C828">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D828">
+        <v>0</v>
+      </c>
+      <c r="E828">
+        <v>19</v>
+      </c>
+      <c r="F828">
+        <v>475</v>
+      </c>
+      <c r="G828">
+        <v>0</v>
+      </c>
+      <c r="H828">
+        <v>0</v>
+      </c>
+      <c r="I828">
+        <v>2</v>
+      </c>
+      <c r="J828">
         <v>50</v>
-      </c>
-      <c r="E828">
-        <v>15</v>
-      </c>
-      <c r="F828">
-        <v>375</v>
-      </c>
-      <c r="G828">
-        <v>0</v>
-      </c>
-      <c r="H828">
-        <v>0</v>
-      </c>
-      <c r="I828">
-        <v>1</v>
-      </c>
-      <c r="J828">
-        <v>25</v>
       </c>
       <c r="K828">
         <v>2</v>
@@ -31927,7 +31935,7 @@
     </row>
     <row r="829" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A829" s="1">
-        <v>46036</v>
+        <v>46064</v>
       </c>
       <c r="B829" t="s">
         <v>2</v>
@@ -31939,10 +31947,10 @@
         <v>0</v>
       </c>
       <c r="E829">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F829">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="G829">
         <v>0</v>
@@ -31957,15 +31965,15 @@
         <v>0</v>
       </c>
       <c r="K829">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L829">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="830" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A830" s="1">
-        <v>46036</v>
+        <v>46064</v>
       </c>
       <c r="B830" t="s">
         <v>3</v>
@@ -31977,33 +31985,33 @@
         <v>0</v>
       </c>
       <c r="E830">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F830">
-        <v>475</v>
+        <v>425</v>
       </c>
       <c r="G830">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H830">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I830">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J830">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K830">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L830">
-        <v>50</v>
+        <v>75</v>
       </c>
     </row>
     <row r="831" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A831" s="1">
-        <v>46037</v>
+        <v>46065</v>
       </c>
       <c r="B831" t="s">
         <v>2</v>
@@ -32015,10 +32023,10 @@
         <v>0</v>
       </c>
       <c r="E831">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F831">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="G831">
         <v>0</v>
@@ -32041,22 +32049,22 @@
     </row>
     <row r="832" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A832" s="1">
-        <v>46037</v>
+        <v>46065</v>
       </c>
       <c r="B832" t="s">
         <v>3</v>
       </c>
       <c r="C832">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D832">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E832">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F832">
-        <v>425</v>
+        <v>450</v>
       </c>
       <c r="G832">
         <v>0</v>
@@ -32065,10 +32073,10 @@
         <v>0</v>
       </c>
       <c r="I832">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J832">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="K832">
         <v>2</v>
@@ -32079,7 +32087,7 @@
     </row>
     <row r="833" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A833" s="1">
-        <v>46038</v>
+        <v>46066</v>
       </c>
       <c r="B833" t="s">
         <v>2</v>
@@ -32091,10 +32099,10 @@
         <v>0</v>
       </c>
       <c r="E833">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F833">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="G833">
         <v>0</v>
@@ -32117,45 +32125,45 @@
     </row>
     <row r="834" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A834" s="1">
-        <v>46038</v>
+        <v>46066</v>
       </c>
       <c r="B834" t="s">
         <v>3</v>
       </c>
       <c r="C834">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D834">
+        <v>25</v>
+      </c>
+      <c r="E834">
+        <v>19</v>
+      </c>
+      <c r="F834">
+        <v>475</v>
+      </c>
+      <c r="G834">
+        <v>0</v>
+      </c>
+      <c r="H834">
+        <v>0</v>
+      </c>
+      <c r="I834">
+        <v>1</v>
+      </c>
+      <c r="J834">
+        <v>25</v>
+      </c>
+      <c r="K834">
+        <v>2</v>
+      </c>
+      <c r="L834">
         <v>50</v>
-      </c>
-      <c r="E834">
-        <v>17</v>
-      </c>
-      <c r="F834">
-        <v>425</v>
-      </c>
-      <c r="G834">
-        <v>0</v>
-      </c>
-      <c r="H834">
-        <v>0</v>
-      </c>
-      <c r="I834">
-        <v>0</v>
-      </c>
-      <c r="J834">
-        <v>0</v>
-      </c>
-      <c r="K834">
-        <v>1</v>
-      </c>
-      <c r="L834">
-        <v>20</v>
       </c>
     </row>
     <row r="835" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A835" s="1">
-        <v>46039</v>
+        <v>46067</v>
       </c>
       <c r="B835" t="s">
         <v>2</v>
@@ -32167,10 +32175,10 @@
         <v>0</v>
       </c>
       <c r="E835">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F835">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="G835">
         <v>0</v>
@@ -32193,22 +32201,22 @@
     </row>
     <row r="836" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A836" s="1">
-        <v>46039</v>
+        <v>46067</v>
       </c>
       <c r="B836" t="s">
         <v>3</v>
       </c>
       <c r="C836">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D836">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E836">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F836">
-        <v>425</v>
+        <v>475</v>
       </c>
       <c r="G836">
         <v>0</v>
@@ -32217,10 +32225,10 @@
         <v>0</v>
       </c>
       <c r="I836">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J836">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K836">
         <v>2</v>
@@ -32231,7 +32239,7 @@
     </row>
     <row r="837" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A837" s="1">
-        <v>46040</v>
+        <v>46068</v>
       </c>
       <c r="B837" t="s">
         <v>2</v>
@@ -32243,10 +32251,10 @@
         <v>0</v>
       </c>
       <c r="E837">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F837">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="G837">
         <v>0</v>
@@ -32269,7 +32277,7 @@
     </row>
     <row r="838" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A838" s="1">
-        <v>46040</v>
+        <v>46068</v>
       </c>
       <c r="B838" t="s">
         <v>3</v>
@@ -32281,10 +32289,10 @@
         <v>0</v>
       </c>
       <c r="E838">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F838">
-        <v>425</v>
+        <v>450</v>
       </c>
       <c r="G838">
         <v>0</v>
@@ -32299,15 +32307,15 @@
         <v>0</v>
       </c>
       <c r="K838">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L838">
-        <v>75</v>
+        <v>50</v>
       </c>
     </row>
     <row r="839" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A839" s="1">
-        <v>46041</v>
+        <v>46069</v>
       </c>
       <c r="B839" t="s">
         <v>2</v>
@@ -32319,10 +32327,10 @@
         <v>0</v>
       </c>
       <c r="E839">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F839">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="G839">
         <v>0</v>
@@ -32337,30 +32345,30 @@
         <v>0</v>
       </c>
       <c r="K839">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L839">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="840" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A840" s="1">
-        <v>46041</v>
+        <v>46069</v>
       </c>
       <c r="B840" t="s">
         <v>3</v>
       </c>
       <c r="C840">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D840">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E840">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F840">
-        <v>550</v>
+        <v>375</v>
       </c>
       <c r="G840">
         <v>0</v>
@@ -32383,7 +32391,7 @@
     </row>
     <row r="841" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A841" s="1">
-        <v>46042</v>
+        <v>46070</v>
       </c>
       <c r="B841" t="s">
         <v>2</v>
@@ -32395,10 +32403,10 @@
         <v>0</v>
       </c>
       <c r="E841">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F841">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="G841">
         <v>0</v>
@@ -32413,15 +32421,15 @@
         <v>0</v>
       </c>
       <c r="K841">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L841">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="842" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A842" s="1">
-        <v>46042</v>
+        <v>46070</v>
       </c>
       <c r="B842" t="s">
         <v>3</v>
@@ -32433,10 +32441,10 @@
         <v>0</v>
       </c>
       <c r="E842">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F842">
-        <v>450</v>
+        <v>475</v>
       </c>
       <c r="G842">
         <v>0</v>
@@ -32445,10 +32453,10 @@
         <v>0</v>
       </c>
       <c r="I842">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J842">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K842">
         <v>2</v>
@@ -32459,7 +32467,7 @@
     </row>
     <row r="843" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A843" s="1">
-        <v>46043</v>
+        <v>46071</v>
       </c>
       <c r="B843" t="s">
         <v>2</v>
@@ -32471,10 +32479,10 @@
         <v>0</v>
       </c>
       <c r="E843">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F843">
-        <v>100</v>
+        <v>175</v>
       </c>
       <c r="G843">
         <v>0</v>
@@ -32497,7 +32505,7 @@
     </row>
     <row r="844" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A844" s="1">
-        <v>46043</v>
+        <v>46071</v>
       </c>
       <c r="B844" t="s">
         <v>3</v>
@@ -32509,10 +32517,10 @@
         <v>0</v>
       </c>
       <c r="E844">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F844">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="G844">
         <v>0</v>
@@ -32521,21 +32529,21 @@
         <v>0</v>
       </c>
       <c r="I844">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J844">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="K844">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L844">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="845" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A845" s="1">
-        <v>46044</v>
+        <v>46072</v>
       </c>
       <c r="B845" t="s">
         <v>2</v>
@@ -32573,7 +32581,7 @@
     </row>
     <row r="846" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A846" s="1">
-        <v>46044</v>
+        <v>46072</v>
       </c>
       <c r="B846" t="s">
         <v>3</v>
@@ -32603,30 +32611,30 @@
         <v>25</v>
       </c>
       <c r="K846">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L846">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="847" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A847" s="1">
-        <v>46045</v>
+        <v>46073</v>
       </c>
       <c r="B847" t="s">
         <v>2</v>
       </c>
       <c r="C847">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D847">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E847">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F847">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="G847">
         <v>0</v>
@@ -32649,7 +32657,7 @@
     </row>
     <row r="848" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A848" s="1">
-        <v>46045</v>
+        <v>46073</v>
       </c>
       <c r="B848" t="s">
         <v>3</v>
@@ -32661,10 +32669,10 @@
         <v>0</v>
       </c>
       <c r="E848">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F848">
-        <v>475</v>
+        <v>375</v>
       </c>
       <c r="G848">
         <v>0</v>
@@ -32673,21 +32681,21 @@
         <v>0</v>
       </c>
       <c r="I848">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J848">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K848">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L848">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="849" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A849" s="1">
-        <v>46046</v>
+        <v>46074</v>
       </c>
       <c r="B849" t="s">
         <v>2</v>
@@ -32717,21 +32725,21 @@
         <v>0</v>
       </c>
       <c r="K849">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L849">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="850" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A850" s="1">
-        <v>46046</v>
+        <v>46074</v>
       </c>
       <c r="B850" t="s">
         <v>3</v>
       </c>
       <c r="C850">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D850">
         <v>0</v>
@@ -32749,10 +32757,10 @@
         <v>0</v>
       </c>
       <c r="I850">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J850">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="K850">
         <v>1</v>
@@ -32763,7 +32771,7 @@
     </row>
     <row r="851" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A851" s="1">
-        <v>46047</v>
+        <v>46075</v>
       </c>
       <c r="B851" t="s">
         <v>2</v>
@@ -32775,10 +32783,10 @@
         <v>0</v>
       </c>
       <c r="E851">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F851">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="G851">
         <v>0</v>
@@ -32801,7 +32809,7 @@
     </row>
     <row r="852" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A852" s="1">
-        <v>46047</v>
+        <v>46075</v>
       </c>
       <c r="B852" t="s">
         <v>3</v>
@@ -32813,10 +32821,10 @@
         <v>0</v>
       </c>
       <c r="E852">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F852">
-        <v>450</v>
+        <v>400</v>
       </c>
       <c r="G852">
         <v>0</v>
@@ -32831,15 +32839,15 @@
         <v>25</v>
       </c>
       <c r="K852">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L852">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="853" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A853" s="1">
-        <v>46048</v>
+        <v>46076</v>
       </c>
       <c r="B853" t="s">
         <v>2</v>
@@ -32851,10 +32859,10 @@
         <v>0</v>
       </c>
       <c r="E853">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F853">
-        <v>200</v>
+        <v>125</v>
       </c>
       <c r="G853">
         <v>0</v>
@@ -32877,22 +32885,22 @@
     </row>
     <row r="854" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A854" s="1">
-        <v>46048</v>
+        <v>46076</v>
       </c>
       <c r="B854" t="s">
         <v>3</v>
       </c>
       <c r="C854">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D854">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E854">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F854">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="G854">
         <v>0</v>
@@ -32901,21 +32909,21 @@
         <v>0</v>
       </c>
       <c r="I854">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J854">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K854">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L854">
-        <v>75</v>
+        <v>50</v>
       </c>
     </row>
     <row r="855" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A855" s="1">
-        <v>46049</v>
+        <v>46077</v>
       </c>
       <c r="B855" t="s">
         <v>2</v>
@@ -32927,10 +32935,10 @@
         <v>0</v>
       </c>
       <c r="E855">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F855">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="G855">
         <v>0</v>
@@ -32953,7 +32961,7 @@
     </row>
     <row r="856" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A856" s="1">
-        <v>46049</v>
+        <v>46077</v>
       </c>
       <c r="B856" t="s">
         <v>3</v>
@@ -32965,10 +32973,10 @@
         <v>0</v>
       </c>
       <c r="E856">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F856">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="G856">
         <v>0</v>
@@ -32977,10 +32985,10 @@
         <v>0</v>
       </c>
       <c r="I856">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J856">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="K856">
         <v>2</v>
@@ -32991,7 +32999,7 @@
     </row>
     <row r="857" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A857" s="1">
-        <v>46050</v>
+        <v>46078</v>
       </c>
       <c r="B857" t="s">
         <v>2</v>
@@ -33003,10 +33011,10 @@
         <v>0</v>
       </c>
       <c r="E857">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F857">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="G857">
         <v>0</v>
@@ -33029,22 +33037,22 @@
     </row>
     <row r="858" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A858" s="1">
-        <v>46050</v>
+        <v>46078</v>
       </c>
       <c r="B858" t="s">
         <v>3</v>
       </c>
       <c r="C858">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D858">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E858">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F858">
-        <v>525</v>
+        <v>450</v>
       </c>
       <c r="G858">
         <v>0</v>
@@ -33059,15 +33067,15 @@
         <v>25</v>
       </c>
       <c r="K858">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L858">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="859" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A859" s="1">
-        <v>46051</v>
+        <v>46079</v>
       </c>
       <c r="B859" t="s">
         <v>2</v>
@@ -33079,10 +33087,10 @@
         <v>0</v>
       </c>
       <c r="E859">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F859">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="G859">
         <v>0</v>
@@ -33091,10 +33099,10 @@
         <v>0</v>
       </c>
       <c r="I859">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J859">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K859">
         <v>0</v>
@@ -33105,7 +33113,7 @@
     </row>
     <row r="860" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A860" s="1">
-        <v>46051</v>
+        <v>46079</v>
       </c>
       <c r="B860" t="s">
         <v>3</v>
@@ -33117,33 +33125,33 @@
         <v>0</v>
       </c>
       <c r="E860">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F860">
-        <v>450</v>
+        <v>425</v>
       </c>
       <c r="G860">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H860">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I860">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J860">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="K860">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L860">
-        <v>75</v>
+        <v>100</v>
       </c>
     </row>
     <row r="861" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A861" s="1">
-        <v>46052</v>
+        <v>46080</v>
       </c>
       <c r="B861" t="s">
         <v>2</v>
@@ -33173,15 +33181,15 @@
         <v>0</v>
       </c>
       <c r="K861">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L861">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="862" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A862" s="1">
-        <v>46052</v>
+        <v>46080</v>
       </c>
       <c r="B862" t="s">
         <v>3</v>
@@ -33193,10 +33201,10 @@
         <v>0</v>
       </c>
       <c r="E862">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F862">
-        <v>425</v>
+        <v>450</v>
       </c>
       <c r="G862">
         <v>0</v>
@@ -33205,10 +33213,10 @@
         <v>0</v>
       </c>
       <c r="I862">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J862">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K862">
         <v>2</v>
@@ -33219,7 +33227,7 @@
     </row>
     <row r="863" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A863" s="1">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B863" t="s">
         <v>2</v>
@@ -33249,15 +33257,15 @@
         <v>0</v>
       </c>
       <c r="K863">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L863">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="864" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A864" s="1">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B864" t="s">
         <v>3</v>
@@ -33269,10 +33277,10 @@
         <v>0</v>
       </c>
       <c r="E864">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F864">
-        <v>475</v>
+        <v>400</v>
       </c>
       <c r="G864">
         <v>0</v>
@@ -33287,10 +33295,2366 @@
         <v>25</v>
       </c>
       <c r="K864">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L864">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="865" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A865" s="1">
+        <v>46082</v>
+      </c>
+      <c r="B865" t="s">
+        <v>2</v>
+      </c>
+      <c r="C865">
+        <v>0</v>
+      </c>
+      <c r="D865">
+        <v>0</v>
+      </c>
+      <c r="E865">
+        <v>6</v>
+      </c>
+      <c r="F865">
+        <v>150</v>
+      </c>
+      <c r="G865">
+        <v>0</v>
+      </c>
+      <c r="H865">
+        <v>0</v>
+      </c>
+      <c r="I865">
+        <v>0</v>
+      </c>
+      <c r="J865">
+        <v>0</v>
+      </c>
+      <c r="K865">
+        <v>1</v>
+      </c>
+      <c r="L865">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="866" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A866" s="1">
+        <v>46082</v>
+      </c>
+      <c r="B866" t="s">
+        <v>3</v>
+      </c>
+      <c r="C866">
+        <v>0</v>
+      </c>
+      <c r="D866">
+        <v>0</v>
+      </c>
+      <c r="E866">
+        <v>18</v>
+      </c>
+      <c r="F866">
+        <v>450</v>
+      </c>
+      <c r="G866">
+        <v>0</v>
+      </c>
+      <c r="H866">
+        <v>0</v>
+      </c>
+      <c r="I866">
+        <v>0</v>
+      </c>
+      <c r="J866">
+        <v>0</v>
+      </c>
+      <c r="K866">
+        <v>1</v>
+      </c>
+      <c r="L866">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="867" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A867" s="1">
+        <v>46083</v>
+      </c>
+      <c r="B867" t="s">
+        <v>2</v>
+      </c>
+      <c r="C867">
+        <v>0</v>
+      </c>
+      <c r="D867">
+        <v>0</v>
+      </c>
+      <c r="E867">
+        <v>6</v>
+      </c>
+      <c r="F867">
+        <v>150</v>
+      </c>
+      <c r="G867">
+        <v>0</v>
+      </c>
+      <c r="H867">
+        <v>0</v>
+      </c>
+      <c r="I867">
+        <v>0</v>
+      </c>
+      <c r="J867">
+        <v>0</v>
+      </c>
+      <c r="K867">
+        <v>0</v>
+      </c>
+      <c r="L867">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="868" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A868" s="1">
+        <v>46083</v>
+      </c>
+      <c r="B868" t="s">
+        <v>3</v>
+      </c>
+      <c r="C868">
+        <v>0</v>
+      </c>
+      <c r="D868">
+        <v>0</v>
+      </c>
+      <c r="E868">
+        <v>19</v>
+      </c>
+      <c r="F868">
+        <v>475</v>
+      </c>
+      <c r="G868">
+        <v>0</v>
+      </c>
+      <c r="H868">
+        <v>0</v>
+      </c>
+      <c r="I868">
+        <v>2</v>
+      </c>
+      <c r="J868">
+        <v>50</v>
+      </c>
+      <c r="K868">
+        <v>1</v>
+      </c>
+      <c r="L868">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="869" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A869" s="1">
+        <v>46084</v>
+      </c>
+      <c r="B869" t="s">
+        <v>2</v>
+      </c>
+      <c r="C869">
+        <v>0</v>
+      </c>
+      <c r="D869">
+        <v>0</v>
+      </c>
+      <c r="E869">
+        <v>6</v>
+      </c>
+      <c r="F869">
+        <v>150</v>
+      </c>
+      <c r="G869">
+        <v>0</v>
+      </c>
+      <c r="H869">
+        <v>0</v>
+      </c>
+      <c r="I869">
+        <v>0</v>
+      </c>
+      <c r="J869">
+        <v>0</v>
+      </c>
+      <c r="K869">
+        <v>1</v>
+      </c>
+      <c r="L869">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="870" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A870" s="1">
+        <v>46084</v>
+      </c>
+      <c r="B870" t="s">
+        <v>3</v>
+      </c>
+      <c r="C870">
+        <v>0</v>
+      </c>
+      <c r="D870">
+        <v>0</v>
+      </c>
+      <c r="E870">
+        <v>19</v>
+      </c>
+      <c r="F870">
+        <v>475</v>
+      </c>
+      <c r="G870">
+        <v>0</v>
+      </c>
+      <c r="H870">
+        <v>0</v>
+      </c>
+      <c r="I870">
+        <v>1</v>
+      </c>
+      <c r="J870">
+        <v>25</v>
+      </c>
+      <c r="K870">
+        <v>2</v>
+      </c>
+      <c r="L870">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="871" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A871" s="1">
+        <v>46085</v>
+      </c>
+      <c r="B871" t="s">
+        <v>2</v>
+      </c>
+      <c r="C871">
+        <v>0</v>
+      </c>
+      <c r="D871">
+        <v>0</v>
+      </c>
+      <c r="E871">
+        <v>6</v>
+      </c>
+      <c r="F871">
+        <v>150</v>
+      </c>
+      <c r="G871">
+        <v>0</v>
+      </c>
+      <c r="H871">
+        <v>0</v>
+      </c>
+      <c r="I871">
+        <v>0</v>
+      </c>
+      <c r="J871">
+        <v>0</v>
+      </c>
+      <c r="K871">
+        <v>0</v>
+      </c>
+      <c r="L871">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="872" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A872" s="1">
+        <v>46085</v>
+      </c>
+      <c r="B872" t="s">
+        <v>3</v>
+      </c>
+      <c r="C872">
+        <v>0</v>
+      </c>
+      <c r="D872">
+        <v>0</v>
+      </c>
+      <c r="E872">
+        <v>19</v>
+      </c>
+      <c r="F872">
+        <v>475</v>
+      </c>
+      <c r="G872">
+        <v>0</v>
+      </c>
+      <c r="H872">
+        <v>0</v>
+      </c>
+      <c r="I872">
+        <v>2</v>
+      </c>
+      <c r="J872">
+        <v>50</v>
+      </c>
+      <c r="K872">
+        <v>2</v>
+      </c>
+      <c r="L872">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="873" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A873" s="1">
+        <v>46086</v>
+      </c>
+      <c r="B873" t="s">
+        <v>2</v>
+      </c>
+      <c r="C873">
+        <v>0</v>
+      </c>
+      <c r="D873">
+        <v>0</v>
+      </c>
+      <c r="E873">
+        <v>7</v>
+      </c>
+      <c r="F873">
+        <v>175</v>
+      </c>
+      <c r="G873">
+        <v>0</v>
+      </c>
+      <c r="H873">
+        <v>0</v>
+      </c>
+      <c r="I873">
+        <v>0</v>
+      </c>
+      <c r="J873">
+        <v>0</v>
+      </c>
+      <c r="K873">
+        <v>1</v>
+      </c>
+      <c r="L873">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="874" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A874" s="1">
+        <v>46086</v>
+      </c>
+      <c r="B874" t="s">
+        <v>3</v>
+      </c>
+      <c r="C874">
+        <v>0</v>
+      </c>
+      <c r="D874">
+        <v>0</v>
+      </c>
+      <c r="E874">
+        <v>19</v>
+      </c>
+      <c r="F874">
+        <v>475</v>
+      </c>
+      <c r="G874">
+        <v>0</v>
+      </c>
+      <c r="H874">
+        <v>0</v>
+      </c>
+      <c r="I874">
+        <v>2</v>
+      </c>
+      <c r="J874">
+        <v>50</v>
+      </c>
+      <c r="K874">
+        <v>1</v>
+      </c>
+      <c r="L874">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="875" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A875" s="1">
+        <v>46087</v>
+      </c>
+      <c r="B875" t="s">
+        <v>2</v>
+      </c>
+      <c r="C875">
+        <v>0</v>
+      </c>
+      <c r="D875">
+        <v>0</v>
+      </c>
+      <c r="E875">
+        <v>7</v>
+      </c>
+      <c r="F875">
+        <v>175</v>
+      </c>
+      <c r="G875">
+        <v>0</v>
+      </c>
+      <c r="H875">
+        <v>0</v>
+      </c>
+      <c r="I875">
+        <v>1</v>
+      </c>
+      <c r="J875">
+        <v>25</v>
+      </c>
+      <c r="K875">
+        <v>1</v>
+      </c>
+      <c r="L875">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="876" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A876" s="2">
+        <v>46087</v>
+      </c>
+      <c r="B876" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C876" s="3">
+        <v>0</v>
+      </c>
+      <c r="D876" s="3">
+        <v>0</v>
+      </c>
+      <c r="E876" s="3">
+        <v>19</v>
+      </c>
+      <c r="F876" s="3">
+        <v>475</v>
+      </c>
+      <c r="G876" s="3">
+        <v>1</v>
+      </c>
+      <c r="H876" s="3">
+        <v>15</v>
+      </c>
+      <c r="I876" s="3">
+        <v>2</v>
+      </c>
+      <c r="J876" s="3">
+        <v>50</v>
+      </c>
+      <c r="K876" s="3">
+        <v>1</v>
+      </c>
+      <c r="L876" s="3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="877" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A877" s="1">
+        <v>46088</v>
+      </c>
+      <c r="B877" t="s">
+        <v>2</v>
+      </c>
+      <c r="C877">
+        <v>0</v>
+      </c>
+      <c r="D877">
+        <v>0</v>
+      </c>
+      <c r="E877">
+        <v>7</v>
+      </c>
+      <c r="F877">
+        <v>175</v>
+      </c>
+      <c r="G877">
+        <v>0</v>
+      </c>
+      <c r="H877">
+        <v>0</v>
+      </c>
+      <c r="I877">
+        <v>0</v>
+      </c>
+      <c r="J877">
+        <v>0</v>
+      </c>
+      <c r="K877">
+        <v>0</v>
+      </c>
+      <c r="L877">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="878" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A878" s="1">
+        <v>46088</v>
+      </c>
+      <c r="B878" t="s">
+        <v>3</v>
+      </c>
+      <c r="C878">
+        <v>0</v>
+      </c>
+      <c r="D878">
+        <v>0</v>
+      </c>
+      <c r="E878">
+        <v>19</v>
+      </c>
+      <c r="F878">
+        <v>475</v>
+      </c>
+      <c r="G878">
+        <v>0</v>
+      </c>
+      <c r="H878">
+        <v>0</v>
+      </c>
+      <c r="I878">
+        <v>1</v>
+      </c>
+      <c r="J878">
+        <v>25</v>
+      </c>
+      <c r="K878">
+        <v>4</v>
+      </c>
+      <c r="L878">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="879" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A879" s="1">
+        <v>46089</v>
+      </c>
+      <c r="B879" t="s">
+        <v>2</v>
+      </c>
+      <c r="C879">
+        <v>0</v>
+      </c>
+      <c r="D879">
+        <v>0</v>
+      </c>
+      <c r="E879">
+        <v>5</v>
+      </c>
+      <c r="F879">
+        <v>125</v>
+      </c>
+      <c r="G879">
+        <v>0</v>
+      </c>
+      <c r="H879">
+        <v>0</v>
+      </c>
+      <c r="I879">
+        <v>0</v>
+      </c>
+      <c r="J879">
+        <v>0</v>
+      </c>
+      <c r="K879">
+        <v>1</v>
+      </c>
+      <c r="L879">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="880" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A880" s="1">
+        <v>46089</v>
+      </c>
+      <c r="B880" t="s">
+        <v>3</v>
+      </c>
+      <c r="C880">
+        <v>0</v>
+      </c>
+      <c r="D880">
+        <v>0</v>
+      </c>
+      <c r="E880">
+        <v>18</v>
+      </c>
+      <c r="F880">
+        <v>450</v>
+      </c>
+      <c r="G880">
+        <v>0</v>
+      </c>
+      <c r="H880">
+        <v>0</v>
+      </c>
+      <c r="I880">
+        <v>0</v>
+      </c>
+      <c r="J880">
+        <v>0</v>
+      </c>
+      <c r="K880">
+        <v>1</v>
+      </c>
+      <c r="L880">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="881" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A881" s="1">
+        <v>46090</v>
+      </c>
+      <c r="B881" t="s">
+        <v>2</v>
+      </c>
+      <c r="C881">
+        <v>0</v>
+      </c>
+      <c r="D881">
+        <v>0</v>
+      </c>
+      <c r="E881">
+        <v>6</v>
+      </c>
+      <c r="F881">
+        <v>150</v>
+      </c>
+      <c r="G881">
+        <v>0</v>
+      </c>
+      <c r="H881">
+        <v>0</v>
+      </c>
+      <c r="I881">
+        <v>0</v>
+      </c>
+      <c r="J881">
+        <v>0</v>
+      </c>
+      <c r="K881">
+        <v>1</v>
+      </c>
+      <c r="L881">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="882" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A882" s="1">
+        <v>46090</v>
+      </c>
+      <c r="B882" t="s">
+        <v>3</v>
+      </c>
+      <c r="C882">
+        <v>0</v>
+      </c>
+      <c r="D882">
+        <v>0</v>
+      </c>
+      <c r="E882">
+        <v>17</v>
+      </c>
+      <c r="F882">
+        <v>425</v>
+      </c>
+      <c r="G882">
+        <v>0</v>
+      </c>
+      <c r="H882">
+        <v>0</v>
+      </c>
+      <c r="I882">
+        <v>1</v>
+      </c>
+      <c r="J882">
+        <v>25</v>
+      </c>
+      <c r="K882">
+        <v>2</v>
+      </c>
+      <c r="L882">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="883" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A883" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B883" t="s">
+        <v>2</v>
+      </c>
+      <c r="C883">
+        <v>0</v>
+      </c>
+      <c r="D883">
+        <v>0</v>
+      </c>
+      <c r="E883">
+        <v>7</v>
+      </c>
+      <c r="F883">
+        <v>175</v>
+      </c>
+      <c r="G883">
+        <v>0</v>
+      </c>
+      <c r="H883">
+        <v>0</v>
+      </c>
+      <c r="I883">
+        <v>0</v>
+      </c>
+      <c r="J883">
+        <v>0</v>
+      </c>
+      <c r="K883">
+        <v>0</v>
+      </c>
+      <c r="L883">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="884" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A884" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B884" t="s">
+        <v>3</v>
+      </c>
+      <c r="C884">
+        <v>0</v>
+      </c>
+      <c r="D884">
+        <v>0</v>
+      </c>
+      <c r="E884">
+        <v>19</v>
+      </c>
+      <c r="F884">
+        <v>475</v>
+      </c>
+      <c r="G884">
+        <v>0</v>
+      </c>
+      <c r="H884">
+        <v>0</v>
+      </c>
+      <c r="I884">
+        <v>1</v>
+      </c>
+      <c r="J884">
+        <v>25</v>
+      </c>
+      <c r="K884">
+        <v>3</v>
+      </c>
+      <c r="L884">
         <v>75</v>
+      </c>
+    </row>
+    <row r="885" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A885" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B885" t="s">
+        <v>2</v>
+      </c>
+      <c r="C885">
+        <v>0</v>
+      </c>
+      <c r="D885">
+        <v>0</v>
+      </c>
+      <c r="E885">
+        <v>6</v>
+      </c>
+      <c r="F885">
+        <v>150</v>
+      </c>
+      <c r="G885">
+        <v>0</v>
+      </c>
+      <c r="H885">
+        <v>0</v>
+      </c>
+      <c r="I885">
+        <v>0</v>
+      </c>
+      <c r="J885">
+        <v>0</v>
+      </c>
+      <c r="K885">
+        <v>0</v>
+      </c>
+      <c r="L885">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="886" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A886" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B886" t="s">
+        <v>3</v>
+      </c>
+      <c r="C886">
+        <v>0</v>
+      </c>
+      <c r="D886">
+        <v>0</v>
+      </c>
+      <c r="E886">
+        <v>21</v>
+      </c>
+      <c r="F886">
+        <v>525</v>
+      </c>
+      <c r="G886">
+        <v>0</v>
+      </c>
+      <c r="H886">
+        <v>0</v>
+      </c>
+      <c r="I886">
+        <v>1</v>
+      </c>
+      <c r="J886">
+        <v>25</v>
+      </c>
+      <c r="K886">
+        <v>3</v>
+      </c>
+      <c r="L886">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="887" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A887" s="1">
+        <v>46093</v>
+      </c>
+      <c r="B887" t="s">
+        <v>2</v>
+      </c>
+      <c r="C887">
+        <v>0</v>
+      </c>
+      <c r="D887">
+        <v>0</v>
+      </c>
+      <c r="E887">
+        <v>7</v>
+      </c>
+      <c r="F887">
+        <v>175</v>
+      </c>
+      <c r="G887">
+        <v>0</v>
+      </c>
+      <c r="H887">
+        <v>0</v>
+      </c>
+      <c r="I887">
+        <v>0</v>
+      </c>
+      <c r="J887">
+        <v>0</v>
+      </c>
+      <c r="K887">
+        <v>1</v>
+      </c>
+      <c r="L887">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="888" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A888" s="1">
+        <v>46093</v>
+      </c>
+      <c r="B888" t="s">
+        <v>3</v>
+      </c>
+      <c r="C888">
+        <v>0</v>
+      </c>
+      <c r="D888">
+        <v>0</v>
+      </c>
+      <c r="E888">
+        <v>23</v>
+      </c>
+      <c r="F888">
+        <v>575</v>
+      </c>
+      <c r="G888">
+        <v>0</v>
+      </c>
+      <c r="H888">
+        <v>0</v>
+      </c>
+      <c r="I888">
+        <v>2</v>
+      </c>
+      <c r="J888">
+        <v>50</v>
+      </c>
+      <c r="K888">
+        <v>1</v>
+      </c>
+      <c r="L888">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="889" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A889" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B889" t="s">
+        <v>2</v>
+      </c>
+      <c r="C889">
+        <v>0</v>
+      </c>
+      <c r="D889">
+        <v>0</v>
+      </c>
+      <c r="E889">
+        <v>6</v>
+      </c>
+      <c r="F889">
+        <v>150</v>
+      </c>
+      <c r="G889">
+        <v>0</v>
+      </c>
+      <c r="H889">
+        <v>0</v>
+      </c>
+      <c r="I889">
+        <v>0</v>
+      </c>
+      <c r="J889">
+        <v>0</v>
+      </c>
+      <c r="K889">
+        <v>0</v>
+      </c>
+      <c r="L889">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="890" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A890" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B890" t="s">
+        <v>3</v>
+      </c>
+      <c r="C890">
+        <v>0</v>
+      </c>
+      <c r="D890">
+        <v>0</v>
+      </c>
+      <c r="E890">
+        <v>18</v>
+      </c>
+      <c r="F890">
+        <v>450</v>
+      </c>
+      <c r="G890">
+        <v>0</v>
+      </c>
+      <c r="H890">
+        <v>0</v>
+      </c>
+      <c r="I890">
+        <v>0</v>
+      </c>
+      <c r="J890">
+        <v>0</v>
+      </c>
+      <c r="K890">
+        <v>2</v>
+      </c>
+      <c r="L890">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="891" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A891" s="1">
+        <v>46095</v>
+      </c>
+      <c r="B891" t="s">
+        <v>2</v>
+      </c>
+      <c r="C891">
+        <v>0</v>
+      </c>
+      <c r="D891">
+        <v>0</v>
+      </c>
+      <c r="E891">
+        <v>6</v>
+      </c>
+      <c r="F891">
+        <v>150</v>
+      </c>
+      <c r="G891">
+        <v>0</v>
+      </c>
+      <c r="H891">
+        <v>0</v>
+      </c>
+      <c r="I891">
+        <v>0</v>
+      </c>
+      <c r="J891">
+        <v>0</v>
+      </c>
+      <c r="K891">
+        <v>0</v>
+      </c>
+      <c r="L891">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="892" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A892" s="1">
+        <v>46095</v>
+      </c>
+      <c r="B892" t="s">
+        <v>3</v>
+      </c>
+      <c r="C892">
+        <v>0</v>
+      </c>
+      <c r="D892">
+        <v>0</v>
+      </c>
+      <c r="E892">
+        <v>18</v>
+      </c>
+      <c r="F892">
+        <v>450</v>
+      </c>
+      <c r="G892">
+        <v>0</v>
+      </c>
+      <c r="H892">
+        <v>0</v>
+      </c>
+      <c r="I892">
+        <v>1</v>
+      </c>
+      <c r="J892">
+        <v>25</v>
+      </c>
+      <c r="K892">
+        <v>0</v>
+      </c>
+      <c r="L892">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="893" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A893" s="1">
+        <v>46096</v>
+      </c>
+      <c r="B893" t="s">
+        <v>2</v>
+      </c>
+      <c r="C893">
+        <v>0</v>
+      </c>
+      <c r="D893">
+        <v>0</v>
+      </c>
+      <c r="E893">
+        <v>5</v>
+      </c>
+      <c r="F893">
+        <v>125</v>
+      </c>
+      <c r="G893">
+        <v>0</v>
+      </c>
+      <c r="H893">
+        <v>0</v>
+      </c>
+      <c r="I893">
+        <v>0</v>
+      </c>
+      <c r="J893">
+        <v>0</v>
+      </c>
+      <c r="K893">
+        <v>1</v>
+      </c>
+      <c r="L893">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="894" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A894" s="1">
+        <v>46096</v>
+      </c>
+      <c r="B894" t="s">
+        <v>3</v>
+      </c>
+      <c r="C894">
+        <v>0</v>
+      </c>
+      <c r="D894">
+        <v>0</v>
+      </c>
+      <c r="E894">
+        <v>19</v>
+      </c>
+      <c r="F894">
+        <v>475</v>
+      </c>
+      <c r="G894">
+        <v>0</v>
+      </c>
+      <c r="H894">
+        <v>0</v>
+      </c>
+      <c r="I894">
+        <v>1</v>
+      </c>
+      <c r="J894">
+        <v>25</v>
+      </c>
+      <c r="K894">
+        <v>3</v>
+      </c>
+      <c r="L894">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="895" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A895" s="1">
+        <v>46097</v>
+      </c>
+      <c r="B895" t="s">
+        <v>2</v>
+      </c>
+      <c r="C895">
+        <v>0</v>
+      </c>
+      <c r="D895">
+        <v>0</v>
+      </c>
+      <c r="E895">
+        <v>7</v>
+      </c>
+      <c r="F895">
+        <v>175</v>
+      </c>
+      <c r="G895">
+        <v>0</v>
+      </c>
+      <c r="H895">
+        <v>0</v>
+      </c>
+      <c r="I895">
+        <v>0</v>
+      </c>
+      <c r="J895">
+        <v>0</v>
+      </c>
+      <c r="K895">
+        <v>0</v>
+      </c>
+      <c r="L895">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="896" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A896" s="1">
+        <v>46097</v>
+      </c>
+      <c r="B896" t="s">
+        <v>3</v>
+      </c>
+      <c r="C896">
+        <v>0</v>
+      </c>
+      <c r="D896">
+        <v>0</v>
+      </c>
+      <c r="E896">
+        <v>17</v>
+      </c>
+      <c r="F896">
+        <v>425</v>
+      </c>
+      <c r="G896">
+        <v>0</v>
+      </c>
+      <c r="H896">
+        <v>0</v>
+      </c>
+      <c r="I896">
+        <v>2</v>
+      </c>
+      <c r="J896">
+        <v>50</v>
+      </c>
+      <c r="K896">
+        <v>2</v>
+      </c>
+      <c r="L896">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="897" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A897" s="1">
+        <v>46098</v>
+      </c>
+      <c r="B897" t="s">
+        <v>2</v>
+      </c>
+      <c r="C897">
+        <v>0</v>
+      </c>
+      <c r="D897">
+        <v>0</v>
+      </c>
+      <c r="E897">
+        <v>6</v>
+      </c>
+      <c r="F897">
+        <v>150</v>
+      </c>
+      <c r="G897">
+        <v>0</v>
+      </c>
+      <c r="H897">
+        <v>0</v>
+      </c>
+      <c r="I897">
+        <v>0</v>
+      </c>
+      <c r="J897">
+        <v>0</v>
+      </c>
+      <c r="K897">
+        <v>0</v>
+      </c>
+      <c r="L897">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="898" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A898" s="1">
+        <v>46098</v>
+      </c>
+      <c r="B898" t="s">
+        <v>3</v>
+      </c>
+      <c r="C898">
+        <v>0</v>
+      </c>
+      <c r="D898">
+        <v>0</v>
+      </c>
+      <c r="E898">
+        <v>20</v>
+      </c>
+      <c r="F898">
+        <v>500</v>
+      </c>
+      <c r="G898">
+        <v>0</v>
+      </c>
+      <c r="H898">
+        <v>0</v>
+      </c>
+      <c r="I898">
+        <v>1</v>
+      </c>
+      <c r="J898">
+        <v>25</v>
+      </c>
+      <c r="K898">
+        <v>1</v>
+      </c>
+      <c r="L898">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="899" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A899" s="1">
+        <v>46099</v>
+      </c>
+      <c r="B899" t="s">
+        <v>2</v>
+      </c>
+      <c r="C899">
+        <v>0</v>
+      </c>
+      <c r="D899">
+        <v>0</v>
+      </c>
+      <c r="E899">
+        <v>5</v>
+      </c>
+      <c r="F899">
+        <v>125</v>
+      </c>
+      <c r="G899">
+        <v>0</v>
+      </c>
+      <c r="H899">
+        <v>0</v>
+      </c>
+      <c r="I899">
+        <v>0</v>
+      </c>
+      <c r="J899">
+        <v>0</v>
+      </c>
+      <c r="K899">
+        <v>1</v>
+      </c>
+      <c r="L899">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="900" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A900" s="1">
+        <v>46099</v>
+      </c>
+      <c r="B900" t="s">
+        <v>3</v>
+      </c>
+      <c r="C900">
+        <v>0</v>
+      </c>
+      <c r="D900">
+        <v>0</v>
+      </c>
+      <c r="E900">
+        <v>18</v>
+      </c>
+      <c r="F900">
+        <v>450</v>
+      </c>
+      <c r="G900">
+        <v>0</v>
+      </c>
+      <c r="H900">
+        <v>0</v>
+      </c>
+      <c r="I900">
+        <v>1</v>
+      </c>
+      <c r="J900">
+        <v>25</v>
+      </c>
+      <c r="K900">
+        <v>3</v>
+      </c>
+      <c r="L900">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="901" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A901" s="1">
+        <v>46100</v>
+      </c>
+      <c r="B901" t="s">
+        <v>2</v>
+      </c>
+      <c r="C901">
+        <v>0</v>
+      </c>
+      <c r="D901">
+        <v>0</v>
+      </c>
+      <c r="E901">
+        <v>6</v>
+      </c>
+      <c r="F901">
+        <v>150</v>
+      </c>
+      <c r="G901">
+        <v>0</v>
+      </c>
+      <c r="H901">
+        <v>0</v>
+      </c>
+      <c r="I901">
+        <v>0</v>
+      </c>
+      <c r="J901">
+        <v>0</v>
+      </c>
+      <c r="K901">
+        <v>0</v>
+      </c>
+      <c r="L901">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="902" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A902" s="1">
+        <v>46100</v>
+      </c>
+      <c r="B902" t="s">
+        <v>3</v>
+      </c>
+      <c r="C902">
+        <v>0</v>
+      </c>
+      <c r="D902">
+        <v>0</v>
+      </c>
+      <c r="E902">
+        <v>19</v>
+      </c>
+      <c r="F902">
+        <v>475</v>
+      </c>
+      <c r="G902">
+        <v>0</v>
+      </c>
+      <c r="H902">
+        <v>0</v>
+      </c>
+      <c r="I902">
+        <v>2</v>
+      </c>
+      <c r="J902">
+        <v>50</v>
+      </c>
+      <c r="K902">
+        <v>1</v>
+      </c>
+      <c r="L902">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="903" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A903" s="1">
+        <v>46101</v>
+      </c>
+      <c r="B903" t="s">
+        <v>2</v>
+      </c>
+      <c r="C903">
+        <v>0</v>
+      </c>
+      <c r="D903">
+        <v>0</v>
+      </c>
+      <c r="E903">
+        <v>8</v>
+      </c>
+      <c r="F903">
+        <v>200</v>
+      </c>
+      <c r="G903">
+        <v>0</v>
+      </c>
+      <c r="H903">
+        <v>0</v>
+      </c>
+      <c r="I903">
+        <v>0</v>
+      </c>
+      <c r="J903">
+        <v>0</v>
+      </c>
+      <c r="K903">
+        <v>1</v>
+      </c>
+      <c r="L903">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="904" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A904" s="1">
+        <v>46101</v>
+      </c>
+      <c r="B904" t="s">
+        <v>3</v>
+      </c>
+      <c r="C904">
+        <v>0</v>
+      </c>
+      <c r="D904">
+        <v>0</v>
+      </c>
+      <c r="E904">
+        <v>17</v>
+      </c>
+      <c r="F904">
+        <v>425</v>
+      </c>
+      <c r="G904">
+        <v>1</v>
+      </c>
+      <c r="H904">
+        <v>15</v>
+      </c>
+      <c r="I904">
+        <v>1</v>
+      </c>
+      <c r="J904">
+        <v>25</v>
+      </c>
+      <c r="K904">
+        <v>2</v>
+      </c>
+      <c r="L904">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="905" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A905" s="1">
+        <v>46102</v>
+      </c>
+      <c r="B905" t="s">
+        <v>2</v>
+      </c>
+      <c r="C905">
+        <v>0</v>
+      </c>
+      <c r="D905">
+        <v>0</v>
+      </c>
+      <c r="E905">
+        <v>6</v>
+      </c>
+      <c r="F905">
+        <v>150</v>
+      </c>
+      <c r="G905">
+        <v>0</v>
+      </c>
+      <c r="H905">
+        <v>0</v>
+      </c>
+      <c r="I905">
+        <v>0</v>
+      </c>
+      <c r="J905">
+        <v>0</v>
+      </c>
+      <c r="K905">
+        <v>1</v>
+      </c>
+      <c r="L905">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="906" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A906" s="1">
+        <v>46102</v>
+      </c>
+      <c r="B906" t="s">
+        <v>3</v>
+      </c>
+      <c r="C906">
+        <v>0</v>
+      </c>
+      <c r="D906">
+        <v>0</v>
+      </c>
+      <c r="E906">
+        <v>17</v>
+      </c>
+      <c r="F906">
+        <v>425</v>
+      </c>
+      <c r="G906">
+        <v>0</v>
+      </c>
+      <c r="H906">
+        <v>0</v>
+      </c>
+      <c r="I906">
+        <v>1</v>
+      </c>
+      <c r="J906">
+        <v>25</v>
+      </c>
+      <c r="K906">
+        <v>1</v>
+      </c>
+      <c r="L906">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="907" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A907" s="1">
+        <v>46103</v>
+      </c>
+      <c r="B907" t="s">
+        <v>2</v>
+      </c>
+      <c r="C907">
+        <v>0</v>
+      </c>
+      <c r="D907">
+        <v>0</v>
+      </c>
+      <c r="E907">
+        <v>6</v>
+      </c>
+      <c r="F907">
+        <v>150</v>
+      </c>
+      <c r="G907">
+        <v>0</v>
+      </c>
+      <c r="H907">
+        <v>0</v>
+      </c>
+      <c r="I907">
+        <v>0</v>
+      </c>
+      <c r="J907">
+        <v>0</v>
+      </c>
+      <c r="K907">
+        <v>0</v>
+      </c>
+      <c r="L907">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="908" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A908" s="1">
+        <v>46103</v>
+      </c>
+      <c r="B908" t="s">
+        <v>3</v>
+      </c>
+      <c r="C908">
+        <v>0</v>
+      </c>
+      <c r="D908">
+        <v>0</v>
+      </c>
+      <c r="E908">
+        <v>20</v>
+      </c>
+      <c r="F908">
+        <v>500</v>
+      </c>
+      <c r="G908">
+        <v>0</v>
+      </c>
+      <c r="H908">
+        <v>0</v>
+      </c>
+      <c r="I908">
+        <v>1</v>
+      </c>
+      <c r="J908">
+        <v>25</v>
+      </c>
+      <c r="K908">
+        <v>2</v>
+      </c>
+      <c r="L908">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="909" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A909" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B909" t="s">
+        <v>2</v>
+      </c>
+      <c r="C909">
+        <v>0</v>
+      </c>
+      <c r="D909">
+        <v>0</v>
+      </c>
+      <c r="E909">
+        <v>6</v>
+      </c>
+      <c r="F909">
+        <v>150</v>
+      </c>
+      <c r="G909">
+        <v>0</v>
+      </c>
+      <c r="H909">
+        <v>0</v>
+      </c>
+      <c r="I909">
+        <v>0</v>
+      </c>
+      <c r="J909">
+        <v>0</v>
+      </c>
+      <c r="K909">
+        <v>1</v>
+      </c>
+      <c r="L909">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="910" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A910" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B910" t="s">
+        <v>3</v>
+      </c>
+      <c r="C910">
+        <v>0</v>
+      </c>
+      <c r="D910">
+        <v>0</v>
+      </c>
+      <c r="E910">
+        <v>16</v>
+      </c>
+      <c r="F910">
+        <v>400</v>
+      </c>
+      <c r="G910">
+        <v>0</v>
+      </c>
+      <c r="H910">
+        <v>0</v>
+      </c>
+      <c r="I910">
+        <v>2</v>
+      </c>
+      <c r="J910">
+        <v>50</v>
+      </c>
+      <c r="K910">
+        <v>3</v>
+      </c>
+      <c r="L910">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="911" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A911" s="1">
+        <v>46105</v>
+      </c>
+      <c r="B911" t="s">
+        <v>2</v>
+      </c>
+      <c r="C911">
+        <v>0</v>
+      </c>
+      <c r="D911">
+        <v>0</v>
+      </c>
+      <c r="E911">
+        <v>8</v>
+      </c>
+      <c r="F911">
+        <v>200</v>
+      </c>
+      <c r="G911">
+        <v>0</v>
+      </c>
+      <c r="H911">
+        <v>0</v>
+      </c>
+      <c r="I911">
+        <v>0</v>
+      </c>
+      <c r="J911">
+        <v>0</v>
+      </c>
+      <c r="K911">
+        <v>1</v>
+      </c>
+      <c r="L911">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="912" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A912" s="1">
+        <v>46105</v>
+      </c>
+      <c r="B912" t="s">
+        <v>3</v>
+      </c>
+      <c r="C912">
+        <v>0</v>
+      </c>
+      <c r="D912">
+        <v>0</v>
+      </c>
+      <c r="E912">
+        <v>17</v>
+      </c>
+      <c r="F912">
+        <v>425</v>
+      </c>
+      <c r="G912">
+        <v>0</v>
+      </c>
+      <c r="H912">
+        <v>0</v>
+      </c>
+      <c r="I912">
+        <v>2</v>
+      </c>
+      <c r="J912">
+        <v>50</v>
+      </c>
+      <c r="K912">
+        <v>2</v>
+      </c>
+      <c r="L912">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="913" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A913" s="1">
+        <v>46106</v>
+      </c>
+      <c r="B913" t="s">
+        <v>2</v>
+      </c>
+      <c r="C913">
+        <v>0</v>
+      </c>
+      <c r="D913">
+        <v>0</v>
+      </c>
+      <c r="E913">
+        <v>6</v>
+      </c>
+      <c r="F913">
+        <v>150</v>
+      </c>
+      <c r="G913">
+        <v>0</v>
+      </c>
+      <c r="H913">
+        <v>0</v>
+      </c>
+      <c r="I913">
+        <v>0</v>
+      </c>
+      <c r="J913">
+        <v>0</v>
+      </c>
+      <c r="K913">
+        <v>0</v>
+      </c>
+      <c r="L913">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="914" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A914" s="1">
+        <v>46106</v>
+      </c>
+      <c r="B914" t="s">
+        <v>3</v>
+      </c>
+      <c r="C914">
+        <v>0</v>
+      </c>
+      <c r="D914">
+        <v>0</v>
+      </c>
+      <c r="E914">
+        <v>17</v>
+      </c>
+      <c r="F914">
+        <v>425</v>
+      </c>
+      <c r="G914">
+        <v>0</v>
+      </c>
+      <c r="H914">
+        <v>0</v>
+      </c>
+      <c r="I914">
+        <v>3</v>
+      </c>
+      <c r="J914">
+        <v>75</v>
+      </c>
+      <c r="K914">
+        <v>2</v>
+      </c>
+      <c r="L914">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="915" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A915" s="1">
+        <v>46107</v>
+      </c>
+      <c r="B915" t="s">
+        <v>2</v>
+      </c>
+      <c r="C915">
+        <v>0</v>
+      </c>
+      <c r="D915">
+        <v>0</v>
+      </c>
+      <c r="E915">
+        <v>7</v>
+      </c>
+      <c r="F915">
+        <v>175</v>
+      </c>
+      <c r="G915">
+        <v>0</v>
+      </c>
+      <c r="H915">
+        <v>0</v>
+      </c>
+      <c r="I915">
+        <v>0</v>
+      </c>
+      <c r="J915">
+        <v>0</v>
+      </c>
+      <c r="K915">
+        <v>0</v>
+      </c>
+      <c r="L915">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="916" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A916" s="1">
+        <v>46107</v>
+      </c>
+      <c r="B916" t="s">
+        <v>3</v>
+      </c>
+      <c r="C916">
+        <v>0</v>
+      </c>
+      <c r="D916">
+        <v>0</v>
+      </c>
+      <c r="E916">
+        <v>19</v>
+      </c>
+      <c r="F916">
+        <v>475</v>
+      </c>
+      <c r="G916">
+        <v>0</v>
+      </c>
+      <c r="H916">
+        <v>0</v>
+      </c>
+      <c r="I916">
+        <v>0</v>
+      </c>
+      <c r="J916">
+        <v>0</v>
+      </c>
+      <c r="K916">
+        <v>2</v>
+      </c>
+      <c r="L916">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="917" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A917" s="1">
+        <v>46108</v>
+      </c>
+      <c r="B917" t="s">
+        <v>2</v>
+      </c>
+      <c r="C917">
+        <v>0</v>
+      </c>
+      <c r="D917">
+        <v>0</v>
+      </c>
+      <c r="E917">
+        <v>7</v>
+      </c>
+      <c r="F917">
+        <v>175</v>
+      </c>
+      <c r="G917">
+        <v>0</v>
+      </c>
+      <c r="H917">
+        <v>0</v>
+      </c>
+      <c r="I917">
+        <v>0</v>
+      </c>
+      <c r="J917">
+        <v>0</v>
+      </c>
+      <c r="K917">
+        <v>1</v>
+      </c>
+      <c r="L917">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="918" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A918" s="1">
+        <v>46108</v>
+      </c>
+      <c r="B918" t="s">
+        <v>3</v>
+      </c>
+      <c r="C918">
+        <v>0</v>
+      </c>
+      <c r="D918">
+        <v>0</v>
+      </c>
+      <c r="E918">
+        <v>19</v>
+      </c>
+      <c r="F918">
+        <v>475</v>
+      </c>
+      <c r="G918">
+        <v>0</v>
+      </c>
+      <c r="H918">
+        <v>0</v>
+      </c>
+      <c r="I918">
+        <v>2</v>
+      </c>
+      <c r="J918">
+        <v>50</v>
+      </c>
+      <c r="K918">
+        <v>3</v>
+      </c>
+      <c r="L918">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="919" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A919" s="1">
+        <v>46109</v>
+      </c>
+      <c r="B919" t="s">
+        <v>2</v>
+      </c>
+      <c r="C919">
+        <v>0</v>
+      </c>
+      <c r="D919">
+        <v>0</v>
+      </c>
+      <c r="E919">
+        <v>6</v>
+      </c>
+      <c r="F919">
+        <v>150</v>
+      </c>
+      <c r="G919">
+        <v>0</v>
+      </c>
+      <c r="H919">
+        <v>0</v>
+      </c>
+      <c r="I919">
+        <v>0</v>
+      </c>
+      <c r="J919">
+        <v>0</v>
+      </c>
+      <c r="K919">
+        <v>1</v>
+      </c>
+      <c r="L919">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="920" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A920" s="1">
+        <v>46109</v>
+      </c>
+      <c r="B920" t="s">
+        <v>3</v>
+      </c>
+      <c r="C920">
+        <v>0</v>
+      </c>
+      <c r="D920">
+        <v>0</v>
+      </c>
+      <c r="E920">
+        <v>14</v>
+      </c>
+      <c r="F920">
+        <v>350</v>
+      </c>
+      <c r="G920">
+        <v>0</v>
+      </c>
+      <c r="H920">
+        <v>0</v>
+      </c>
+      <c r="I920">
+        <v>1</v>
+      </c>
+      <c r="J920">
+        <v>25</v>
+      </c>
+      <c r="K920">
+        <v>1</v>
+      </c>
+      <c r="L920">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="921" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A921" s="1">
+        <v>46110</v>
+      </c>
+      <c r="B921" t="s">
+        <v>2</v>
+      </c>
+      <c r="C921">
+        <v>0</v>
+      </c>
+      <c r="D921">
+        <v>0</v>
+      </c>
+      <c r="E921">
+        <v>5</v>
+      </c>
+      <c r="F921">
+        <v>125</v>
+      </c>
+      <c r="G921">
+        <v>0</v>
+      </c>
+      <c r="H921">
+        <v>0</v>
+      </c>
+      <c r="I921">
+        <v>0</v>
+      </c>
+      <c r="J921">
+        <v>0</v>
+      </c>
+      <c r="K921">
+        <v>0</v>
+      </c>
+      <c r="L921">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="922" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A922" s="1">
+        <v>46110</v>
+      </c>
+      <c r="B922" t="s">
+        <v>3</v>
+      </c>
+      <c r="C922">
+        <v>0</v>
+      </c>
+      <c r="D922">
+        <v>0</v>
+      </c>
+      <c r="E922">
+        <v>16</v>
+      </c>
+      <c r="F922">
+        <v>400</v>
+      </c>
+      <c r="G922">
+        <v>0</v>
+      </c>
+      <c r="H922">
+        <v>0</v>
+      </c>
+      <c r="I922">
+        <v>1</v>
+      </c>
+      <c r="J922">
+        <v>25</v>
+      </c>
+      <c r="K922">
+        <v>3</v>
+      </c>
+      <c r="L922">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="923" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A923" s="1">
+        <v>46111</v>
+      </c>
+      <c r="B923" t="s">
+        <v>2</v>
+      </c>
+      <c r="C923">
+        <v>0</v>
+      </c>
+      <c r="D923">
+        <v>0</v>
+      </c>
+      <c r="E923">
+        <v>8</v>
+      </c>
+      <c r="F923">
+        <v>200</v>
+      </c>
+      <c r="G923">
+        <v>0</v>
+      </c>
+      <c r="H923">
+        <v>0</v>
+      </c>
+      <c r="I923">
+        <v>0</v>
+      </c>
+      <c r="J923">
+        <v>0</v>
+      </c>
+      <c r="K923">
+        <v>1</v>
+      </c>
+      <c r="L923">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="924" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A924" s="1">
+        <v>46111</v>
+      </c>
+      <c r="B924" t="s">
+        <v>3</v>
+      </c>
+      <c r="C924">
+        <v>0</v>
+      </c>
+      <c r="D924">
+        <v>0</v>
+      </c>
+      <c r="E924">
+        <v>18</v>
+      </c>
+      <c r="F924">
+        <v>450</v>
+      </c>
+      <c r="G924">
+        <v>0</v>
+      </c>
+      <c r="H924">
+        <v>0</v>
+      </c>
+      <c r="I924">
+        <v>2</v>
+      </c>
+      <c r="J924">
+        <v>50</v>
+      </c>
+      <c r="K924">
+        <v>2</v>
+      </c>
+      <c r="L924">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="925" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A925" s="1">
+        <v>46112</v>
+      </c>
+      <c r="B925" t="s">
+        <v>2</v>
+      </c>
+      <c r="C925">
+        <v>0</v>
+      </c>
+      <c r="D925">
+        <v>0</v>
+      </c>
+      <c r="E925">
+        <v>6</v>
+      </c>
+      <c r="F925">
+        <v>150</v>
+      </c>
+      <c r="G925">
+        <v>0</v>
+      </c>
+      <c r="H925">
+        <v>0</v>
+      </c>
+      <c r="I925">
+        <v>0</v>
+      </c>
+      <c r="J925">
+        <v>0</v>
+      </c>
+      <c r="K925">
+        <v>0</v>
+      </c>
+      <c r="L925">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="926" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A926" s="1">
+        <v>46112</v>
+      </c>
+      <c r="B926" t="s">
+        <v>3</v>
+      </c>
+      <c r="C926">
+        <v>0</v>
+      </c>
+      <c r="D926">
+        <v>0</v>
+      </c>
+      <c r="E926">
+        <v>20</v>
+      </c>
+      <c r="F926">
+        <v>500</v>
+      </c>
+      <c r="G926">
+        <v>0</v>
+      </c>
+      <c r="H926">
+        <v>0</v>
+      </c>
+      <c r="I926">
+        <v>1</v>
+      </c>
+      <c r="J926">
+        <v>25</v>
+      </c>
+      <c r="K926">
+        <v>1</v>
+      </c>
+      <c r="L926">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/dados/BD_Bombonas.xlsx
+++ b/dados/BD_Bombonas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupomateus-my.sharepoint.com/personal/hamilton_pires_grupomateus_com/Documents/hamilton/Consultoria/Lidiane/2026/app_bombonas/dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="198" documentId="8_{40E215D4-4623-41EB-B246-4B63951E0A13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F4EC47C-0C1D-4A60-A064-51090B02DF62}"/>
+  <xr:revisionPtr revIDLastSave="210" documentId="8_{40E215D4-4623-41EB-B246-4B63951E0A13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD25099F-61A1-4F53-81B3-FDEBE2665E6C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{9588DCE0-F8D9-46B8-8782-90EC7820DC70}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="BASE BOMBONAS" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BASE BOMBONAS'!$A$1:$L$926</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BASE BOMBONAS'!$A$1:$L$986</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="937" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="997" uniqueCount="14">
   <si>
     <t>DATA</t>
   </si>
@@ -145,6 +145,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -467,7 +471,7 @@
   <sheetPr>
     <tabColor theme="6" tint="0.39997558519241921"/>
   </sheetPr>
-  <dimension ref="A1:L926"/>
+  <dimension ref="A1:L986"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
@@ -35657,6 +35661,2286 @@
         <v>25</v>
       </c>
     </row>
+    <row r="927" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A927" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B927" t="s">
+        <v>2</v>
+      </c>
+      <c r="C927">
+        <v>0</v>
+      </c>
+      <c r="D927">
+        <v>0</v>
+      </c>
+      <c r="E927">
+        <v>7</v>
+      </c>
+      <c r="F927">
+        <v>175</v>
+      </c>
+      <c r="G927">
+        <v>0</v>
+      </c>
+      <c r="H927">
+        <v>0</v>
+      </c>
+      <c r="I927">
+        <v>0</v>
+      </c>
+      <c r="J927">
+        <v>0</v>
+      </c>
+      <c r="K927">
+        <v>0</v>
+      </c>
+      <c r="L927">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="928" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A928" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B928" t="s">
+        <v>3</v>
+      </c>
+      <c r="C928">
+        <v>0</v>
+      </c>
+      <c r="D928">
+        <v>0</v>
+      </c>
+      <c r="E928">
+        <v>23</v>
+      </c>
+      <c r="F928">
+        <v>575</v>
+      </c>
+      <c r="G928">
+        <v>0</v>
+      </c>
+      <c r="H928">
+        <v>0</v>
+      </c>
+      <c r="I928">
+        <v>2</v>
+      </c>
+      <c r="J928">
+        <v>50</v>
+      </c>
+      <c r="K928">
+        <v>3</v>
+      </c>
+      <c r="L928">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="929" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A929" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B929" t="s">
+        <v>2</v>
+      </c>
+      <c r="C929">
+        <v>0</v>
+      </c>
+      <c r="D929">
+        <v>0</v>
+      </c>
+      <c r="E929">
+        <v>6</v>
+      </c>
+      <c r="F929">
+        <v>150</v>
+      </c>
+      <c r="G929">
+        <v>0</v>
+      </c>
+      <c r="H929">
+        <v>0</v>
+      </c>
+      <c r="I929">
+        <v>0</v>
+      </c>
+      <c r="J929">
+        <v>0</v>
+      </c>
+      <c r="K929">
+        <v>1</v>
+      </c>
+      <c r="L929">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="930" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A930" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B930" t="s">
+        <v>3</v>
+      </c>
+      <c r="C930">
+        <v>0</v>
+      </c>
+      <c r="D930">
+        <v>0</v>
+      </c>
+      <c r="E930">
+        <v>18</v>
+      </c>
+      <c r="F930">
+        <v>450</v>
+      </c>
+      <c r="G930">
+        <v>0</v>
+      </c>
+      <c r="H930">
+        <v>0</v>
+      </c>
+      <c r="I930">
+        <v>2</v>
+      </c>
+      <c r="J930">
+        <v>50</v>
+      </c>
+      <c r="K930">
+        <v>2</v>
+      </c>
+      <c r="L930">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="931" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A931" s="1">
+        <v>46115</v>
+      </c>
+      <c r="B931" t="s">
+        <v>2</v>
+      </c>
+      <c r="C931">
+        <v>0</v>
+      </c>
+      <c r="D931">
+        <v>0</v>
+      </c>
+      <c r="E931">
+        <v>6</v>
+      </c>
+      <c r="F931">
+        <v>150</v>
+      </c>
+      <c r="G931">
+        <v>0</v>
+      </c>
+      <c r="H931">
+        <v>0</v>
+      </c>
+      <c r="I931">
+        <v>0</v>
+      </c>
+      <c r="J931">
+        <v>0</v>
+      </c>
+      <c r="K931">
+        <v>0</v>
+      </c>
+      <c r="L931">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="932" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A932" s="1">
+        <v>46115</v>
+      </c>
+      <c r="B932" t="s">
+        <v>3</v>
+      </c>
+      <c r="C932">
+        <v>0</v>
+      </c>
+      <c r="D932">
+        <v>0</v>
+      </c>
+      <c r="E932">
+        <v>18</v>
+      </c>
+      <c r="F932">
+        <v>450</v>
+      </c>
+      <c r="G932">
+        <v>1</v>
+      </c>
+      <c r="H932">
+        <v>15</v>
+      </c>
+      <c r="I932">
+        <v>1</v>
+      </c>
+      <c r="J932">
+        <v>25</v>
+      </c>
+      <c r="K932">
+        <v>3</v>
+      </c>
+      <c r="L932">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="933" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A933" s="1">
+        <v>46116</v>
+      </c>
+      <c r="B933" t="s">
+        <v>2</v>
+      </c>
+      <c r="C933">
+        <v>0</v>
+      </c>
+      <c r="D933">
+        <v>0</v>
+      </c>
+      <c r="E933">
+        <v>6</v>
+      </c>
+      <c r="F933">
+        <v>150</v>
+      </c>
+      <c r="G933">
+        <v>0</v>
+      </c>
+      <c r="H933">
+        <v>0</v>
+      </c>
+      <c r="I933">
+        <v>0</v>
+      </c>
+      <c r="J933">
+        <v>0</v>
+      </c>
+      <c r="K933">
+        <v>1</v>
+      </c>
+      <c r="L933">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="934" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A934" s="1">
+        <v>46116</v>
+      </c>
+      <c r="B934" t="s">
+        <v>3</v>
+      </c>
+      <c r="C934">
+        <v>0</v>
+      </c>
+      <c r="D934">
+        <v>0</v>
+      </c>
+      <c r="E934">
+        <v>16</v>
+      </c>
+      <c r="F934">
+        <v>400</v>
+      </c>
+      <c r="G934">
+        <v>0</v>
+      </c>
+      <c r="H934">
+        <v>0</v>
+      </c>
+      <c r="I934">
+        <v>2</v>
+      </c>
+      <c r="J934">
+        <v>50</v>
+      </c>
+      <c r="K934">
+        <v>2</v>
+      </c>
+      <c r="L934">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="935" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A935" s="1">
+        <v>46117</v>
+      </c>
+      <c r="B935" t="s">
+        <v>2</v>
+      </c>
+      <c r="C935">
+        <v>0</v>
+      </c>
+      <c r="D935">
+        <v>0</v>
+      </c>
+      <c r="E935">
+        <v>6</v>
+      </c>
+      <c r="F935">
+        <v>150</v>
+      </c>
+      <c r="G935">
+        <v>0</v>
+      </c>
+      <c r="H935">
+        <v>0</v>
+      </c>
+      <c r="I935">
+        <v>0</v>
+      </c>
+      <c r="J935">
+        <v>0</v>
+      </c>
+      <c r="K935">
+        <v>0</v>
+      </c>
+      <c r="L935">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="936" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A936" s="1">
+        <v>46117</v>
+      </c>
+      <c r="B936" t="s">
+        <v>3</v>
+      </c>
+      <c r="C936">
+        <v>0</v>
+      </c>
+      <c r="D936">
+        <v>0</v>
+      </c>
+      <c r="E936">
+        <v>19</v>
+      </c>
+      <c r="F936">
+        <v>475</v>
+      </c>
+      <c r="G936">
+        <v>0</v>
+      </c>
+      <c r="H936">
+        <v>0</v>
+      </c>
+      <c r="I936">
+        <v>0</v>
+      </c>
+      <c r="J936">
+        <v>0</v>
+      </c>
+      <c r="K936">
+        <v>2</v>
+      </c>
+      <c r="L936">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="937" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A937" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B937" t="s">
+        <v>2</v>
+      </c>
+      <c r="C937">
+        <v>0</v>
+      </c>
+      <c r="D937">
+        <v>0</v>
+      </c>
+      <c r="E937">
+        <v>6</v>
+      </c>
+      <c r="F937">
+        <v>150</v>
+      </c>
+      <c r="G937">
+        <v>0</v>
+      </c>
+      <c r="H937">
+        <v>0</v>
+      </c>
+      <c r="I937">
+        <v>0</v>
+      </c>
+      <c r="J937">
+        <v>0</v>
+      </c>
+      <c r="K937">
+        <v>0</v>
+      </c>
+      <c r="L937">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="938" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A938" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B938" t="s">
+        <v>3</v>
+      </c>
+      <c r="C938">
+        <v>0</v>
+      </c>
+      <c r="D938">
+        <v>0</v>
+      </c>
+      <c r="E938">
+        <v>17</v>
+      </c>
+      <c r="F938">
+        <v>425</v>
+      </c>
+      <c r="G938">
+        <v>1</v>
+      </c>
+      <c r="H938">
+        <v>15</v>
+      </c>
+      <c r="I938">
+        <v>1</v>
+      </c>
+      <c r="J938">
+        <v>25</v>
+      </c>
+      <c r="K938">
+        <v>1</v>
+      </c>
+      <c r="L938">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="939" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A939" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B939" t="s">
+        <v>2</v>
+      </c>
+      <c r="C939">
+        <v>0</v>
+      </c>
+      <c r="D939">
+        <v>0</v>
+      </c>
+      <c r="E939">
+        <v>5</v>
+      </c>
+      <c r="F939">
+        <v>125</v>
+      </c>
+      <c r="G939">
+        <v>0</v>
+      </c>
+      <c r="H939">
+        <v>0</v>
+      </c>
+      <c r="I939">
+        <v>0</v>
+      </c>
+      <c r="J939">
+        <v>0</v>
+      </c>
+      <c r="K939">
+        <v>1</v>
+      </c>
+      <c r="L939">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="940" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A940" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B940" t="s">
+        <v>3</v>
+      </c>
+      <c r="C940">
+        <v>0</v>
+      </c>
+      <c r="D940">
+        <v>0</v>
+      </c>
+      <c r="E940">
+        <v>19</v>
+      </c>
+      <c r="F940">
+        <v>475</v>
+      </c>
+      <c r="G940">
+        <v>0</v>
+      </c>
+      <c r="H940">
+        <v>0</v>
+      </c>
+      <c r="I940">
+        <v>2</v>
+      </c>
+      <c r="J940">
+        <v>50</v>
+      </c>
+      <c r="K940">
+        <v>3</v>
+      </c>
+      <c r="L940">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="941" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A941" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B941" t="s">
+        <v>2</v>
+      </c>
+      <c r="C941">
+        <v>0</v>
+      </c>
+      <c r="D941">
+        <v>0</v>
+      </c>
+      <c r="E941">
+        <v>7</v>
+      </c>
+      <c r="F941">
+        <v>175</v>
+      </c>
+      <c r="G941">
+        <v>0</v>
+      </c>
+      <c r="H941">
+        <v>0</v>
+      </c>
+      <c r="I941">
+        <v>0</v>
+      </c>
+      <c r="J941">
+        <v>0</v>
+      </c>
+      <c r="K941">
+        <v>0</v>
+      </c>
+      <c r="L941">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="942" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A942" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B942" t="s">
+        <v>3</v>
+      </c>
+      <c r="C942">
+        <v>0</v>
+      </c>
+      <c r="D942">
+        <v>0</v>
+      </c>
+      <c r="E942">
+        <v>18</v>
+      </c>
+      <c r="F942">
+        <v>450</v>
+      </c>
+      <c r="G942">
+        <v>0</v>
+      </c>
+      <c r="H942">
+        <v>0</v>
+      </c>
+      <c r="I942">
+        <v>1</v>
+      </c>
+      <c r="J942">
+        <v>25</v>
+      </c>
+      <c r="K942">
+        <v>2</v>
+      </c>
+      <c r="L942">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="943" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A943" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B943" t="s">
+        <v>2</v>
+      </c>
+      <c r="C943">
+        <v>0</v>
+      </c>
+      <c r="D943">
+        <v>0</v>
+      </c>
+      <c r="E943">
+        <v>6</v>
+      </c>
+      <c r="F943">
+        <v>150</v>
+      </c>
+      <c r="G943">
+        <v>0</v>
+      </c>
+      <c r="H943">
+        <v>0</v>
+      </c>
+      <c r="I943">
+        <v>0</v>
+      </c>
+      <c r="J943">
+        <v>0</v>
+      </c>
+      <c r="K943">
+        <v>0</v>
+      </c>
+      <c r="L943">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="944" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A944" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B944" t="s">
+        <v>3</v>
+      </c>
+      <c r="C944">
+        <v>0</v>
+      </c>
+      <c r="D944">
+        <v>0</v>
+      </c>
+      <c r="E944">
+        <v>19</v>
+      </c>
+      <c r="F944">
+        <v>475</v>
+      </c>
+      <c r="G944">
+        <v>0</v>
+      </c>
+      <c r="H944">
+        <v>0</v>
+      </c>
+      <c r="I944">
+        <v>2</v>
+      </c>
+      <c r="J944">
+        <v>50</v>
+      </c>
+      <c r="K944">
+        <v>2</v>
+      </c>
+      <c r="L944">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="945" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A945" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B945" t="s">
+        <v>2</v>
+      </c>
+      <c r="C945">
+        <v>0</v>
+      </c>
+      <c r="D945">
+        <v>0</v>
+      </c>
+      <c r="E945">
+        <v>5</v>
+      </c>
+      <c r="F945">
+        <v>125</v>
+      </c>
+      <c r="G945">
+        <v>0</v>
+      </c>
+      <c r="H945">
+        <v>0</v>
+      </c>
+      <c r="I945">
+        <v>0</v>
+      </c>
+      <c r="J945">
+        <v>0</v>
+      </c>
+      <c r="K945">
+        <v>0</v>
+      </c>
+      <c r="L945">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="946" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A946" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B946" t="s">
+        <v>3</v>
+      </c>
+      <c r="C946">
+        <v>0</v>
+      </c>
+      <c r="D946">
+        <v>0</v>
+      </c>
+      <c r="E946">
+        <v>13</v>
+      </c>
+      <c r="F946">
+        <v>325</v>
+      </c>
+      <c r="G946">
+        <v>0</v>
+      </c>
+      <c r="H946">
+        <v>0</v>
+      </c>
+      <c r="I946">
+        <v>1</v>
+      </c>
+      <c r="J946">
+        <v>25</v>
+      </c>
+      <c r="K946">
+        <v>2</v>
+      </c>
+      <c r="L946">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="947" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A947" s="1">
+        <v>46123</v>
+      </c>
+      <c r="B947" t="s">
+        <v>2</v>
+      </c>
+      <c r="C947">
+        <v>0</v>
+      </c>
+      <c r="D947">
+        <v>0</v>
+      </c>
+      <c r="E947">
+        <v>8</v>
+      </c>
+      <c r="F947">
+        <v>200</v>
+      </c>
+      <c r="G947">
+        <v>0</v>
+      </c>
+      <c r="H947">
+        <v>0</v>
+      </c>
+      <c r="I947">
+        <v>0</v>
+      </c>
+      <c r="J947">
+        <v>0</v>
+      </c>
+      <c r="K947">
+        <v>1</v>
+      </c>
+      <c r="L947">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="948" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A948" s="1">
+        <v>46123</v>
+      </c>
+      <c r="B948" t="s">
+        <v>3</v>
+      </c>
+      <c r="C948">
+        <v>0</v>
+      </c>
+      <c r="D948">
+        <v>0</v>
+      </c>
+      <c r="E948">
+        <v>22</v>
+      </c>
+      <c r="F948">
+        <v>550</v>
+      </c>
+      <c r="G948">
+        <v>0</v>
+      </c>
+      <c r="H948">
+        <v>0</v>
+      </c>
+      <c r="I948">
+        <v>0</v>
+      </c>
+      <c r="J948">
+        <v>0</v>
+      </c>
+      <c r="K948">
+        <v>3</v>
+      </c>
+      <c r="L948">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="949" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A949" s="1">
+        <v>46124</v>
+      </c>
+      <c r="B949" t="s">
+        <v>2</v>
+      </c>
+      <c r="C949">
+        <v>0</v>
+      </c>
+      <c r="D949">
+        <v>0</v>
+      </c>
+      <c r="E949">
+        <v>6</v>
+      </c>
+      <c r="F949">
+        <v>150</v>
+      </c>
+      <c r="G949">
+        <v>0</v>
+      </c>
+      <c r="H949">
+        <v>0</v>
+      </c>
+      <c r="I949">
+        <v>0</v>
+      </c>
+      <c r="J949">
+        <v>0</v>
+      </c>
+      <c r="K949">
+        <v>0</v>
+      </c>
+      <c r="L949">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="950" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A950" s="1">
+        <v>46124</v>
+      </c>
+      <c r="B950" t="s">
+        <v>3</v>
+      </c>
+      <c r="C950">
+        <v>0</v>
+      </c>
+      <c r="D950">
+        <v>0</v>
+      </c>
+      <c r="E950">
+        <v>27</v>
+      </c>
+      <c r="F950">
+        <v>675</v>
+      </c>
+      <c r="G950">
+        <v>0</v>
+      </c>
+      <c r="H950">
+        <v>0</v>
+      </c>
+      <c r="I950">
+        <v>1</v>
+      </c>
+      <c r="J950">
+        <v>25</v>
+      </c>
+      <c r="K950">
+        <v>3</v>
+      </c>
+      <c r="L950">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="951" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A951" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B951" t="s">
+        <v>2</v>
+      </c>
+      <c r="C951">
+        <v>0</v>
+      </c>
+      <c r="D951">
+        <v>0</v>
+      </c>
+      <c r="E951">
+        <v>6</v>
+      </c>
+      <c r="F951">
+        <v>150</v>
+      </c>
+      <c r="G951">
+        <v>0</v>
+      </c>
+      <c r="H951">
+        <v>0</v>
+      </c>
+      <c r="I951">
+        <v>0</v>
+      </c>
+      <c r="J951">
+        <v>0</v>
+      </c>
+      <c r="K951">
+        <v>0</v>
+      </c>
+      <c r="L951">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="952" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A952" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B952" t="s">
+        <v>3</v>
+      </c>
+      <c r="C952">
+        <v>0</v>
+      </c>
+      <c r="D952">
+        <v>0</v>
+      </c>
+      <c r="E952">
+        <v>21</v>
+      </c>
+      <c r="F952">
+        <v>525</v>
+      </c>
+      <c r="G952">
+        <v>0</v>
+      </c>
+      <c r="H952">
+        <v>0</v>
+      </c>
+      <c r="I952">
+        <v>2</v>
+      </c>
+      <c r="J952">
+        <v>50</v>
+      </c>
+      <c r="K952">
+        <v>1</v>
+      </c>
+      <c r="L952">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="953" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A953" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B953" t="s">
+        <v>2</v>
+      </c>
+      <c r="C953">
+        <v>0</v>
+      </c>
+      <c r="D953">
+        <v>0</v>
+      </c>
+      <c r="E953">
+        <v>6</v>
+      </c>
+      <c r="F953">
+        <v>150</v>
+      </c>
+      <c r="G953">
+        <v>0</v>
+      </c>
+      <c r="H953">
+        <v>0</v>
+      </c>
+      <c r="I953">
+        <v>0</v>
+      </c>
+      <c r="J953">
+        <v>0</v>
+      </c>
+      <c r="K953">
+        <v>1</v>
+      </c>
+      <c r="L953">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="954" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A954" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B954" t="s">
+        <v>3</v>
+      </c>
+      <c r="C954">
+        <v>0</v>
+      </c>
+      <c r="D954">
+        <v>0</v>
+      </c>
+      <c r="E954">
+        <v>25</v>
+      </c>
+      <c r="F954">
+        <v>625</v>
+      </c>
+      <c r="G954">
+        <v>0</v>
+      </c>
+      <c r="H954">
+        <v>0</v>
+      </c>
+      <c r="I954">
+        <v>1</v>
+      </c>
+      <c r="J954">
+        <v>25</v>
+      </c>
+      <c r="K954">
+        <v>2</v>
+      </c>
+      <c r="L954">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="955" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A955" s="1">
+        <v>46127</v>
+      </c>
+      <c r="B955" t="s">
+        <v>2</v>
+      </c>
+      <c r="C955">
+        <v>0</v>
+      </c>
+      <c r="D955">
+        <v>0</v>
+      </c>
+      <c r="E955">
+        <v>5</v>
+      </c>
+      <c r="F955">
+        <v>125</v>
+      </c>
+      <c r="G955">
+        <v>0</v>
+      </c>
+      <c r="H955">
+        <v>0</v>
+      </c>
+      <c r="I955">
+        <v>0</v>
+      </c>
+      <c r="J955">
+        <v>0</v>
+      </c>
+      <c r="K955">
+        <v>1</v>
+      </c>
+      <c r="L955">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="956" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A956" s="1">
+        <v>46127</v>
+      </c>
+      <c r="B956" t="s">
+        <v>3</v>
+      </c>
+      <c r="C956">
+        <v>0</v>
+      </c>
+      <c r="D956">
+        <v>0</v>
+      </c>
+      <c r="E956">
+        <v>26</v>
+      </c>
+      <c r="F956">
+        <v>650</v>
+      </c>
+      <c r="G956">
+        <v>1</v>
+      </c>
+      <c r="H956">
+        <v>15</v>
+      </c>
+      <c r="I956">
+        <v>1</v>
+      </c>
+      <c r="J956">
+        <v>25</v>
+      </c>
+      <c r="K956">
+        <v>2</v>
+      </c>
+      <c r="L956">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="957" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A957" s="1">
+        <v>46128</v>
+      </c>
+      <c r="B957" t="s">
+        <v>2</v>
+      </c>
+      <c r="C957">
+        <v>0</v>
+      </c>
+      <c r="D957">
+        <v>0</v>
+      </c>
+      <c r="E957">
+        <v>7</v>
+      </c>
+      <c r="F957">
+        <v>175</v>
+      </c>
+      <c r="G957">
+        <v>0</v>
+      </c>
+      <c r="H957">
+        <v>0</v>
+      </c>
+      <c r="I957">
+        <v>0</v>
+      </c>
+      <c r="J957">
+        <v>0</v>
+      </c>
+      <c r="K957">
+        <v>0</v>
+      </c>
+      <c r="L957">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="958" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A958" s="1">
+        <v>46128</v>
+      </c>
+      <c r="B958" t="s">
+        <v>3</v>
+      </c>
+      <c r="C958">
+        <v>2</v>
+      </c>
+      <c r="D958">
+        <v>50</v>
+      </c>
+      <c r="E958">
+        <v>23</v>
+      </c>
+      <c r="F958">
+        <v>575</v>
+      </c>
+      <c r="G958">
+        <v>0</v>
+      </c>
+      <c r="H958">
+        <v>0</v>
+      </c>
+      <c r="I958">
+        <v>2</v>
+      </c>
+      <c r="J958">
+        <v>50</v>
+      </c>
+      <c r="K958">
+        <v>3</v>
+      </c>
+      <c r="L958">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="959" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A959" s="1">
+        <v>46129</v>
+      </c>
+      <c r="B959" t="s">
+        <v>2</v>
+      </c>
+      <c r="C959">
+        <v>0</v>
+      </c>
+      <c r="D959">
+        <v>0</v>
+      </c>
+      <c r="E959">
+        <v>6</v>
+      </c>
+      <c r="F959">
+        <v>150</v>
+      </c>
+      <c r="G959">
+        <v>0</v>
+      </c>
+      <c r="H959">
+        <v>0</v>
+      </c>
+      <c r="I959">
+        <v>0</v>
+      </c>
+      <c r="J959">
+        <v>0</v>
+      </c>
+      <c r="K959">
+        <v>1</v>
+      </c>
+      <c r="L959">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="960" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A960" s="1">
+        <v>46129</v>
+      </c>
+      <c r="B960" t="s">
+        <v>3</v>
+      </c>
+      <c r="C960">
+        <v>2</v>
+      </c>
+      <c r="D960">
+        <v>50</v>
+      </c>
+      <c r="E960">
+        <v>19</v>
+      </c>
+      <c r="F960">
+        <v>475</v>
+      </c>
+      <c r="G960">
+        <v>0</v>
+      </c>
+      <c r="H960">
+        <v>0</v>
+      </c>
+      <c r="I960">
+        <v>2</v>
+      </c>
+      <c r="J960">
+        <v>50</v>
+      </c>
+      <c r="K960">
+        <v>2</v>
+      </c>
+      <c r="L960">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="961" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A961" s="1">
+        <v>46130</v>
+      </c>
+      <c r="B961" t="s">
+        <v>2</v>
+      </c>
+      <c r="C961">
+        <v>0</v>
+      </c>
+      <c r="D961">
+        <v>0</v>
+      </c>
+      <c r="E961">
+        <v>7</v>
+      </c>
+      <c r="F961">
+        <v>175</v>
+      </c>
+      <c r="G961">
+        <v>0</v>
+      </c>
+      <c r="H961">
+        <v>0</v>
+      </c>
+      <c r="I961">
+        <v>0</v>
+      </c>
+      <c r="J961">
+        <v>0</v>
+      </c>
+      <c r="K961">
+        <v>0</v>
+      </c>
+      <c r="L961">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="962" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A962" s="1">
+        <v>46130</v>
+      </c>
+      <c r="B962" t="s">
+        <v>3</v>
+      </c>
+      <c r="C962">
+        <v>0</v>
+      </c>
+      <c r="D962">
+        <v>0</v>
+      </c>
+      <c r="E962">
+        <v>18</v>
+      </c>
+      <c r="F962">
+        <v>450</v>
+      </c>
+      <c r="G962">
+        <v>0</v>
+      </c>
+      <c r="H962">
+        <v>0</v>
+      </c>
+      <c r="I962">
+        <v>1</v>
+      </c>
+      <c r="J962">
+        <v>25</v>
+      </c>
+      <c r="K962">
+        <v>2</v>
+      </c>
+      <c r="L962">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="963" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A963" s="1">
+        <v>46131</v>
+      </c>
+      <c r="B963" t="s">
+        <v>2</v>
+      </c>
+      <c r="C963">
+        <v>0</v>
+      </c>
+      <c r="D963">
+        <v>0</v>
+      </c>
+      <c r="E963">
+        <v>5</v>
+      </c>
+      <c r="F963">
+        <v>125</v>
+      </c>
+      <c r="G963">
+        <v>0</v>
+      </c>
+      <c r="H963">
+        <v>0</v>
+      </c>
+      <c r="I963">
+        <v>0</v>
+      </c>
+      <c r="J963">
+        <v>0</v>
+      </c>
+      <c r="K963">
+        <v>0</v>
+      </c>
+      <c r="L963">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="964" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A964" s="1">
+        <v>46131</v>
+      </c>
+      <c r="B964" t="s">
+        <v>3</v>
+      </c>
+      <c r="C964">
+        <v>0</v>
+      </c>
+      <c r="D964">
+        <v>0</v>
+      </c>
+      <c r="E964">
+        <v>18</v>
+      </c>
+      <c r="F964">
+        <v>450</v>
+      </c>
+      <c r="G964">
+        <v>0</v>
+      </c>
+      <c r="H964">
+        <v>0</v>
+      </c>
+      <c r="I964">
+        <v>0</v>
+      </c>
+      <c r="J964">
+        <v>0</v>
+      </c>
+      <c r="K964">
+        <v>0</v>
+      </c>
+      <c r="L964">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="965" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A965" s="1">
+        <v>46132</v>
+      </c>
+      <c r="B965" t="s">
+        <v>2</v>
+      </c>
+      <c r="C965">
+        <v>0</v>
+      </c>
+      <c r="D965">
+        <v>0</v>
+      </c>
+      <c r="E965">
+        <v>7</v>
+      </c>
+      <c r="F965">
+        <v>175</v>
+      </c>
+      <c r="G965">
+        <v>0</v>
+      </c>
+      <c r="H965">
+        <v>0</v>
+      </c>
+      <c r="I965">
+        <v>0</v>
+      </c>
+      <c r="J965">
+        <v>0</v>
+      </c>
+      <c r="K965">
+        <v>1</v>
+      </c>
+      <c r="L965">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="966" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A966" s="1">
+        <v>46132</v>
+      </c>
+      <c r="B966" t="s">
+        <v>3</v>
+      </c>
+      <c r="C966">
+        <v>2</v>
+      </c>
+      <c r="D966">
+        <v>50</v>
+      </c>
+      <c r="E966">
+        <v>19</v>
+      </c>
+      <c r="F966">
+        <v>475</v>
+      </c>
+      <c r="G966">
+        <v>0</v>
+      </c>
+      <c r="H966">
+        <v>0</v>
+      </c>
+      <c r="I966">
+        <v>2</v>
+      </c>
+      <c r="J966">
+        <v>50</v>
+      </c>
+      <c r="K966">
+        <v>4</v>
+      </c>
+      <c r="L966">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="967" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A967" s="1">
+        <v>46133</v>
+      </c>
+      <c r="B967" t="s">
+        <v>2</v>
+      </c>
+      <c r="C967">
+        <v>0</v>
+      </c>
+      <c r="D967">
+        <v>0</v>
+      </c>
+      <c r="E967">
+        <v>6</v>
+      </c>
+      <c r="F967">
+        <v>150</v>
+      </c>
+      <c r="G967">
+        <v>0</v>
+      </c>
+      <c r="H967">
+        <v>0</v>
+      </c>
+      <c r="I967">
+        <v>0</v>
+      </c>
+      <c r="J967">
+        <v>0</v>
+      </c>
+      <c r="K967">
+        <v>1</v>
+      </c>
+      <c r="L967">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="968" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A968" s="1">
+        <v>46133</v>
+      </c>
+      <c r="B968" t="s">
+        <v>3</v>
+      </c>
+      <c r="C968">
+        <v>0</v>
+      </c>
+      <c r="D968">
+        <v>0</v>
+      </c>
+      <c r="E968">
+        <v>21</v>
+      </c>
+      <c r="F968">
+        <v>525</v>
+      </c>
+      <c r="G968">
+        <v>0</v>
+      </c>
+      <c r="H968">
+        <v>0</v>
+      </c>
+      <c r="I968">
+        <v>1</v>
+      </c>
+      <c r="J968">
+        <v>25</v>
+      </c>
+      <c r="K968">
+        <v>1</v>
+      </c>
+      <c r="L968">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="969" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A969" s="1">
+        <v>46134</v>
+      </c>
+      <c r="B969" t="s">
+        <v>2</v>
+      </c>
+      <c r="C969">
+        <v>0</v>
+      </c>
+      <c r="D969">
+        <v>0</v>
+      </c>
+      <c r="E969">
+        <v>8</v>
+      </c>
+      <c r="F969">
+        <v>200</v>
+      </c>
+      <c r="G969">
+        <v>0</v>
+      </c>
+      <c r="H969">
+        <v>0</v>
+      </c>
+      <c r="I969">
+        <v>0</v>
+      </c>
+      <c r="J969">
+        <v>0</v>
+      </c>
+      <c r="K969">
+        <v>0</v>
+      </c>
+      <c r="L969">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="970" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A970" s="1">
+        <v>46134</v>
+      </c>
+      <c r="B970" t="s">
+        <v>3</v>
+      </c>
+      <c r="C970">
+        <v>0</v>
+      </c>
+      <c r="D970">
+        <v>0</v>
+      </c>
+      <c r="E970">
+        <v>18</v>
+      </c>
+      <c r="F970">
+        <v>450</v>
+      </c>
+      <c r="G970">
+        <v>0</v>
+      </c>
+      <c r="H970">
+        <v>0</v>
+      </c>
+      <c r="I970">
+        <v>1</v>
+      </c>
+      <c r="J970">
+        <v>25</v>
+      </c>
+      <c r="K970">
+        <v>2</v>
+      </c>
+      <c r="L970">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="971" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A971" s="1">
+        <v>46135</v>
+      </c>
+      <c r="B971" t="s">
+        <v>2</v>
+      </c>
+      <c r="C971">
+        <v>0</v>
+      </c>
+      <c r="D971">
+        <v>0</v>
+      </c>
+      <c r="E971">
+        <v>8</v>
+      </c>
+      <c r="F971">
+        <v>200</v>
+      </c>
+      <c r="G971">
+        <v>0</v>
+      </c>
+      <c r="H971">
+        <v>0</v>
+      </c>
+      <c r="I971">
+        <v>0</v>
+      </c>
+      <c r="J971">
+        <v>0</v>
+      </c>
+      <c r="K971">
+        <v>1</v>
+      </c>
+      <c r="L971">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="972" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A972" s="1">
+        <v>46135</v>
+      </c>
+      <c r="B972" t="s">
+        <v>3</v>
+      </c>
+      <c r="C972">
+        <v>2</v>
+      </c>
+      <c r="D972">
+        <v>50</v>
+      </c>
+      <c r="E972">
+        <v>18</v>
+      </c>
+      <c r="F972">
+        <v>450</v>
+      </c>
+      <c r="G972">
+        <v>0</v>
+      </c>
+      <c r="H972">
+        <v>0</v>
+      </c>
+      <c r="I972">
+        <v>1</v>
+      </c>
+      <c r="J972">
+        <v>25</v>
+      </c>
+      <c r="K972">
+        <v>2</v>
+      </c>
+      <c r="L972">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="973" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A973" s="1">
+        <v>46136</v>
+      </c>
+      <c r="B973" t="s">
+        <v>2</v>
+      </c>
+      <c r="C973">
+        <v>0</v>
+      </c>
+      <c r="D973">
+        <v>0</v>
+      </c>
+      <c r="E973">
+        <v>6</v>
+      </c>
+      <c r="F973">
+        <v>150</v>
+      </c>
+      <c r="G973">
+        <v>0</v>
+      </c>
+      <c r="H973">
+        <v>0</v>
+      </c>
+      <c r="I973">
+        <v>0</v>
+      </c>
+      <c r="J973">
+        <v>0</v>
+      </c>
+      <c r="K973">
+        <v>0</v>
+      </c>
+      <c r="L973">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="974" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A974" s="1">
+        <v>46136</v>
+      </c>
+      <c r="B974" t="s">
+        <v>3</v>
+      </c>
+      <c r="C974">
+        <v>0</v>
+      </c>
+      <c r="D974">
+        <v>0</v>
+      </c>
+      <c r="E974">
+        <v>18</v>
+      </c>
+      <c r="F974">
+        <v>450</v>
+      </c>
+      <c r="G974">
+        <v>1</v>
+      </c>
+      <c r="H974">
+        <v>15</v>
+      </c>
+      <c r="I974">
+        <v>2</v>
+      </c>
+      <c r="J974">
+        <v>50</v>
+      </c>
+      <c r="K974">
+        <v>2</v>
+      </c>
+      <c r="L974">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="975" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A975" s="1">
+        <v>46137</v>
+      </c>
+      <c r="B975" t="s">
+        <v>2</v>
+      </c>
+      <c r="C975">
+        <v>0</v>
+      </c>
+      <c r="D975">
+        <v>0</v>
+      </c>
+      <c r="E975">
+        <v>5</v>
+      </c>
+      <c r="F975">
+        <v>125</v>
+      </c>
+      <c r="G975">
+        <v>0</v>
+      </c>
+      <c r="H975">
+        <v>0</v>
+      </c>
+      <c r="I975">
+        <v>0</v>
+      </c>
+      <c r="J975">
+        <v>0</v>
+      </c>
+      <c r="K975">
+        <v>1</v>
+      </c>
+      <c r="L975">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="976" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A976" s="1">
+        <v>46137</v>
+      </c>
+      <c r="B976" t="s">
+        <v>3</v>
+      </c>
+      <c r="C976">
+        <v>0</v>
+      </c>
+      <c r="D976">
+        <v>0</v>
+      </c>
+      <c r="E976">
+        <v>18</v>
+      </c>
+      <c r="F976">
+        <v>450</v>
+      </c>
+      <c r="G976">
+        <v>1</v>
+      </c>
+      <c r="H976">
+        <v>15</v>
+      </c>
+      <c r="I976">
+        <v>0</v>
+      </c>
+      <c r="J976">
+        <v>0</v>
+      </c>
+      <c r="K976">
+        <v>1</v>
+      </c>
+      <c r="L976">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="977" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A977" s="1">
+        <v>46138</v>
+      </c>
+      <c r="B977" t="s">
+        <v>2</v>
+      </c>
+      <c r="C977">
+        <v>0</v>
+      </c>
+      <c r="D977">
+        <v>0</v>
+      </c>
+      <c r="E977">
+        <v>8</v>
+      </c>
+      <c r="F977">
+        <v>200</v>
+      </c>
+      <c r="G977">
+        <v>0</v>
+      </c>
+      <c r="H977">
+        <v>0</v>
+      </c>
+      <c r="I977">
+        <v>0</v>
+      </c>
+      <c r="J977">
+        <v>0</v>
+      </c>
+      <c r="K977">
+        <v>1</v>
+      </c>
+      <c r="L977">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="978" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A978" s="1">
+        <v>46138</v>
+      </c>
+      <c r="B978" t="s">
+        <v>3</v>
+      </c>
+      <c r="C978">
+        <v>0</v>
+      </c>
+      <c r="D978">
+        <v>0</v>
+      </c>
+      <c r="E978">
+        <v>18</v>
+      </c>
+      <c r="F978">
+        <v>450</v>
+      </c>
+      <c r="G978">
+        <v>0</v>
+      </c>
+      <c r="H978">
+        <v>0</v>
+      </c>
+      <c r="I978">
+        <v>1</v>
+      </c>
+      <c r="J978">
+        <v>25</v>
+      </c>
+      <c r="K978">
+        <v>3</v>
+      </c>
+      <c r="L978">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="979" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A979" s="1">
+        <v>46139</v>
+      </c>
+      <c r="B979" t="s">
+        <v>2</v>
+      </c>
+      <c r="C979">
+        <v>0</v>
+      </c>
+      <c r="D979">
+        <v>0</v>
+      </c>
+      <c r="E979">
+        <v>5</v>
+      </c>
+      <c r="F979">
+        <v>125</v>
+      </c>
+      <c r="G979">
+        <v>0</v>
+      </c>
+      <c r="H979">
+        <v>0</v>
+      </c>
+      <c r="I979">
+        <v>0</v>
+      </c>
+      <c r="J979">
+        <v>0</v>
+      </c>
+      <c r="K979">
+        <v>1</v>
+      </c>
+      <c r="L979">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="980" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A980" s="1">
+        <v>46139</v>
+      </c>
+      <c r="B980" t="s">
+        <v>3</v>
+      </c>
+      <c r="C980">
+        <v>2</v>
+      </c>
+      <c r="D980">
+        <v>50</v>
+      </c>
+      <c r="E980">
+        <v>19</v>
+      </c>
+      <c r="F980">
+        <v>475</v>
+      </c>
+      <c r="G980">
+        <v>0</v>
+      </c>
+      <c r="H980">
+        <v>0</v>
+      </c>
+      <c r="I980">
+        <v>0</v>
+      </c>
+      <c r="J980">
+        <v>0</v>
+      </c>
+      <c r="K980">
+        <v>2</v>
+      </c>
+      <c r="L980">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="981" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A981" s="1">
+        <v>46140</v>
+      </c>
+      <c r="B981" t="s">
+        <v>2</v>
+      </c>
+      <c r="C981">
+        <v>0</v>
+      </c>
+      <c r="D981">
+        <v>0</v>
+      </c>
+      <c r="E981">
+        <v>7</v>
+      </c>
+      <c r="F981">
+        <v>175</v>
+      </c>
+      <c r="G981">
+        <v>0</v>
+      </c>
+      <c r="H981">
+        <v>0</v>
+      </c>
+      <c r="I981">
+        <v>0</v>
+      </c>
+      <c r="J981">
+        <v>0</v>
+      </c>
+      <c r="K981">
+        <v>0</v>
+      </c>
+      <c r="L981">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="982" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A982" s="1">
+        <v>46140</v>
+      </c>
+      <c r="B982" t="s">
+        <v>3</v>
+      </c>
+      <c r="C982">
+        <v>1</v>
+      </c>
+      <c r="D982">
+        <v>25</v>
+      </c>
+      <c r="E982">
+        <v>21</v>
+      </c>
+      <c r="F982">
+        <v>525</v>
+      </c>
+      <c r="G982">
+        <v>0</v>
+      </c>
+      <c r="H982">
+        <v>0</v>
+      </c>
+      <c r="I982">
+        <v>3</v>
+      </c>
+      <c r="J982">
+        <v>75</v>
+      </c>
+      <c r="K982">
+        <v>3</v>
+      </c>
+      <c r="L982">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="983" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A983" s="1">
+        <v>46141</v>
+      </c>
+      <c r="B983" t="s">
+        <v>2</v>
+      </c>
+      <c r="C983">
+        <v>0</v>
+      </c>
+      <c r="D983">
+        <v>0</v>
+      </c>
+      <c r="E983">
+        <v>5</v>
+      </c>
+      <c r="F983">
+        <v>125</v>
+      </c>
+      <c r="G983">
+        <v>0</v>
+      </c>
+      <c r="H983">
+        <v>0</v>
+      </c>
+      <c r="I983">
+        <v>0</v>
+      </c>
+      <c r="J983">
+        <v>0</v>
+      </c>
+      <c r="K983">
+        <v>0</v>
+      </c>
+      <c r="L983">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="984" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A984" s="1">
+        <v>46141</v>
+      </c>
+      <c r="B984" t="s">
+        <v>3</v>
+      </c>
+      <c r="C984">
+        <v>0</v>
+      </c>
+      <c r="D984">
+        <v>0</v>
+      </c>
+      <c r="E984">
+        <v>16</v>
+      </c>
+      <c r="F984">
+        <v>400</v>
+      </c>
+      <c r="G984">
+        <v>0</v>
+      </c>
+      <c r="H984">
+        <v>0</v>
+      </c>
+      <c r="I984">
+        <v>1</v>
+      </c>
+      <c r="J984">
+        <v>25</v>
+      </c>
+      <c r="K984">
+        <v>2</v>
+      </c>
+      <c r="L984">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="985" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A985" s="1">
+        <v>46142</v>
+      </c>
+      <c r="B985" t="s">
+        <v>2</v>
+      </c>
+      <c r="C985">
+        <v>0</v>
+      </c>
+      <c r="D985">
+        <v>0</v>
+      </c>
+      <c r="E985">
+        <v>7</v>
+      </c>
+      <c r="F985">
+        <v>175</v>
+      </c>
+      <c r="G985">
+        <v>0</v>
+      </c>
+      <c r="H985">
+        <v>0</v>
+      </c>
+      <c r="I985">
+        <v>0</v>
+      </c>
+      <c r="J985">
+        <v>0</v>
+      </c>
+      <c r="K985">
+        <v>1</v>
+      </c>
+      <c r="L985">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="986" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A986" s="1">
+        <v>46142</v>
+      </c>
+      <c r="B986" t="s">
+        <v>3</v>
+      </c>
+      <c r="C986">
+        <v>0</v>
+      </c>
+      <c r="D986">
+        <v>0</v>
+      </c>
+      <c r="E986">
+        <v>18</v>
+      </c>
+      <c r="F986">
+        <v>450</v>
+      </c>
+      <c r="G986">
+        <v>0</v>
+      </c>
+      <c r="H986">
+        <v>0</v>
+      </c>
+      <c r="I986">
+        <v>1</v>
+      </c>
+      <c r="J986">
+        <v>25</v>
+      </c>
+      <c r="K986">
+        <v>2</v>
+      </c>
+      <c r="L986">
+        <v>50</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/dados/BD_Bombonas.xlsx
+++ b/dados/BD_Bombonas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupomateus-my.sharepoint.com/personal/hamilton_pires_grupomateus_com/Documents/hamilton/Consultoria/Lidiane/2026/app_bombonas/dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="210" documentId="8_{40E215D4-4623-41EB-B246-4B63951E0A13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD25099F-61A1-4F53-81B3-FDEBE2665E6C}"/>
+  <xr:revisionPtr revIDLastSave="215" documentId="8_{40E215D4-4623-41EB-B246-4B63951E0A13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{340A8610-5EA5-4A6A-BAB3-C013E52339F7}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{9588DCE0-F8D9-46B8-8782-90EC7820DC70}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="997" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1060" uniqueCount="15">
   <si>
     <t>DATA</t>
   </si>
@@ -81,6 +81,9 @@
   </si>
   <si>
     <t>PESO COLCHOES</t>
+  </si>
+  <si>
+    <t>31/04/2026</t>
   </si>
 </sst>
 </file>
@@ -145,10 +148,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -471,7 +470,7 @@
   <sheetPr>
     <tabColor theme="6" tint="0.39997558519241921"/>
   </sheetPr>
-  <dimension ref="A1:L986"/>
+  <dimension ref="A1:L1048"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
@@ -37941,6 +37940,2362 @@
         <v>50</v>
       </c>
     </row>
+    <row r="987" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A987" s="1">
+        <v>46143</v>
+      </c>
+      <c r="B987" t="s">
+        <v>2</v>
+      </c>
+      <c r="C987">
+        <v>0</v>
+      </c>
+      <c r="D987">
+        <v>0</v>
+      </c>
+      <c r="E987">
+        <v>6</v>
+      </c>
+      <c r="F987">
+        <v>150</v>
+      </c>
+      <c r="G987">
+        <v>0</v>
+      </c>
+      <c r="H987">
+        <v>0</v>
+      </c>
+      <c r="I987">
+        <v>0</v>
+      </c>
+      <c r="J987">
+        <v>0</v>
+      </c>
+      <c r="K987">
+        <v>0</v>
+      </c>
+      <c r="L987">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="988" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A988" s="1">
+        <v>46143</v>
+      </c>
+      <c r="B988" t="s">
+        <v>3</v>
+      </c>
+      <c r="C988">
+        <v>0</v>
+      </c>
+      <c r="D988">
+        <v>0</v>
+      </c>
+      <c r="E988">
+        <v>19</v>
+      </c>
+      <c r="F988">
+        <v>475</v>
+      </c>
+      <c r="G988">
+        <v>1</v>
+      </c>
+      <c r="H988">
+        <v>15</v>
+      </c>
+      <c r="I988">
+        <v>1</v>
+      </c>
+      <c r="J988">
+        <v>25</v>
+      </c>
+      <c r="K988">
+        <v>2</v>
+      </c>
+      <c r="L988">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="989" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A989" s="1">
+        <v>46144</v>
+      </c>
+      <c r="B989" t="s">
+        <v>2</v>
+      </c>
+      <c r="C989">
+        <v>0</v>
+      </c>
+      <c r="D989">
+        <v>0</v>
+      </c>
+      <c r="E989">
+        <v>6</v>
+      </c>
+      <c r="F989">
+        <v>150</v>
+      </c>
+      <c r="G989">
+        <v>0</v>
+      </c>
+      <c r="H989">
+        <v>0</v>
+      </c>
+      <c r="I989">
+        <v>0</v>
+      </c>
+      <c r="J989">
+        <v>0</v>
+      </c>
+      <c r="K989">
+        <v>1</v>
+      </c>
+      <c r="L989">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="990" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A990" s="1">
+        <v>46144</v>
+      </c>
+      <c r="B990" t="s">
+        <v>3</v>
+      </c>
+      <c r="C990">
+        <v>0</v>
+      </c>
+      <c r="D990">
+        <v>0</v>
+      </c>
+      <c r="E990">
+        <v>18</v>
+      </c>
+      <c r="F990">
+        <v>450</v>
+      </c>
+      <c r="G990">
+        <v>0</v>
+      </c>
+      <c r="H990">
+        <v>0</v>
+      </c>
+      <c r="I990">
+        <v>2</v>
+      </c>
+      <c r="J990">
+        <v>50</v>
+      </c>
+      <c r="K990">
+        <v>2</v>
+      </c>
+      <c r="L990">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="991" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A991" s="1">
+        <v>46145</v>
+      </c>
+      <c r="B991" t="s">
+        <v>2</v>
+      </c>
+      <c r="C991">
+        <v>0</v>
+      </c>
+      <c r="D991">
+        <v>0</v>
+      </c>
+      <c r="E991">
+        <v>5</v>
+      </c>
+      <c r="F991">
+        <v>125</v>
+      </c>
+      <c r="G991">
+        <v>0</v>
+      </c>
+      <c r="H991">
+        <v>0</v>
+      </c>
+      <c r="I991">
+        <v>0</v>
+      </c>
+      <c r="J991">
+        <v>0</v>
+      </c>
+      <c r="K991">
+        <v>1</v>
+      </c>
+      <c r="L991">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="992" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A992" s="1">
+        <v>46145</v>
+      </c>
+      <c r="B992" t="s">
+        <v>3</v>
+      </c>
+      <c r="C992">
+        <v>0</v>
+      </c>
+      <c r="D992">
+        <v>0</v>
+      </c>
+      <c r="E992">
+        <v>16</v>
+      </c>
+      <c r="F992">
+        <v>400</v>
+      </c>
+      <c r="G992">
+        <v>0</v>
+      </c>
+      <c r="H992">
+        <v>0</v>
+      </c>
+      <c r="I992">
+        <v>1</v>
+      </c>
+      <c r="J992">
+        <v>25</v>
+      </c>
+      <c r="K992">
+        <v>3</v>
+      </c>
+      <c r="L992">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="993" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A993" s="1">
+        <v>46146</v>
+      </c>
+      <c r="B993" t="s">
+        <v>2</v>
+      </c>
+      <c r="C993">
+        <v>0</v>
+      </c>
+      <c r="D993">
+        <v>0</v>
+      </c>
+      <c r="E993">
+        <v>6</v>
+      </c>
+      <c r="F993">
+        <v>150</v>
+      </c>
+      <c r="G993">
+        <v>0</v>
+      </c>
+      <c r="H993">
+        <v>0</v>
+      </c>
+      <c r="I993">
+        <v>0</v>
+      </c>
+      <c r="J993">
+        <v>0</v>
+      </c>
+      <c r="K993">
+        <v>0</v>
+      </c>
+      <c r="L993">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="994" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A994" s="1">
+        <v>46146</v>
+      </c>
+      <c r="B994" t="s">
+        <v>3</v>
+      </c>
+      <c r="C994">
+        <v>0</v>
+      </c>
+      <c r="D994">
+        <v>0</v>
+      </c>
+      <c r="E994">
+        <v>17</v>
+      </c>
+      <c r="F994">
+        <v>425</v>
+      </c>
+      <c r="G994">
+        <v>0</v>
+      </c>
+      <c r="H994">
+        <v>0</v>
+      </c>
+      <c r="I994">
+        <v>3</v>
+      </c>
+      <c r="J994">
+        <v>75</v>
+      </c>
+      <c r="K994">
+        <v>2</v>
+      </c>
+      <c r="L994">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="995" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A995" s="1">
+        <v>46147</v>
+      </c>
+      <c r="B995" t="s">
+        <v>2</v>
+      </c>
+      <c r="C995">
+        <v>0</v>
+      </c>
+      <c r="D995">
+        <v>0</v>
+      </c>
+      <c r="E995">
+        <v>6</v>
+      </c>
+      <c r="F995">
+        <v>150</v>
+      </c>
+      <c r="G995">
+        <v>0</v>
+      </c>
+      <c r="H995">
+        <v>0</v>
+      </c>
+      <c r="I995">
+        <v>0</v>
+      </c>
+      <c r="J995">
+        <v>0</v>
+      </c>
+      <c r="K995">
+        <v>1</v>
+      </c>
+      <c r="L995">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="996" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A996" s="1">
+        <v>46147</v>
+      </c>
+      <c r="B996" t="s">
+        <v>3</v>
+      </c>
+      <c r="C996">
+        <v>0</v>
+      </c>
+      <c r="D996">
+        <v>0</v>
+      </c>
+      <c r="E996">
+        <v>20</v>
+      </c>
+      <c r="F996">
+        <v>500</v>
+      </c>
+      <c r="G996">
+        <v>1</v>
+      </c>
+      <c r="H996">
+        <v>15</v>
+      </c>
+      <c r="I996">
+        <v>0</v>
+      </c>
+      <c r="J996">
+        <v>0</v>
+      </c>
+      <c r="K996">
+        <v>1</v>
+      </c>
+      <c r="L996">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="997" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A997" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B997" t="s">
+        <v>2</v>
+      </c>
+      <c r="C997">
+        <v>0</v>
+      </c>
+      <c r="D997">
+        <v>0</v>
+      </c>
+      <c r="E997">
+        <v>7</v>
+      </c>
+      <c r="F997">
+        <v>175</v>
+      </c>
+      <c r="G997">
+        <v>0</v>
+      </c>
+      <c r="H997">
+        <v>0</v>
+      </c>
+      <c r="I997">
+        <v>0</v>
+      </c>
+      <c r="J997">
+        <v>0</v>
+      </c>
+      <c r="K997">
+        <v>0</v>
+      </c>
+      <c r="L997">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="998" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A998" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B998" t="s">
+        <v>3</v>
+      </c>
+      <c r="C998">
+        <v>0</v>
+      </c>
+      <c r="D998">
+        <v>0</v>
+      </c>
+      <c r="E998">
+        <v>19</v>
+      </c>
+      <c r="F998">
+        <v>475</v>
+      </c>
+      <c r="G998">
+        <v>0</v>
+      </c>
+      <c r="H998">
+        <v>0</v>
+      </c>
+      <c r="I998">
+        <v>2</v>
+      </c>
+      <c r="J998">
+        <v>50</v>
+      </c>
+      <c r="K998">
+        <v>3</v>
+      </c>
+      <c r="L998">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="999" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A999" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B999" t="s">
+        <v>2</v>
+      </c>
+      <c r="C999">
+        <v>0</v>
+      </c>
+      <c r="D999">
+        <v>0</v>
+      </c>
+      <c r="E999">
+        <v>7</v>
+      </c>
+      <c r="F999">
+        <v>175</v>
+      </c>
+      <c r="G999">
+        <v>0</v>
+      </c>
+      <c r="H999">
+        <v>0</v>
+      </c>
+      <c r="I999">
+        <v>0</v>
+      </c>
+      <c r="J999">
+        <v>0</v>
+      </c>
+      <c r="K999">
+        <v>1</v>
+      </c>
+      <c r="L999">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1000" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1000" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B1000" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1000">
+        <v>0</v>
+      </c>
+      <c r="D1000">
+        <v>0</v>
+      </c>
+      <c r="E1000">
+        <v>19</v>
+      </c>
+      <c r="F1000">
+        <v>475</v>
+      </c>
+      <c r="G1000">
+        <v>0</v>
+      </c>
+      <c r="H1000">
+        <v>0</v>
+      </c>
+      <c r="I1000">
+        <v>1</v>
+      </c>
+      <c r="J1000">
+        <v>25</v>
+      </c>
+      <c r="K1000">
+        <v>1</v>
+      </c>
+      <c r="L1000">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1001" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1001" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B1001" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1001">
+        <v>0</v>
+      </c>
+      <c r="D1001">
+        <v>0</v>
+      </c>
+      <c r="E1001">
+        <v>6</v>
+      </c>
+      <c r="F1001">
+        <v>150</v>
+      </c>
+      <c r="G1001">
+        <v>0</v>
+      </c>
+      <c r="H1001">
+        <v>0</v>
+      </c>
+      <c r="I1001">
+        <v>0</v>
+      </c>
+      <c r="J1001">
+        <v>0</v>
+      </c>
+      <c r="K1001">
+        <v>1</v>
+      </c>
+      <c r="L1001">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1002" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1002" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B1002" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1002">
+        <v>0</v>
+      </c>
+      <c r="D1002">
+        <v>0</v>
+      </c>
+      <c r="E1002">
+        <v>19</v>
+      </c>
+      <c r="F1002">
+        <v>475</v>
+      </c>
+      <c r="G1002">
+        <v>1</v>
+      </c>
+      <c r="H1002">
+        <v>15</v>
+      </c>
+      <c r="I1002">
+        <v>2</v>
+      </c>
+      <c r="J1002">
+        <v>50</v>
+      </c>
+      <c r="K1002">
+        <v>2</v>
+      </c>
+      <c r="L1002">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1003" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1003" s="1">
+        <v>46151</v>
+      </c>
+      <c r="B1003" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1003">
+        <v>0</v>
+      </c>
+      <c r="D1003">
+        <v>0</v>
+      </c>
+      <c r="E1003">
+        <v>6</v>
+      </c>
+      <c r="F1003">
+        <v>150</v>
+      </c>
+      <c r="G1003">
+        <v>0</v>
+      </c>
+      <c r="H1003">
+        <v>0</v>
+      </c>
+      <c r="I1003">
+        <v>0</v>
+      </c>
+      <c r="J1003">
+        <v>0</v>
+      </c>
+      <c r="K1003">
+        <v>1</v>
+      </c>
+      <c r="L1003">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1004" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1004" s="1">
+        <v>46151</v>
+      </c>
+      <c r="B1004" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1004">
+        <v>0</v>
+      </c>
+      <c r="D1004">
+        <v>0</v>
+      </c>
+      <c r="E1004">
+        <v>18</v>
+      </c>
+      <c r="F1004">
+        <v>450</v>
+      </c>
+      <c r="G1004">
+        <v>0</v>
+      </c>
+      <c r="H1004">
+        <v>0</v>
+      </c>
+      <c r="I1004">
+        <v>1</v>
+      </c>
+      <c r="J1004">
+        <v>25</v>
+      </c>
+      <c r="K1004">
+        <v>2</v>
+      </c>
+      <c r="L1004">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1005" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1005" s="1">
+        <v>46152</v>
+      </c>
+      <c r="B1005" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1005">
+        <v>0</v>
+      </c>
+      <c r="D1005">
+        <v>0</v>
+      </c>
+      <c r="E1005">
+        <v>6</v>
+      </c>
+      <c r="F1005">
+        <v>150</v>
+      </c>
+      <c r="G1005">
+        <v>0</v>
+      </c>
+      <c r="H1005">
+        <v>0</v>
+      </c>
+      <c r="I1005">
+        <v>0</v>
+      </c>
+      <c r="J1005">
+        <v>0</v>
+      </c>
+      <c r="K1005">
+        <v>0</v>
+      </c>
+      <c r="L1005">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1006" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1006" s="1">
+        <v>46152</v>
+      </c>
+      <c r="B1006" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1006">
+        <v>0</v>
+      </c>
+      <c r="D1006">
+        <v>0</v>
+      </c>
+      <c r="E1006">
+        <v>19</v>
+      </c>
+      <c r="F1006">
+        <v>475</v>
+      </c>
+      <c r="G1006">
+        <v>0</v>
+      </c>
+      <c r="H1006">
+        <v>0</v>
+      </c>
+      <c r="I1006">
+        <v>1</v>
+      </c>
+      <c r="J1006">
+        <v>25</v>
+      </c>
+      <c r="K1006">
+        <v>1</v>
+      </c>
+      <c r="L1006">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1007" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1007" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B1007" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1007">
+        <v>0</v>
+      </c>
+      <c r="D1007">
+        <v>0</v>
+      </c>
+      <c r="E1007">
+        <v>5</v>
+      </c>
+      <c r="F1007">
+        <v>125</v>
+      </c>
+      <c r="G1007">
+        <v>0</v>
+      </c>
+      <c r="H1007">
+        <v>0</v>
+      </c>
+      <c r="I1007">
+        <v>0</v>
+      </c>
+      <c r="J1007">
+        <v>0</v>
+      </c>
+      <c r="K1007">
+        <v>1</v>
+      </c>
+      <c r="L1007">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1008" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1008" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B1008" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1008">
+        <v>0</v>
+      </c>
+      <c r="D1008">
+        <v>0</v>
+      </c>
+      <c r="E1008">
+        <v>17</v>
+      </c>
+      <c r="F1008">
+        <v>425</v>
+      </c>
+      <c r="G1008">
+        <v>0</v>
+      </c>
+      <c r="H1008">
+        <v>0</v>
+      </c>
+      <c r="I1008">
+        <v>0</v>
+      </c>
+      <c r="J1008">
+        <v>0</v>
+      </c>
+      <c r="K1008">
+        <v>2</v>
+      </c>
+      <c r="L1008">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1009" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1009" s="1">
+        <v>46154</v>
+      </c>
+      <c r="B1009" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1009">
+        <v>0</v>
+      </c>
+      <c r="D1009">
+        <v>0</v>
+      </c>
+      <c r="E1009">
+        <v>6</v>
+      </c>
+      <c r="F1009">
+        <v>150</v>
+      </c>
+      <c r="G1009">
+        <v>0</v>
+      </c>
+      <c r="H1009">
+        <v>0</v>
+      </c>
+      <c r="I1009">
+        <v>0</v>
+      </c>
+      <c r="J1009">
+        <v>0</v>
+      </c>
+      <c r="K1009">
+        <v>0</v>
+      </c>
+      <c r="L1009">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1010" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1010" s="1">
+        <v>46154</v>
+      </c>
+      <c r="B1010" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1010">
+        <v>2</v>
+      </c>
+      <c r="D1010">
+        <v>50</v>
+      </c>
+      <c r="E1010">
+        <v>20</v>
+      </c>
+      <c r="F1010">
+        <v>500</v>
+      </c>
+      <c r="G1010">
+        <v>0</v>
+      </c>
+      <c r="H1010">
+        <v>0</v>
+      </c>
+      <c r="I1010">
+        <v>2</v>
+      </c>
+      <c r="J1010">
+        <v>50</v>
+      </c>
+      <c r="K1010">
+        <v>2</v>
+      </c>
+      <c r="L1010">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1011" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1011" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B1011" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1011">
+        <v>0</v>
+      </c>
+      <c r="D1011">
+        <v>0</v>
+      </c>
+      <c r="E1011">
+        <v>6</v>
+      </c>
+      <c r="F1011">
+        <v>150</v>
+      </c>
+      <c r="G1011">
+        <v>0</v>
+      </c>
+      <c r="H1011">
+        <v>0</v>
+      </c>
+      <c r="I1011">
+        <v>0</v>
+      </c>
+      <c r="J1011">
+        <v>0</v>
+      </c>
+      <c r="K1011">
+        <v>0</v>
+      </c>
+      <c r="L1011">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1012" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1012" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B1012" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1012">
+        <v>2</v>
+      </c>
+      <c r="D1012">
+        <v>50</v>
+      </c>
+      <c r="E1012">
+        <v>20</v>
+      </c>
+      <c r="F1012">
+        <v>500</v>
+      </c>
+      <c r="G1012">
+        <v>0</v>
+      </c>
+      <c r="H1012">
+        <v>0</v>
+      </c>
+      <c r="I1012">
+        <v>2</v>
+      </c>
+      <c r="J1012">
+        <v>50</v>
+      </c>
+      <c r="K1012">
+        <v>2</v>
+      </c>
+      <c r="L1012">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1013" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1013" s="1">
+        <v>46156</v>
+      </c>
+      <c r="B1013" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1013">
+        <v>0</v>
+      </c>
+      <c r="D1013">
+        <v>0</v>
+      </c>
+      <c r="E1013">
+        <v>10</v>
+      </c>
+      <c r="F1013">
+        <v>250</v>
+      </c>
+      <c r="G1013">
+        <v>0</v>
+      </c>
+      <c r="H1013">
+        <v>0</v>
+      </c>
+      <c r="I1013">
+        <v>0</v>
+      </c>
+      <c r="J1013">
+        <v>0</v>
+      </c>
+      <c r="K1013">
+        <v>1</v>
+      </c>
+      <c r="L1013">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1014" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1014" s="1">
+        <v>46156</v>
+      </c>
+      <c r="B1014" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1014">
+        <v>0</v>
+      </c>
+      <c r="D1014">
+        <v>0</v>
+      </c>
+      <c r="E1014">
+        <v>21</v>
+      </c>
+      <c r="F1014">
+        <v>525</v>
+      </c>
+      <c r="G1014">
+        <v>0</v>
+      </c>
+      <c r="H1014">
+        <v>0</v>
+      </c>
+      <c r="I1014">
+        <v>0</v>
+      </c>
+      <c r="J1014">
+        <v>0</v>
+      </c>
+      <c r="K1014">
+        <v>1</v>
+      </c>
+      <c r="L1014">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1015" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1015" s="1">
+        <v>46157</v>
+      </c>
+      <c r="B1015" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1015">
+        <v>0</v>
+      </c>
+      <c r="D1015">
+        <v>0</v>
+      </c>
+      <c r="E1015">
+        <v>7</v>
+      </c>
+      <c r="F1015">
+        <v>175</v>
+      </c>
+      <c r="G1015">
+        <v>0</v>
+      </c>
+      <c r="H1015">
+        <v>0</v>
+      </c>
+      <c r="I1015">
+        <v>0</v>
+      </c>
+      <c r="J1015">
+        <v>0</v>
+      </c>
+      <c r="K1015">
+        <v>1</v>
+      </c>
+      <c r="L1015">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1016" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1016" s="1">
+        <v>46157</v>
+      </c>
+      <c r="B1016" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1016">
+        <v>2</v>
+      </c>
+      <c r="D1016">
+        <v>50</v>
+      </c>
+      <c r="E1016">
+        <v>19</v>
+      </c>
+      <c r="F1016">
+        <v>475</v>
+      </c>
+      <c r="G1016">
+        <v>0</v>
+      </c>
+      <c r="H1016">
+        <v>0</v>
+      </c>
+      <c r="I1016">
+        <v>2</v>
+      </c>
+      <c r="J1016">
+        <v>50</v>
+      </c>
+      <c r="K1016">
+        <v>3</v>
+      </c>
+      <c r="L1016">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="1017" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1017" s="1">
+        <v>46158</v>
+      </c>
+      <c r="B1017" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1017">
+        <v>0</v>
+      </c>
+      <c r="D1017">
+        <v>0</v>
+      </c>
+      <c r="E1017">
+        <v>7</v>
+      </c>
+      <c r="F1017">
+        <v>175</v>
+      </c>
+      <c r="G1017">
+        <v>0</v>
+      </c>
+      <c r="H1017">
+        <v>0</v>
+      </c>
+      <c r="I1017">
+        <v>0</v>
+      </c>
+      <c r="J1017">
+        <v>0</v>
+      </c>
+      <c r="K1017">
+        <v>0</v>
+      </c>
+      <c r="L1017">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1018" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1018" s="1">
+        <v>46158</v>
+      </c>
+      <c r="B1018" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1018">
+        <v>0</v>
+      </c>
+      <c r="D1018">
+        <v>0</v>
+      </c>
+      <c r="E1018">
+        <v>20</v>
+      </c>
+      <c r="F1018">
+        <v>500</v>
+      </c>
+      <c r="G1018">
+        <v>1</v>
+      </c>
+      <c r="H1018">
+        <v>15</v>
+      </c>
+      <c r="I1018">
+        <v>2</v>
+      </c>
+      <c r="J1018">
+        <v>50</v>
+      </c>
+      <c r="K1018">
+        <v>2</v>
+      </c>
+      <c r="L1018">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1019" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1019" s="1">
+        <v>46159</v>
+      </c>
+      <c r="B1019" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1019">
+        <v>0</v>
+      </c>
+      <c r="D1019">
+        <v>0</v>
+      </c>
+      <c r="E1019">
+        <v>8</v>
+      </c>
+      <c r="F1019">
+        <v>200</v>
+      </c>
+      <c r="G1019">
+        <v>0</v>
+      </c>
+      <c r="H1019">
+        <v>0</v>
+      </c>
+      <c r="I1019">
+        <v>0</v>
+      </c>
+      <c r="J1019">
+        <v>0</v>
+      </c>
+      <c r="K1019">
+        <v>1</v>
+      </c>
+      <c r="L1019">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1020" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1020" s="1">
+        <v>46159</v>
+      </c>
+      <c r="B1020" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1020">
+        <v>0</v>
+      </c>
+      <c r="D1020">
+        <v>0</v>
+      </c>
+      <c r="E1020">
+        <v>24</v>
+      </c>
+      <c r="F1020">
+        <v>600</v>
+      </c>
+      <c r="G1020">
+        <v>0</v>
+      </c>
+      <c r="H1020">
+        <v>0</v>
+      </c>
+      <c r="I1020">
+        <v>0</v>
+      </c>
+      <c r="J1020">
+        <v>0</v>
+      </c>
+      <c r="K1020">
+        <v>2</v>
+      </c>
+      <c r="L1020">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1021" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1021" s="1">
+        <v>46160</v>
+      </c>
+      <c r="B1021" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1021">
+        <v>0</v>
+      </c>
+      <c r="D1021">
+        <v>0</v>
+      </c>
+      <c r="E1021">
+        <v>8</v>
+      </c>
+      <c r="F1021">
+        <v>200</v>
+      </c>
+      <c r="G1021">
+        <v>0</v>
+      </c>
+      <c r="H1021">
+        <v>0</v>
+      </c>
+      <c r="I1021">
+        <v>0</v>
+      </c>
+      <c r="J1021">
+        <v>0</v>
+      </c>
+      <c r="K1021">
+        <v>0</v>
+      </c>
+      <c r="L1021">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1022" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1022" s="1">
+        <v>46160</v>
+      </c>
+      <c r="B1022" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1022">
+        <v>0</v>
+      </c>
+      <c r="D1022">
+        <v>0</v>
+      </c>
+      <c r="E1022">
+        <v>19</v>
+      </c>
+      <c r="F1022">
+        <v>475</v>
+      </c>
+      <c r="G1022">
+        <v>0</v>
+      </c>
+      <c r="H1022">
+        <v>0</v>
+      </c>
+      <c r="I1022">
+        <v>2</v>
+      </c>
+      <c r="J1022">
+        <v>50</v>
+      </c>
+      <c r="K1022">
+        <v>1</v>
+      </c>
+      <c r="L1022">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1023" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1023" s="1">
+        <v>46161</v>
+      </c>
+      <c r="B1023" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1023">
+        <v>0</v>
+      </c>
+      <c r="D1023">
+        <v>0</v>
+      </c>
+      <c r="E1023">
+        <v>6</v>
+      </c>
+      <c r="F1023">
+        <v>150</v>
+      </c>
+      <c r="G1023">
+        <v>0</v>
+      </c>
+      <c r="H1023">
+        <v>0</v>
+      </c>
+      <c r="I1023">
+        <v>0</v>
+      </c>
+      <c r="J1023">
+        <v>0</v>
+      </c>
+      <c r="K1023">
+        <v>1</v>
+      </c>
+      <c r="L1023">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1024" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1024" s="1">
+        <v>46161</v>
+      </c>
+      <c r="B1024" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1024">
+        <v>2</v>
+      </c>
+      <c r="D1024">
+        <v>50</v>
+      </c>
+      <c r="E1024">
+        <v>20</v>
+      </c>
+      <c r="F1024">
+        <v>500</v>
+      </c>
+      <c r="G1024">
+        <v>0</v>
+      </c>
+      <c r="H1024">
+        <v>0</v>
+      </c>
+      <c r="I1024">
+        <v>1</v>
+      </c>
+      <c r="J1024">
+        <v>25</v>
+      </c>
+      <c r="K1024">
+        <v>2</v>
+      </c>
+      <c r="L1024">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1025" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1025" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B1025" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1025">
+        <v>0</v>
+      </c>
+      <c r="D1025">
+        <v>0</v>
+      </c>
+      <c r="E1025">
+        <v>8</v>
+      </c>
+      <c r="F1025">
+        <v>200</v>
+      </c>
+      <c r="G1025">
+        <v>0</v>
+      </c>
+      <c r="H1025">
+        <v>0</v>
+      </c>
+      <c r="I1025">
+        <v>0</v>
+      </c>
+      <c r="J1025">
+        <v>0</v>
+      </c>
+      <c r="K1025">
+        <v>1</v>
+      </c>
+      <c r="L1025">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1026" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1026" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B1026" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1026">
+        <v>2</v>
+      </c>
+      <c r="D1026">
+        <v>50</v>
+      </c>
+      <c r="E1026">
+        <v>19</v>
+      </c>
+      <c r="F1026">
+        <v>475</v>
+      </c>
+      <c r="G1026">
+        <v>0</v>
+      </c>
+      <c r="H1026">
+        <v>0</v>
+      </c>
+      <c r="I1026">
+        <v>1</v>
+      </c>
+      <c r="J1026">
+        <v>25</v>
+      </c>
+      <c r="K1026">
+        <v>2</v>
+      </c>
+      <c r="L1026">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1027" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1027" s="1">
+        <v>46163</v>
+      </c>
+      <c r="B1027" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1027">
+        <v>0</v>
+      </c>
+      <c r="D1027">
+        <v>0</v>
+      </c>
+      <c r="E1027">
+        <v>7</v>
+      </c>
+      <c r="F1027">
+        <v>175</v>
+      </c>
+      <c r="G1027">
+        <v>0</v>
+      </c>
+      <c r="H1027">
+        <v>0</v>
+      </c>
+      <c r="I1027">
+        <v>0</v>
+      </c>
+      <c r="J1027">
+        <v>0</v>
+      </c>
+      <c r="K1027">
+        <v>0</v>
+      </c>
+      <c r="L1027">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1028" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1028" s="1">
+        <v>46163</v>
+      </c>
+      <c r="B1028" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1028">
+        <v>0</v>
+      </c>
+      <c r="D1028">
+        <v>0</v>
+      </c>
+      <c r="E1028">
+        <v>21</v>
+      </c>
+      <c r="F1028">
+        <v>525</v>
+      </c>
+      <c r="G1028">
+        <v>0</v>
+      </c>
+      <c r="H1028">
+        <v>0</v>
+      </c>
+      <c r="I1028">
+        <v>2</v>
+      </c>
+      <c r="J1028">
+        <v>50</v>
+      </c>
+      <c r="K1028">
+        <v>1</v>
+      </c>
+      <c r="L1028">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1029" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1029" s="1">
+        <v>46164</v>
+      </c>
+      <c r="B1029" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1029">
+        <v>0</v>
+      </c>
+      <c r="D1029">
+        <v>0</v>
+      </c>
+      <c r="E1029">
+        <v>8</v>
+      </c>
+      <c r="F1029">
+        <v>200</v>
+      </c>
+      <c r="G1029">
+        <v>0</v>
+      </c>
+      <c r="H1029">
+        <v>0</v>
+      </c>
+      <c r="I1029">
+        <v>0</v>
+      </c>
+      <c r="J1029">
+        <v>0</v>
+      </c>
+      <c r="K1029">
+        <v>1</v>
+      </c>
+      <c r="L1029">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1030" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1030" s="1">
+        <v>46164</v>
+      </c>
+      <c r="B1030" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1030">
+        <v>0</v>
+      </c>
+      <c r="D1030">
+        <v>0</v>
+      </c>
+      <c r="E1030">
+        <v>20</v>
+      </c>
+      <c r="F1030">
+        <v>500</v>
+      </c>
+      <c r="G1030">
+        <v>0</v>
+      </c>
+      <c r="H1030">
+        <v>0</v>
+      </c>
+      <c r="I1030">
+        <v>2</v>
+      </c>
+      <c r="J1030">
+        <v>50</v>
+      </c>
+      <c r="K1030">
+        <v>2</v>
+      </c>
+      <c r="L1030">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1031" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1031" s="1">
+        <v>46165</v>
+      </c>
+      <c r="B1031" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1031">
+        <v>0</v>
+      </c>
+      <c r="D1031">
+        <v>0</v>
+      </c>
+      <c r="E1031">
+        <v>7</v>
+      </c>
+      <c r="F1031">
+        <v>175</v>
+      </c>
+      <c r="G1031">
+        <v>0</v>
+      </c>
+      <c r="H1031">
+        <v>0</v>
+      </c>
+      <c r="I1031">
+        <v>0</v>
+      </c>
+      <c r="J1031">
+        <v>0</v>
+      </c>
+      <c r="K1031">
+        <v>1</v>
+      </c>
+      <c r="L1031">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1032" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1032" s="1">
+        <v>46165</v>
+      </c>
+      <c r="B1032" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1032">
+        <v>0</v>
+      </c>
+      <c r="D1032">
+        <v>0</v>
+      </c>
+      <c r="E1032">
+        <v>18</v>
+      </c>
+      <c r="F1032">
+        <v>450</v>
+      </c>
+      <c r="G1032">
+        <v>0</v>
+      </c>
+      <c r="H1032">
+        <v>0</v>
+      </c>
+      <c r="I1032">
+        <v>1</v>
+      </c>
+      <c r="J1032">
+        <v>25</v>
+      </c>
+      <c r="K1032">
+        <v>2</v>
+      </c>
+      <c r="L1032">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1033" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1033" s="1">
+        <v>46166</v>
+      </c>
+      <c r="B1033" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1033">
+        <v>0</v>
+      </c>
+      <c r="D1033">
+        <v>0</v>
+      </c>
+      <c r="E1033">
+        <v>6</v>
+      </c>
+      <c r="F1033">
+        <v>150</v>
+      </c>
+      <c r="G1033">
+        <v>0</v>
+      </c>
+      <c r="H1033">
+        <v>0</v>
+      </c>
+      <c r="I1033">
+        <v>0</v>
+      </c>
+      <c r="J1033">
+        <v>0</v>
+      </c>
+      <c r="K1033">
+        <v>1</v>
+      </c>
+      <c r="L1033">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1034" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1034" s="1">
+        <v>46166</v>
+      </c>
+      <c r="B1034" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1034">
+        <v>0</v>
+      </c>
+      <c r="D1034">
+        <v>0</v>
+      </c>
+      <c r="E1034">
+        <v>18</v>
+      </c>
+      <c r="F1034">
+        <v>450</v>
+      </c>
+      <c r="G1034">
+        <v>0</v>
+      </c>
+      <c r="H1034">
+        <v>0</v>
+      </c>
+      <c r="I1034">
+        <v>0</v>
+      </c>
+      <c r="J1034">
+        <v>0</v>
+      </c>
+      <c r="K1034">
+        <v>2</v>
+      </c>
+      <c r="L1034">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1035" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1035" s="1">
+        <v>46167</v>
+      </c>
+      <c r="B1035" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1035">
+        <v>0</v>
+      </c>
+      <c r="D1035">
+        <v>0</v>
+      </c>
+      <c r="E1035">
+        <v>7</v>
+      </c>
+      <c r="F1035">
+        <v>175</v>
+      </c>
+      <c r="G1035">
+        <v>0</v>
+      </c>
+      <c r="H1035">
+        <v>0</v>
+      </c>
+      <c r="I1035">
+        <v>0</v>
+      </c>
+      <c r="J1035">
+        <v>0</v>
+      </c>
+      <c r="K1035">
+        <v>0</v>
+      </c>
+      <c r="L1035">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1036" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1036" s="1">
+        <v>46167</v>
+      </c>
+      <c r="B1036" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1036">
+        <v>0</v>
+      </c>
+      <c r="D1036">
+        <v>0</v>
+      </c>
+      <c r="E1036">
+        <v>20</v>
+      </c>
+      <c r="F1036">
+        <v>500</v>
+      </c>
+      <c r="G1036">
+        <v>0</v>
+      </c>
+      <c r="H1036">
+        <v>0</v>
+      </c>
+      <c r="I1036">
+        <v>2</v>
+      </c>
+      <c r="J1036">
+        <v>50</v>
+      </c>
+      <c r="K1036">
+        <v>2</v>
+      </c>
+      <c r="L1036">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1037" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1037" s="1">
+        <v>46168</v>
+      </c>
+      <c r="B1037" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1037">
+        <v>0</v>
+      </c>
+      <c r="D1037">
+        <v>0</v>
+      </c>
+      <c r="E1037">
+        <v>7</v>
+      </c>
+      <c r="F1037">
+        <v>175</v>
+      </c>
+      <c r="G1037">
+        <v>0</v>
+      </c>
+      <c r="H1037">
+        <v>0</v>
+      </c>
+      <c r="I1037">
+        <v>0</v>
+      </c>
+      <c r="J1037">
+        <v>0</v>
+      </c>
+      <c r="K1037">
+        <v>1</v>
+      </c>
+      <c r="L1037">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1038" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1038" s="1">
+        <v>46168</v>
+      </c>
+      <c r="B1038" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1038">
+        <v>0</v>
+      </c>
+      <c r="D1038">
+        <v>0</v>
+      </c>
+      <c r="E1038">
+        <v>19</v>
+      </c>
+      <c r="F1038">
+        <v>475</v>
+      </c>
+      <c r="G1038">
+        <v>0</v>
+      </c>
+      <c r="H1038">
+        <v>0</v>
+      </c>
+      <c r="I1038">
+        <v>2</v>
+      </c>
+      <c r="J1038">
+        <v>50</v>
+      </c>
+      <c r="K1038">
+        <v>2</v>
+      </c>
+      <c r="L1038">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1039" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1039" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B1039" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1039">
+        <v>0</v>
+      </c>
+      <c r="D1039">
+        <v>0</v>
+      </c>
+      <c r="E1039">
+        <v>8</v>
+      </c>
+      <c r="F1039">
+        <v>200</v>
+      </c>
+      <c r="G1039">
+        <v>0</v>
+      </c>
+      <c r="H1039">
+        <v>0</v>
+      </c>
+      <c r="I1039">
+        <v>0</v>
+      </c>
+      <c r="J1039">
+        <v>0</v>
+      </c>
+      <c r="K1039">
+        <v>0</v>
+      </c>
+      <c r="L1039">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1040" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1040" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B1040" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1040">
+        <v>0</v>
+      </c>
+      <c r="D1040">
+        <v>0</v>
+      </c>
+      <c r="E1040">
+        <v>22</v>
+      </c>
+      <c r="F1040">
+        <v>550</v>
+      </c>
+      <c r="G1040">
+        <v>0</v>
+      </c>
+      <c r="H1040">
+        <v>0</v>
+      </c>
+      <c r="I1040">
+        <v>2</v>
+      </c>
+      <c r="J1040">
+        <v>50</v>
+      </c>
+      <c r="K1040">
+        <v>3</v>
+      </c>
+      <c r="L1040">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="1041" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1041" s="1">
+        <v>46170</v>
+      </c>
+      <c r="B1041" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1041">
+        <v>0</v>
+      </c>
+      <c r="D1041">
+        <v>0</v>
+      </c>
+      <c r="E1041">
+        <v>6</v>
+      </c>
+      <c r="F1041">
+        <v>150</v>
+      </c>
+      <c r="G1041">
+        <v>0</v>
+      </c>
+      <c r="H1041">
+        <v>0</v>
+      </c>
+      <c r="I1041">
+        <v>0</v>
+      </c>
+      <c r="J1041">
+        <v>0</v>
+      </c>
+      <c r="K1041">
+        <v>0</v>
+      </c>
+      <c r="L1041">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1042" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1042" s="1">
+        <v>46170</v>
+      </c>
+      <c r="B1042" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1042">
+        <v>0</v>
+      </c>
+      <c r="D1042">
+        <v>0</v>
+      </c>
+      <c r="E1042">
+        <v>20</v>
+      </c>
+      <c r="F1042">
+        <v>500</v>
+      </c>
+      <c r="G1042">
+        <v>0</v>
+      </c>
+      <c r="H1042">
+        <v>0</v>
+      </c>
+      <c r="I1042">
+        <v>0</v>
+      </c>
+      <c r="J1042">
+        <v>0</v>
+      </c>
+      <c r="K1042">
+        <v>1</v>
+      </c>
+      <c r="L1042">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1043" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1043" s="1">
+        <v>46171</v>
+      </c>
+      <c r="B1043" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1043">
+        <v>0</v>
+      </c>
+      <c r="D1043">
+        <v>0</v>
+      </c>
+      <c r="E1043">
+        <v>6</v>
+      </c>
+      <c r="F1043">
+        <v>150</v>
+      </c>
+      <c r="G1043">
+        <v>0</v>
+      </c>
+      <c r="H1043">
+        <v>0</v>
+      </c>
+      <c r="I1043">
+        <v>0</v>
+      </c>
+      <c r="J1043">
+        <v>0</v>
+      </c>
+      <c r="K1043">
+        <v>1</v>
+      </c>
+      <c r="L1043">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1044" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1044" s="1">
+        <v>46171</v>
+      </c>
+      <c r="B1044" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1044">
+        <v>0</v>
+      </c>
+      <c r="D1044">
+        <v>0</v>
+      </c>
+      <c r="E1044">
+        <v>16</v>
+      </c>
+      <c r="F1044">
+        <v>400</v>
+      </c>
+      <c r="G1044">
+        <v>0</v>
+      </c>
+      <c r="H1044">
+        <v>0</v>
+      </c>
+      <c r="I1044">
+        <v>2</v>
+      </c>
+      <c r="J1044">
+        <v>50</v>
+      </c>
+      <c r="K1044">
+        <v>3</v>
+      </c>
+      <c r="L1044">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="1045" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1045" s="1">
+        <v>46172</v>
+      </c>
+      <c r="B1045" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1045">
+        <v>0</v>
+      </c>
+      <c r="D1045">
+        <v>0</v>
+      </c>
+      <c r="E1045">
+        <v>7</v>
+      </c>
+      <c r="F1045">
+        <v>175</v>
+      </c>
+      <c r="G1045">
+        <v>0</v>
+      </c>
+      <c r="H1045">
+        <v>0</v>
+      </c>
+      <c r="I1045">
+        <v>0</v>
+      </c>
+      <c r="J1045">
+        <v>0</v>
+      </c>
+      <c r="K1045">
+        <v>0</v>
+      </c>
+      <c r="L1045">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1046" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1046" s="1">
+        <v>46172</v>
+      </c>
+      <c r="B1046" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1046">
+        <v>0</v>
+      </c>
+      <c r="D1046">
+        <v>0</v>
+      </c>
+      <c r="E1046">
+        <v>19</v>
+      </c>
+      <c r="F1046">
+        <v>475</v>
+      </c>
+      <c r="G1046">
+        <v>0</v>
+      </c>
+      <c r="H1046">
+        <v>0</v>
+      </c>
+      <c r="I1046">
+        <v>0</v>
+      </c>
+      <c r="J1046">
+        <v>0</v>
+      </c>
+      <c r="K1046">
+        <v>1</v>
+      </c>
+      <c r="L1046">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1047" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1047" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1047" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1047">
+        <v>0</v>
+      </c>
+      <c r="D1047">
+        <v>0</v>
+      </c>
+      <c r="E1047">
+        <v>7</v>
+      </c>
+      <c r="F1047">
+        <v>175</v>
+      </c>
+      <c r="G1047">
+        <v>0</v>
+      </c>
+      <c r="H1047">
+        <v>0</v>
+      </c>
+      <c r="I1047">
+        <v>1</v>
+      </c>
+      <c r="J1047">
+        <v>25</v>
+      </c>
+      <c r="K1047">
+        <v>1</v>
+      </c>
+      <c r="L1047">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1048" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1048" s="1">
+        <v>46173</v>
+      </c>
+      <c r="B1048" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1048">
+        <v>0</v>
+      </c>
+      <c r="D1048">
+        <v>0</v>
+      </c>
+      <c r="E1048">
+        <v>18</v>
+      </c>
+      <c r="F1048">
+        <v>450</v>
+      </c>
+      <c r="G1048">
+        <v>1</v>
+      </c>
+      <c r="H1048">
+        <v>15</v>
+      </c>
+      <c r="I1048">
+        <v>2</v>
+      </c>
+      <c r="J1048">
+        <v>50</v>
+      </c>
+      <c r="K1048">
+        <v>3</v>
+      </c>
+      <c r="L1048">
+        <v>75</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/dados/BD_Bombonas.xlsx
+++ b/dados/BD_Bombonas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupomateus-my.sharepoint.com/personal/hamilton_pires_grupomateus_com/Documents/hamilton/Consultoria/Lidiane/2026/app_bombonas/dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="215" documentId="8_{40E215D4-4623-41EB-B246-4B63951E0A13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{340A8610-5EA5-4A6A-BAB3-C013E52339F7}"/>
+  <xr:revisionPtr revIDLastSave="224" documentId="8_{40E215D4-4623-41EB-B246-4B63951E0A13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{005B6462-5B54-443F-9B0D-462DB860747C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{9588DCE0-F8D9-46B8-8782-90EC7820DC70}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="BASE BOMBONAS" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BASE BOMBONAS'!$A$1:$L$986</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BASE BOMBONAS'!$A$987:$L$1048</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1060" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1059" uniqueCount="14">
   <si>
     <t>DATA</t>
   </si>
@@ -81,9 +81,6 @@
   </si>
   <si>
     <t>PESO COLCHOES</t>
-  </si>
-  <si>
-    <t>31/04/2026</t>
   </si>
 </sst>
 </file>
@@ -148,6 +145,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -39886,16 +39887,16 @@
         <v>3</v>
       </c>
       <c r="C1038">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D1038">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E1038">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F1038">
-        <v>475</v>
+        <v>450</v>
       </c>
       <c r="G1038">
         <v>0</v>
@@ -40221,8 +40222,8 @@
       </c>
     </row>
     <row r="1047" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1047" s="1" t="s">
-        <v>14</v>
+      <c r="A1047" s="1">
+        <v>46173</v>
       </c>
       <c r="B1047" t="s">
         <v>2</v>

--- a/dados/BD_Bombonas.xlsx
+++ b/dados/BD_Bombonas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupomateus-my.sharepoint.com/personal/hamilton_pires_grupomateus_com/Documents/hamilton/Consultoria/Lidiane/2026/app_bombonas/dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="224" documentId="8_{40E215D4-4623-41EB-B246-4B63951E0A13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{005B6462-5B54-443F-9B0D-462DB860747C}"/>
+  <xr:revisionPtr revIDLastSave="230" documentId="8_{40E215D4-4623-41EB-B246-4B63951E0A13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{554A3A8C-3798-499D-A62C-01DAE64160D0}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{9588DCE0-F8D9-46B8-8782-90EC7820DC70}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1059" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1101" uniqueCount="14">
   <si>
     <t>DATA</t>
   </si>
@@ -471,7 +471,7 @@
   <sheetPr>
     <tabColor theme="6" tint="0.39997558519241921"/>
   </sheetPr>
-  <dimension ref="A1:L1048"/>
+  <dimension ref="A1:L1090"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
@@ -40297,6 +40297,1602 @@
         <v>75</v>
       </c>
     </row>
+    <row r="1049" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1049" s="1">
+        <v>46174</v>
+      </c>
+      <c r="B1049" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1049">
+        <v>0</v>
+      </c>
+      <c r="D1049">
+        <v>0</v>
+      </c>
+      <c r="E1049">
+        <v>6</v>
+      </c>
+      <c r="F1049">
+        <v>150</v>
+      </c>
+      <c r="G1049">
+        <v>0</v>
+      </c>
+      <c r="H1049">
+        <v>0</v>
+      </c>
+      <c r="I1049">
+        <v>0</v>
+      </c>
+      <c r="J1049">
+        <v>0</v>
+      </c>
+      <c r="K1049">
+        <v>1</v>
+      </c>
+      <c r="L1049">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1050" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1050" s="1">
+        <v>46174</v>
+      </c>
+      <c r="B1050" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1050">
+        <v>0</v>
+      </c>
+      <c r="D1050">
+        <v>0</v>
+      </c>
+      <c r="E1050">
+        <v>18</v>
+      </c>
+      <c r="F1050">
+        <v>450</v>
+      </c>
+      <c r="G1050">
+        <v>0</v>
+      </c>
+      <c r="H1050">
+        <v>0</v>
+      </c>
+      <c r="I1050">
+        <v>1</v>
+      </c>
+      <c r="J1050">
+        <v>25</v>
+      </c>
+      <c r="K1050">
+        <v>1</v>
+      </c>
+      <c r="L1050">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1051" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1051" s="1">
+        <v>46175</v>
+      </c>
+      <c r="B1051" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1051">
+        <v>0</v>
+      </c>
+      <c r="D1051">
+        <v>0</v>
+      </c>
+      <c r="E1051">
+        <v>7</v>
+      </c>
+      <c r="F1051">
+        <v>131</v>
+      </c>
+      <c r="G1051">
+        <v>0</v>
+      </c>
+      <c r="H1051">
+        <v>0</v>
+      </c>
+      <c r="I1051">
+        <v>0</v>
+      </c>
+      <c r="J1051">
+        <v>0</v>
+      </c>
+      <c r="K1051">
+        <v>0</v>
+      </c>
+      <c r="L1051">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1052" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1052" s="1">
+        <v>46175</v>
+      </c>
+      <c r="B1052" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1052">
+        <v>0</v>
+      </c>
+      <c r="D1052">
+        <v>0</v>
+      </c>
+      <c r="E1052">
+        <v>20</v>
+      </c>
+      <c r="F1052">
+        <v>452</v>
+      </c>
+      <c r="G1052">
+        <v>0</v>
+      </c>
+      <c r="H1052">
+        <v>0</v>
+      </c>
+      <c r="I1052">
+        <v>1</v>
+      </c>
+      <c r="J1052">
+        <v>50</v>
+      </c>
+      <c r="K1052">
+        <v>2</v>
+      </c>
+      <c r="L1052">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1053" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1053" s="1">
+        <v>46176</v>
+      </c>
+      <c r="B1053" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1053">
+        <v>0</v>
+      </c>
+      <c r="D1053">
+        <v>0</v>
+      </c>
+      <c r="E1053">
+        <v>6</v>
+      </c>
+      <c r="F1053">
+        <v>112</v>
+      </c>
+      <c r="G1053">
+        <v>0</v>
+      </c>
+      <c r="H1053">
+        <v>0</v>
+      </c>
+      <c r="I1053">
+        <v>0</v>
+      </c>
+      <c r="J1053">
+        <v>0</v>
+      </c>
+      <c r="K1053">
+        <v>0</v>
+      </c>
+      <c r="L1053">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1054" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1054" s="1">
+        <v>46176</v>
+      </c>
+      <c r="B1054" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1054">
+        <v>0</v>
+      </c>
+      <c r="D1054">
+        <v>0</v>
+      </c>
+      <c r="E1054">
+        <v>22</v>
+      </c>
+      <c r="F1054">
+        <v>550</v>
+      </c>
+      <c r="G1054">
+        <v>0</v>
+      </c>
+      <c r="H1054">
+        <v>0</v>
+      </c>
+      <c r="I1054">
+        <v>2</v>
+      </c>
+      <c r="J1054">
+        <v>50</v>
+      </c>
+      <c r="K1054">
+        <v>1</v>
+      </c>
+      <c r="L1054">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1055" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1055" s="1">
+        <v>46177</v>
+      </c>
+      <c r="B1055" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1055">
+        <v>0</v>
+      </c>
+      <c r="D1055">
+        <v>0</v>
+      </c>
+      <c r="E1055">
+        <v>6</v>
+      </c>
+      <c r="F1055">
+        <v>150</v>
+      </c>
+      <c r="G1055">
+        <v>0</v>
+      </c>
+      <c r="H1055">
+        <v>0</v>
+      </c>
+      <c r="I1055">
+        <v>0</v>
+      </c>
+      <c r="J1055">
+        <v>0</v>
+      </c>
+      <c r="K1055">
+        <v>2</v>
+      </c>
+      <c r="L1055">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1056" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1056" s="1">
+        <v>46177</v>
+      </c>
+      <c r="B1056" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1056">
+        <v>0</v>
+      </c>
+      <c r="D1056">
+        <v>0</v>
+      </c>
+      <c r="E1056">
+        <v>22</v>
+      </c>
+      <c r="F1056">
+        <v>550</v>
+      </c>
+      <c r="G1056">
+        <v>0</v>
+      </c>
+      <c r="H1056">
+        <v>0</v>
+      </c>
+      <c r="I1056">
+        <v>1</v>
+      </c>
+      <c r="J1056">
+        <v>25</v>
+      </c>
+      <c r="K1056">
+        <v>3</v>
+      </c>
+      <c r="L1056">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="1057" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1057" s="1">
+        <v>46178</v>
+      </c>
+      <c r="B1057" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1057">
+        <v>0</v>
+      </c>
+      <c r="D1057">
+        <v>0</v>
+      </c>
+      <c r="E1057">
+        <v>8</v>
+      </c>
+      <c r="F1057">
+        <v>129</v>
+      </c>
+      <c r="G1057">
+        <v>0</v>
+      </c>
+      <c r="H1057">
+        <v>0</v>
+      </c>
+      <c r="I1057">
+        <v>0</v>
+      </c>
+      <c r="J1057">
+        <v>0</v>
+      </c>
+      <c r="K1057">
+        <v>0</v>
+      </c>
+      <c r="L1057">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1058" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1058" s="1">
+        <v>46178</v>
+      </c>
+      <c r="B1058" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1058">
+        <v>0</v>
+      </c>
+      <c r="D1058">
+        <v>0</v>
+      </c>
+      <c r="E1058">
+        <v>20</v>
+      </c>
+      <c r="F1058">
+        <v>395</v>
+      </c>
+      <c r="G1058">
+        <v>0</v>
+      </c>
+      <c r="H1058">
+        <v>0</v>
+      </c>
+      <c r="I1058">
+        <v>1</v>
+      </c>
+      <c r="J1058">
+        <v>30</v>
+      </c>
+      <c r="K1058">
+        <v>2</v>
+      </c>
+      <c r="L1058">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1059" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1059" s="1">
+        <v>46179</v>
+      </c>
+      <c r="B1059" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1059">
+        <v>0</v>
+      </c>
+      <c r="D1059">
+        <v>0</v>
+      </c>
+      <c r="E1059">
+        <v>6</v>
+      </c>
+      <c r="F1059">
+        <v>150</v>
+      </c>
+      <c r="G1059">
+        <v>0</v>
+      </c>
+      <c r="H1059">
+        <v>0</v>
+      </c>
+      <c r="I1059">
+        <v>0</v>
+      </c>
+      <c r="J1059">
+        <v>0</v>
+      </c>
+      <c r="K1059">
+        <v>0</v>
+      </c>
+      <c r="L1059">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1060" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1060" s="1">
+        <v>46179</v>
+      </c>
+      <c r="B1060" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1060">
+        <v>0</v>
+      </c>
+      <c r="D1060">
+        <v>0</v>
+      </c>
+      <c r="E1060">
+        <v>20</v>
+      </c>
+      <c r="F1060">
+        <v>500</v>
+      </c>
+      <c r="G1060">
+        <v>0</v>
+      </c>
+      <c r="H1060">
+        <v>0</v>
+      </c>
+      <c r="I1060">
+        <v>2</v>
+      </c>
+      <c r="J1060">
+        <v>50</v>
+      </c>
+      <c r="K1060">
+        <v>3</v>
+      </c>
+      <c r="L1060">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="1061" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1061" s="1">
+        <v>46180</v>
+      </c>
+      <c r="B1061" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1061">
+        <v>0</v>
+      </c>
+      <c r="D1061">
+        <v>0</v>
+      </c>
+      <c r="E1061">
+        <v>6</v>
+      </c>
+      <c r="F1061">
+        <v>147</v>
+      </c>
+      <c r="G1061">
+        <v>0</v>
+      </c>
+      <c r="H1061">
+        <v>0</v>
+      </c>
+      <c r="I1061">
+        <v>0</v>
+      </c>
+      <c r="J1061">
+        <v>0</v>
+      </c>
+      <c r="K1061">
+        <v>1</v>
+      </c>
+      <c r="L1061">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1062" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1062" s="1">
+        <v>46180</v>
+      </c>
+      <c r="B1062" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1062">
+        <v>0</v>
+      </c>
+      <c r="D1062">
+        <v>0</v>
+      </c>
+      <c r="E1062">
+        <v>20</v>
+      </c>
+      <c r="F1062">
+        <v>486</v>
+      </c>
+      <c r="G1062">
+        <v>0</v>
+      </c>
+      <c r="H1062">
+        <v>0</v>
+      </c>
+      <c r="I1062">
+        <v>0</v>
+      </c>
+      <c r="J1062">
+        <v>0</v>
+      </c>
+      <c r="K1062">
+        <v>1</v>
+      </c>
+      <c r="L1062">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1063" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1063" s="1">
+        <v>46181</v>
+      </c>
+      <c r="B1063" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1063">
+        <v>0</v>
+      </c>
+      <c r="D1063">
+        <v>0</v>
+      </c>
+      <c r="E1063">
+        <v>7</v>
+      </c>
+      <c r="F1063">
+        <v>98</v>
+      </c>
+      <c r="G1063">
+        <v>0</v>
+      </c>
+      <c r="H1063">
+        <v>0</v>
+      </c>
+      <c r="I1063">
+        <v>0</v>
+      </c>
+      <c r="J1063">
+        <v>0</v>
+      </c>
+      <c r="K1063">
+        <v>1</v>
+      </c>
+      <c r="L1063">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1064" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1064" s="1">
+        <v>46181</v>
+      </c>
+      <c r="B1064" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1064">
+        <v>1</v>
+      </c>
+      <c r="D1064">
+        <v>25</v>
+      </c>
+      <c r="E1064">
+        <v>20</v>
+      </c>
+      <c r="F1064">
+        <v>407</v>
+      </c>
+      <c r="G1064">
+        <v>1</v>
+      </c>
+      <c r="H1064">
+        <v>25</v>
+      </c>
+      <c r="I1064">
+        <v>1</v>
+      </c>
+      <c r="J1064">
+        <v>32</v>
+      </c>
+      <c r="K1064">
+        <v>1</v>
+      </c>
+      <c r="L1064">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1065" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1065" s="1">
+        <v>46182</v>
+      </c>
+      <c r="B1065" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1065">
+        <v>0</v>
+      </c>
+      <c r="D1065">
+        <v>0</v>
+      </c>
+      <c r="E1065">
+        <v>7</v>
+      </c>
+      <c r="F1065">
+        <v>115</v>
+      </c>
+      <c r="G1065">
+        <v>0</v>
+      </c>
+      <c r="H1065">
+        <v>0</v>
+      </c>
+      <c r="I1065">
+        <v>0</v>
+      </c>
+      <c r="J1065">
+        <v>0</v>
+      </c>
+      <c r="K1065">
+        <v>0</v>
+      </c>
+      <c r="L1065">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1066" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1066" s="1">
+        <v>46182</v>
+      </c>
+      <c r="B1066" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1066">
+        <v>0</v>
+      </c>
+      <c r="D1066">
+        <v>0</v>
+      </c>
+      <c r="E1066">
+        <v>20</v>
+      </c>
+      <c r="F1066">
+        <v>404</v>
+      </c>
+      <c r="G1066">
+        <v>0</v>
+      </c>
+      <c r="H1066">
+        <v>0</v>
+      </c>
+      <c r="I1066">
+        <v>2</v>
+      </c>
+      <c r="J1066">
+        <v>40</v>
+      </c>
+      <c r="K1066">
+        <v>1</v>
+      </c>
+      <c r="L1066">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1067" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1067" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B1067" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1067">
+        <v>0</v>
+      </c>
+      <c r="D1067">
+        <v>0</v>
+      </c>
+      <c r="E1067">
+        <v>6</v>
+      </c>
+      <c r="F1067">
+        <v>127</v>
+      </c>
+      <c r="G1067">
+        <v>0</v>
+      </c>
+      <c r="H1067">
+        <v>0</v>
+      </c>
+      <c r="I1067">
+        <v>0</v>
+      </c>
+      <c r="J1067">
+        <v>0</v>
+      </c>
+      <c r="K1067">
+        <v>1</v>
+      </c>
+      <c r="L1067">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1068" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1068" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B1068" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1068">
+        <v>0</v>
+      </c>
+      <c r="D1068">
+        <v>0</v>
+      </c>
+      <c r="E1068">
+        <v>20</v>
+      </c>
+      <c r="F1068">
+        <v>410</v>
+      </c>
+      <c r="G1068">
+        <v>0</v>
+      </c>
+      <c r="H1068">
+        <v>0</v>
+      </c>
+      <c r="I1068">
+        <v>1</v>
+      </c>
+      <c r="J1068">
+        <v>19</v>
+      </c>
+      <c r="K1068">
+        <v>4</v>
+      </c>
+      <c r="L1068">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="1069" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1069" s="1">
+        <v>46184</v>
+      </c>
+      <c r="B1069" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1069">
+        <v>0</v>
+      </c>
+      <c r="D1069">
+        <v>0</v>
+      </c>
+      <c r="E1069">
+        <v>7</v>
+      </c>
+      <c r="F1069">
+        <v>127</v>
+      </c>
+      <c r="G1069">
+        <v>0</v>
+      </c>
+      <c r="H1069">
+        <v>0</v>
+      </c>
+      <c r="I1069">
+        <v>0</v>
+      </c>
+      <c r="J1069">
+        <v>0</v>
+      </c>
+      <c r="K1069">
+        <v>0</v>
+      </c>
+      <c r="L1069">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1070" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1070" s="1">
+        <v>46184</v>
+      </c>
+      <c r="B1070" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1070">
+        <v>0</v>
+      </c>
+      <c r="D1070">
+        <v>0</v>
+      </c>
+      <c r="E1070">
+        <v>21</v>
+      </c>
+      <c r="F1070">
+        <v>508</v>
+      </c>
+      <c r="G1070">
+        <v>0</v>
+      </c>
+      <c r="H1070">
+        <v>0</v>
+      </c>
+      <c r="I1070">
+        <v>1</v>
+      </c>
+      <c r="J1070">
+        <v>37</v>
+      </c>
+      <c r="K1070">
+        <v>0</v>
+      </c>
+      <c r="L1070">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1071" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1071" s="1">
+        <v>46185</v>
+      </c>
+      <c r="B1071" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1071">
+        <v>0</v>
+      </c>
+      <c r="D1071">
+        <v>0</v>
+      </c>
+      <c r="E1071">
+        <v>7</v>
+      </c>
+      <c r="F1071">
+        <v>128</v>
+      </c>
+      <c r="G1071">
+        <v>0</v>
+      </c>
+      <c r="H1071">
+        <v>0</v>
+      </c>
+      <c r="I1071">
+        <v>0</v>
+      </c>
+      <c r="J1071">
+        <v>0</v>
+      </c>
+      <c r="K1071">
+        <v>0</v>
+      </c>
+      <c r="L1071">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1072" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1072" s="1">
+        <v>46185</v>
+      </c>
+      <c r="B1072" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1072">
+        <v>0</v>
+      </c>
+      <c r="D1072">
+        <v>1</v>
+      </c>
+      <c r="E1072">
+        <v>19</v>
+      </c>
+      <c r="F1072">
+        <v>373</v>
+      </c>
+      <c r="G1072">
+        <v>15</v>
+      </c>
+      <c r="H1072">
+        <v>0</v>
+      </c>
+      <c r="I1072">
+        <v>1</v>
+      </c>
+      <c r="J1072">
+        <v>30</v>
+      </c>
+      <c r="K1072">
+        <v>2</v>
+      </c>
+      <c r="L1072">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="1073" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1073" s="1">
+        <v>46186</v>
+      </c>
+      <c r="B1073" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1073">
+        <v>0</v>
+      </c>
+      <c r="D1073">
+        <v>0</v>
+      </c>
+      <c r="E1073">
+        <v>7</v>
+      </c>
+      <c r="F1073">
+        <v>140</v>
+      </c>
+      <c r="G1073">
+        <v>0</v>
+      </c>
+      <c r="H1073">
+        <v>0</v>
+      </c>
+      <c r="I1073">
+        <v>0</v>
+      </c>
+      <c r="J1073">
+        <v>0</v>
+      </c>
+      <c r="K1073">
+        <v>1</v>
+      </c>
+      <c r="L1073">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1074" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1074" s="1">
+        <v>46186</v>
+      </c>
+      <c r="B1074" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1074">
+        <v>0</v>
+      </c>
+      <c r="D1074">
+        <v>0</v>
+      </c>
+      <c r="E1074">
+        <v>20</v>
+      </c>
+      <c r="F1074">
+        <v>440</v>
+      </c>
+      <c r="G1074">
+        <v>0</v>
+      </c>
+      <c r="H1074">
+        <v>0</v>
+      </c>
+      <c r="I1074">
+        <v>0</v>
+      </c>
+      <c r="J1074">
+        <v>0</v>
+      </c>
+      <c r="K1074">
+        <v>2</v>
+      </c>
+      <c r="L1074">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="1075" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1075" s="1">
+        <v>46187</v>
+      </c>
+      <c r="B1075" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1075">
+        <v>0</v>
+      </c>
+      <c r="D1075">
+        <v>0</v>
+      </c>
+      <c r="E1075">
+        <v>6</v>
+      </c>
+      <c r="F1075">
+        <v>144</v>
+      </c>
+      <c r="G1075">
+        <v>0</v>
+      </c>
+      <c r="H1075">
+        <v>0</v>
+      </c>
+      <c r="I1075">
+        <v>0</v>
+      </c>
+      <c r="J1075">
+        <v>0</v>
+      </c>
+      <c r="K1075">
+        <v>1</v>
+      </c>
+      <c r="L1075">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1076" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1076" s="1">
+        <v>46187</v>
+      </c>
+      <c r="B1076" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1076">
+        <v>0</v>
+      </c>
+      <c r="D1076">
+        <v>0</v>
+      </c>
+      <c r="E1076">
+        <v>19</v>
+      </c>
+      <c r="F1076">
+        <v>371</v>
+      </c>
+      <c r="G1076">
+        <v>0</v>
+      </c>
+      <c r="H1076">
+        <v>0</v>
+      </c>
+      <c r="I1076">
+        <v>1</v>
+      </c>
+      <c r="J1076">
+        <v>20</v>
+      </c>
+      <c r="K1076">
+        <v>3</v>
+      </c>
+      <c r="L1076">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="1077" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1077" s="1">
+        <v>46188</v>
+      </c>
+      <c r="B1077" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1077">
+        <v>0</v>
+      </c>
+      <c r="D1077">
+        <v>0</v>
+      </c>
+      <c r="E1077">
+        <v>6</v>
+      </c>
+      <c r="F1077">
+        <v>125</v>
+      </c>
+      <c r="G1077">
+        <v>0</v>
+      </c>
+      <c r="H1077">
+        <v>0</v>
+      </c>
+      <c r="I1077">
+        <v>0</v>
+      </c>
+      <c r="J1077">
+        <v>0</v>
+      </c>
+      <c r="K1077">
+        <v>0</v>
+      </c>
+      <c r="L1077">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1078" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1078" s="1">
+        <v>46188</v>
+      </c>
+      <c r="B1078" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1078">
+        <v>0</v>
+      </c>
+      <c r="D1078">
+        <v>0</v>
+      </c>
+      <c r="E1078">
+        <v>20</v>
+      </c>
+      <c r="F1078">
+        <v>440</v>
+      </c>
+      <c r="G1078">
+        <v>0</v>
+      </c>
+      <c r="H1078">
+        <v>0</v>
+      </c>
+      <c r="I1078">
+        <v>1</v>
+      </c>
+      <c r="J1078">
+        <v>48</v>
+      </c>
+      <c r="K1078">
+        <v>1</v>
+      </c>
+      <c r="L1078">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1079" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1079" s="1">
+        <v>46189</v>
+      </c>
+      <c r="B1079" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1079">
+        <v>0</v>
+      </c>
+      <c r="D1079">
+        <v>0</v>
+      </c>
+      <c r="E1079">
+        <v>9</v>
+      </c>
+      <c r="F1079">
+        <v>192</v>
+      </c>
+      <c r="G1079">
+        <v>0</v>
+      </c>
+      <c r="H1079">
+        <v>0</v>
+      </c>
+      <c r="I1079">
+        <v>0</v>
+      </c>
+      <c r="J1079">
+        <v>0</v>
+      </c>
+      <c r="K1079">
+        <v>0</v>
+      </c>
+      <c r="L1079">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1080" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1080" s="1">
+        <v>46189</v>
+      </c>
+      <c r="B1080" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1080">
+        <v>0</v>
+      </c>
+      <c r="D1080">
+        <v>0</v>
+      </c>
+      <c r="E1080">
+        <v>22</v>
+      </c>
+      <c r="F1080">
+        <v>452</v>
+      </c>
+      <c r="G1080">
+        <v>0</v>
+      </c>
+      <c r="H1080">
+        <v>0</v>
+      </c>
+      <c r="I1080">
+        <v>1</v>
+      </c>
+      <c r="J1080">
+        <v>40</v>
+      </c>
+      <c r="K1080">
+        <v>2</v>
+      </c>
+      <c r="L1080">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="1081" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1081" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B1081" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1081">
+        <v>0</v>
+      </c>
+      <c r="D1081">
+        <v>0</v>
+      </c>
+      <c r="E1081">
+        <v>6</v>
+      </c>
+      <c r="F1081">
+        <v>120</v>
+      </c>
+      <c r="G1081">
+        <v>0</v>
+      </c>
+      <c r="H1081">
+        <v>0</v>
+      </c>
+      <c r="I1081">
+        <v>0</v>
+      </c>
+      <c r="J1081">
+        <v>0</v>
+      </c>
+      <c r="K1081">
+        <v>1</v>
+      </c>
+      <c r="L1081">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1082" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1082" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B1082" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1082">
+        <v>0</v>
+      </c>
+      <c r="D1082">
+        <v>0</v>
+      </c>
+      <c r="E1082">
+        <v>22</v>
+      </c>
+      <c r="F1082">
+        <v>455</v>
+      </c>
+      <c r="G1082">
+        <v>0</v>
+      </c>
+      <c r="H1082">
+        <v>0</v>
+      </c>
+      <c r="I1082">
+        <v>1</v>
+      </c>
+      <c r="J1082">
+        <v>24</v>
+      </c>
+      <c r="K1082">
+        <v>1</v>
+      </c>
+      <c r="L1082">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1083" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1083" s="1">
+        <v>46191</v>
+      </c>
+      <c r="B1083" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1083">
+        <v>0</v>
+      </c>
+      <c r="D1083">
+        <v>0</v>
+      </c>
+      <c r="E1083">
+        <v>14</v>
+      </c>
+      <c r="F1083">
+        <v>258</v>
+      </c>
+      <c r="G1083">
+        <v>0</v>
+      </c>
+      <c r="H1083">
+        <v>0</v>
+      </c>
+      <c r="I1083">
+        <v>0</v>
+      </c>
+      <c r="J1083">
+        <v>0</v>
+      </c>
+      <c r="K1083">
+        <v>0</v>
+      </c>
+      <c r="L1083">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1084" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1084" s="1">
+        <v>46191</v>
+      </c>
+      <c r="B1084" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1084">
+        <v>2</v>
+      </c>
+      <c r="D1084">
+        <v>50</v>
+      </c>
+      <c r="E1084">
+        <v>21</v>
+      </c>
+      <c r="F1084">
+        <v>434</v>
+      </c>
+      <c r="G1084">
+        <v>0</v>
+      </c>
+      <c r="H1084">
+        <v>0</v>
+      </c>
+      <c r="I1084">
+        <v>1</v>
+      </c>
+      <c r="J1084">
+        <v>16</v>
+      </c>
+      <c r="K1084">
+        <v>3</v>
+      </c>
+      <c r="L1084">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="1085" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1085" s="1">
+        <v>46192</v>
+      </c>
+      <c r="B1085" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1085">
+        <v>0</v>
+      </c>
+      <c r="D1085">
+        <v>0</v>
+      </c>
+      <c r="E1085">
+        <v>16</v>
+      </c>
+      <c r="F1085">
+        <v>332</v>
+      </c>
+      <c r="G1085">
+        <v>0</v>
+      </c>
+      <c r="H1085">
+        <v>0</v>
+      </c>
+      <c r="I1085">
+        <v>2</v>
+      </c>
+      <c r="J1085">
+        <v>50</v>
+      </c>
+      <c r="K1085">
+        <v>1</v>
+      </c>
+      <c r="L1085">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1086" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1086" s="1">
+        <v>46192</v>
+      </c>
+      <c r="B1086" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1086">
+        <v>0</v>
+      </c>
+      <c r="D1086">
+        <v>0</v>
+      </c>
+      <c r="E1086">
+        <v>21</v>
+      </c>
+      <c r="F1086">
+        <v>525</v>
+      </c>
+      <c r="G1086">
+        <v>0</v>
+      </c>
+      <c r="H1086">
+        <v>0</v>
+      </c>
+      <c r="I1086">
+        <v>0</v>
+      </c>
+      <c r="J1086">
+        <v>0</v>
+      </c>
+      <c r="K1086">
+        <v>2</v>
+      </c>
+      <c r="L1086">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1087" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1087" s="1">
+        <v>46193</v>
+      </c>
+      <c r="B1087" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1087">
+        <v>0</v>
+      </c>
+      <c r="D1087">
+        <v>0</v>
+      </c>
+      <c r="E1087">
+        <v>15</v>
+      </c>
+      <c r="F1087">
+        <v>335</v>
+      </c>
+      <c r="G1087">
+        <v>0</v>
+      </c>
+      <c r="H1087">
+        <v>0</v>
+      </c>
+      <c r="I1087">
+        <v>0</v>
+      </c>
+      <c r="J1087">
+        <v>0</v>
+      </c>
+      <c r="K1087">
+        <v>0</v>
+      </c>
+      <c r="L1087">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1088" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1088" s="1">
+        <v>46193</v>
+      </c>
+      <c r="B1088" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1088">
+        <v>0</v>
+      </c>
+      <c r="D1088">
+        <v>0</v>
+      </c>
+      <c r="E1088">
+        <v>18</v>
+      </c>
+      <c r="F1088">
+        <v>450</v>
+      </c>
+      <c r="G1088">
+        <v>0</v>
+      </c>
+      <c r="H1088">
+        <v>0</v>
+      </c>
+      <c r="I1088">
+        <v>0</v>
+      </c>
+      <c r="J1088">
+        <v>0</v>
+      </c>
+      <c r="K1088">
+        <v>2</v>
+      </c>
+      <c r="L1088">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1089" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1089" s="1">
+        <v>46194</v>
+      </c>
+      <c r="B1089" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1089">
+        <v>0</v>
+      </c>
+      <c r="D1089">
+        <v>0</v>
+      </c>
+      <c r="E1089">
+        <v>9</v>
+      </c>
+      <c r="F1089">
+        <v>225</v>
+      </c>
+      <c r="G1089">
+        <v>0</v>
+      </c>
+      <c r="H1089">
+        <v>0</v>
+      </c>
+      <c r="I1089">
+        <v>0</v>
+      </c>
+      <c r="J1089">
+        <v>0</v>
+      </c>
+      <c r="K1089">
+        <v>0</v>
+      </c>
+      <c r="L1089">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1090" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1090" s="1">
+        <v>46194</v>
+      </c>
+      <c r="B1090" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1090">
+        <v>0</v>
+      </c>
+      <c r="D1090">
+        <v>0</v>
+      </c>
+      <c r="E1090">
+        <v>18</v>
+      </c>
+      <c r="F1090">
+        <v>450</v>
+      </c>
+      <c r="G1090">
+        <v>0</v>
+      </c>
+      <c r="H1090">
+        <v>0</v>
+      </c>
+      <c r="I1090">
+        <v>0</v>
+      </c>
+      <c r="J1090">
+        <v>0</v>
+      </c>
+      <c r="K1090">
+        <v>2</v>
+      </c>
+      <c r="L1090">
+        <v>50</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
